--- a/BDT-September-2026.xlsx
+++ b/BDT-September-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e9fde80517f38ba/Documents/Glass-Transition-Model/Tensile-Compressive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{C6E70166-2613-4CD1-8E92-5F0BF076E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC312CE7-3F1F-4B46-B613-2E80C0179A14}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{C6E70166-2613-4CD1-8E92-5F0BF076E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DF6808-3A06-4E35-9E12-397CF9DCBD0C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{72BE8CD8-FBE8-40DE-B611-7B1BCBBA4B2A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{72BE8CD8-FBE8-40DE-B611-7B1BCBBA4B2A}"/>
   </bookViews>
   <sheets>
     <sheet name="FictiveCalc" sheetId="3" r:id="rId1"/>
@@ -1005,64 +1005,64 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.14467767829500935</c:v>
+                  <c:v>0.14467767838622869</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.3482546295753024E-2</c:v>
+                  <c:v>8.3482546350073378E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8171463754149497E-2</c:v>
+                  <c:v>4.8171463786465737E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7796108566173056E-2</c:v>
+                  <c:v>2.7796108585381195E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6039032057769499E-2</c:v>
+                  <c:v>1.6039032069176715E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.2549123823477582E-3</c:v>
+                  <c:v>9.2549123891167585E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.3403099947943369E-3</c:v>
+                  <c:v>5.3403099988079796E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.0814890149468851E-3</c:v>
+                  <c:v>3.0814890173250344E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7780942601636389E-3</c:v>
+                  <c:v>1.7780942615717701E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0260037218017967E-3</c:v>
+                  <c:v>1.0260037226350258E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.9202915207333666E-4</c:v>
+                  <c:v>5.9202915256607587E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.4161524900626328E-4</c:v>
+                  <c:v>3.4161524929747977E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9712032413423165E-4</c:v>
+                  <c:v>1.9712032430624823E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1374323101739647E-4</c:v>
+                  <c:v>1.1374323111894951E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.5632616317467328E-5</c:v>
+                  <c:v>6.5632616377390342E-5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.7871619138522769E-5</c:v>
+                  <c:v>3.7871619173864033E-5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.1852847206879107E-5</c:v>
+                  <c:v>2.1852847227712818E-5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.2609625411062715E-5</c:v>
+                  <c:v>1.2609625423338728E-5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.276061169606483E-6</c:v>
+                  <c:v>7.276061176836868E-6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.1984646187355667E-6</c:v>
+                  <c:v>4.1984646229924045E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1573,97 +1573,97 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>0.30803175836306385</c:v>
+                  <c:v>0.3080317603530463</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.1519748308033648E-2</c:v>
+                  <c:v>7.1519748833780858E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4873651594740619E-2</c:v>
+                  <c:v>1.4873651718768232E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7584150601495864E-3</c:v>
+                  <c:v>2.7584150861537011E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.5497920197831097E-4</c:v>
+                  <c:v>4.5497920680963126E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.8629782495154997E-5</c:v>
+                  <c:v>8.8629783528930696E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.3521805295200755E-5</c:v>
+                  <c:v>3.3521805701667825E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2678711361057238E-5</c:v>
+                  <c:v>1.2678711520643298E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.7953778253110561E-6</c:v>
+                  <c:v>4.7953778878831053E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.8137212712418483E-6</c:v>
+                  <c:v>1.8137212957450137E-6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.8599075392808256E-7</c:v>
+                  <c:v>6.8599076351230822E-7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.594573498896038E-7</c:v>
+                  <c:v>2.5945735363430999E-7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.8132687687500087E-8</c:v>
+                  <c:v>9.8132689149119627E-8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.7116020790584137E-8</c:v>
+                  <c:v>3.7116021360530141E-8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.403812564182479E-8</c:v>
+                  <c:v>1.4038125863869629E-8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.3095393131596276E-9</c:v>
+                  <c:v>5.3095393995922956E-9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.008188873448741E-9</c:v>
+                  <c:v>2.0081889070662718E-9</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.595428366916843E-10</c:v>
+                  <c:v>7.5954284975711219E-10</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.8727642523928175E-10</c:v>
+                  <c:v>2.8727643031349683E-10</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0865449650966854E-10</c:v>
+                  <c:v>1.0865449847899388E-10</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.1095608878926082E-11</c:v>
+                  <c:v>4.1095609642734636E-11</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.554329662720763E-11</c:v>
+                  <c:v>1.5543296923270308E-11</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.878829311256514E-12</c:v>
+                  <c:v>5.8788294259471117E-12</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.2235073356569755E-12</c:v>
+                  <c:v>2.2235073800616795E-12</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.4098119029478641E-13</c:v>
+                  <c:v>8.4098120747774798E-13</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.1807826809830204E-13</c:v>
+                  <c:v>3.1807827474407783E-13</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.2030445603777559E-13</c:v>
+                  <c:v>1.2030445860687677E-13</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.5501889296228487E-14</c:v>
+                  <c:v>4.5501890288919204E-14</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.7209852383822929E-14</c:v>
+                  <c:v>1.7209852767223197E-14</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.5091587108565196E-15</c:v>
+                  <c:v>6.5091588588710679E-15</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.4619122917606277E-15</c:v>
+                  <c:v>2.4619123488792371E-15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2207,127 +2207,127 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>4726.5754464530355</c:v>
+                  <c:v>4726.575419991188</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2248.0446294983572</c:v>
+                  <c:v>2248.0446152389682</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1040.2958384659935</c:v>
+                  <c:v>1040.2958310186398</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>468.36012230271689</c:v>
+                  <c:v>468.36011853417642</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>205.26771346110047</c:v>
+                  <c:v>205.26771161294542</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100.0532310396873</c:v>
+                  <c:v>100.05323007074396</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>55.815163341321316</c:v>
+                  <c:v>55.815162782409722</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>31.136750172342467</c:v>
+                  <c:v>31.136749850296617</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.369781852400802</c:v>
+                  <c:v>17.369781667025496</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.6898141241466362</c:v>
+                  <c:v>9.6898140175429699</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.4055081726622296</c:v>
+                  <c:v>5.4055081114126393</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.0154880403643856</c:v>
+                  <c:v>3.0154880052029074</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.6822041205243856</c:v>
+                  <c:v>1.6822041003553803</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.93842544398460037</c:v>
+                  <c:v>0.93842543242417109</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.52350502722772008</c:v>
+                  <c:v>0.52350502060627169</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.29203973026246371</c:v>
+                  <c:v>0.2920397264724785</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16291573073026674</c:v>
+                  <c:v>0.16291572856235176</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.0883303088669889E-2</c:v>
+                  <c:v>9.0883301849357348E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.0699676104221304E-2</c:v>
+                  <c:v>5.0699675396167744E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.8283051668633666E-2</c:v>
+                  <c:v>2.8283051264328105E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.5777832782328038E-2</c:v>
+                  <c:v>1.5777832551588083E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.8017378825915437E-3</c:v>
+                  <c:v>8.8017377509734609E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.9100906837229357E-3</c:v>
+                  <c:v>4.9100906086820958E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.7391170748297731E-3</c:v>
+                  <c:v>2.7391170320658002E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.52802928355191E-3</c:v>
+                  <c:v>1.5280292591925944E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.5241828939979435E-4</c:v>
+                  <c:v>8.5241827553010434E-4</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.755255333943921E-4</c:v>
+                  <c:v>4.7552552550051308E-4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.6527414500835989E-4</c:v>
+                  <c:v>2.6527414051735803E-4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.4798442369140475E-4</c:v>
+                  <c:v>1.4798442113734194E-4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.2553803555137205E-5</c:v>
+                  <c:v>8.2553802103153462E-5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.6053025794335568E-5</c:v>
+                  <c:v>4.6053024969172699E-5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.5690896039662573E-5</c:v>
+                  <c:v>2.5690895570880695E-5</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.4331786629358269E-5</c:v>
+                  <c:v>1.4331786363126124E-5</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>7.9950542663964714E-6</c:v>
+                  <c:v>7.9950541152445583E-6</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.4600784518856455E-6</c:v>
+                  <c:v>4.4600783660959929E-6</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.4880756445372812E-6</c:v>
+                  <c:v>2.4880755958597029E-6</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.3879846463961498E-6</c:v>
+                  <c:v>1.3879846187840232E-6</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>7.7429373293419493E-7</c:v>
+                  <c:v>7.7429371727563904E-7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.3194338382476935E-7</c:v>
+                  <c:v>4.3194337494731667E-7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.4096163883822647E-7</c:v>
+                  <c:v>2.4096163380654049E-7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.3442157830378663E-7</c:v>
+                  <c:v>1.3442157545256711E-7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6846,7 +6846,7 @@
     <col min="25" max="25" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="60">
+    <row r="1" spans="1:27" ht="30">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6947,19 +6947,19 @@
       </c>
       <c r="Q2">
         <f>-0.5*$A$13*$C$13*I2</f>
-        <v>8.4947117158515031</v>
+        <v>8.4947117160403707</v>
       </c>
       <c r="R2">
         <f>-(1 - 0.5*$A$13*$C$13)*M2</f>
-        <v>-0.46698500762558909</v>
+        <v>-0.46698500753353839</v>
       </c>
       <c r="T2">
         <f>P2 + Q2 + R2</f>
-        <v>4.7627332861764229</v>
+        <v>4.7627332864573413</v>
       </c>
       <c r="V2" s="7">
         <f>EXP(T2)</f>
-        <v>117.06546241784406</v>
+        <v>117.0654624507299</v>
       </c>
       <c r="W2">
         <f>$C$7/G2</f>
@@ -6967,11 +6967,11 @@
       </c>
       <c r="Z2" s="7">
         <f>$Y$4*LN(V2) + $Y$7</f>
-        <v>368.55424663873168</v>
+        <v>368.55424664001009</v>
       </c>
       <c r="AA2" s="7">
         <f>(Z2 - W2)^2</f>
-        <v>89.222256561911692</v>
+        <v>89.222256537760629</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -7015,19 +7015,19 @@
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q62" si="7">-0.5*$A$13*$C$13*I3</f>
-        <v>8.0925703245677454</v>
+        <v>8.0925703247476708</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R62" si="8">-(1 - 0.5*$A$13*$C$13)*M3</f>
-        <v>-0.70897756453445371</v>
+        <v>-0.70897756439470216</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T62" si="9">P3 + Q3 + R3</f>
-        <v>4.1185993379838006</v>
+        <v>4.1185993383034774</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:V62" si="10">EXP(T3)</f>
-        <v>61.473078928984947</v>
+        <v>61.473078948636456</v>
       </c>
       <c r="W3">
         <f t="shared" ref="W3:W62" si="11">$C$7/G3</f>
@@ -7038,11 +7038,11 @@
       </c>
       <c r="Z3" s="7">
         <f t="shared" ref="Z3:Z62" si="12">$Y$4*LN(V3) + $Y$7</f>
-        <v>365.62292186729667</v>
+        <v>365.62292186875146</v>
       </c>
       <c r="AA3" s="7">
         <f t="shared" ref="AA3:AA62" si="13">(Z3 - W3)^2</f>
-        <v>74.55465717218344</v>
+        <v>74.554657147060595</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -7089,19 +7089,19 @@
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>7.6904289332839824</v>
+        <v>7.6904289334549665</v>
       </c>
       <c r="R4">
         <f t="shared" si="8"/>
-        <v>-0.97241474648859638</v>
+        <v>-0.97241474629691682</v>
       </c>
       <c r="T4">
         <f t="shared" si="9"/>
-        <v>3.453020764745895</v>
+        <v>3.4530207651085578</v>
       </c>
       <c r="V4" s="7">
         <f t="shared" si="10"/>
-        <v>31.59569144899044</v>
+        <v>31.595691460449022</v>
       </c>
       <c r="W4">
         <f t="shared" si="11"/>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="Z4" s="7">
         <f t="shared" si="12"/>
-        <v>362.5940068962056</v>
+        <v>362.59400689785605</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" si="13"/>
-        <v>63.907687677983056</v>
+        <v>63.907687651594934</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -7159,19 +7159,19 @@
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>7.2882875420002247</v>
+        <v>7.2882875421622684</v>
       </c>
       <c r="R5">
         <f t="shared" si="8"/>
-        <v>-1.2581694393534764</v>
+        <v>-1.2581694391054694</v>
       </c>
       <c r="T5">
         <f t="shared" si="9"/>
-        <v>2.7651246805972574</v>
+        <v>2.7651246810073071</v>
       </c>
       <c r="V5" s="7">
         <f t="shared" si="10"/>
-        <v>15.88101992223068</v>
+        <v>15.881019928742688</v>
       </c>
       <c r="W5">
         <f t="shared" si="11"/>
@@ -7179,11 +7179,11 @@
       </c>
       <c r="Z5" s="7">
         <f t="shared" si="12"/>
-        <v>359.46352939646198</v>
+        <v>359.46352939832803</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="13"/>
-        <v>56.652144182563774</v>
+        <v>56.652144154473056</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -7227,19 +7227,19 @@
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>6.886146150716467</v>
+        <v>6.8861461508695694</v>
       </c>
       <c r="R6">
         <f t="shared" si="8"/>
-        <v>-1.566781814224534</v>
+        <v>-1.5667818139156944</v>
       </c>
       <c r="T6">
         <f t="shared" si="9"/>
-        <v>2.0543709144424414</v>
+        <v>2.0543709149043838</v>
       </c>
       <c r="V6" s="7">
         <f t="shared" si="10"/>
-        <v>7.8019282481288723</v>
+        <v>7.8019282517329138</v>
       </c>
       <c r="W6">
         <f t="shared" si="11"/>
@@ -7250,11 +7250,11 @@
       </c>
       <c r="Z6" s="7">
         <f t="shared" si="12"/>
-        <v>356.22903115744464</v>
+        <v>356.22903115954688</v>
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="13"/>
-        <v>52.309161903770381</v>
+        <v>52.309161873361447</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -7301,19 +7301,19 @@
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>6.484004759432703</v>
+        <v>6.4840047595768651</v>
       </c>
       <c r="R7">
         <f t="shared" si="8"/>
-        <v>-1.8530335995478797</v>
+        <v>-1.853033599182615</v>
       </c>
       <c r="T7">
         <f t="shared" si="9"/>
-        <v>1.3659777378353319</v>
+        <v>1.3659777383447587</v>
       </c>
       <c r="V7" s="7">
         <f t="shared" si="10"/>
-        <v>3.9195534748428615</v>
+        <v>3.919553476839587</v>
       </c>
       <c r="W7">
         <f t="shared" si="11"/>
@@ -7324,11 +7324,11 @@
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="12"/>
-        <v>353.09629148934101</v>
+        <v>353.09629149165931</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="13"/>
-        <v>47.661191200145332</v>
+        <v>47.661191168135566</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -7371,19 +7371,19 @@
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>6.0818633681489462</v>
+        <v>6.0818633682841661</v>
       </c>
       <c r="R8">
         <f t="shared" si="8"/>
-        <v>-2.0007629844366757</v>
+        <v>-2.0007629840422911</v>
       </c>
       <c r="T8">
         <f t="shared" si="9"/>
-        <v>0.81610696166277918</v>
+        <v>0.81610696219238354</v>
       </c>
       <c r="V8" s="7">
         <f t="shared" si="10"/>
-        <v>2.2616778778757616</v>
+        <v>2.2616778790735559</v>
       </c>
       <c r="W8">
         <f t="shared" si="11"/>
@@ -7391,11 +7391,11 @@
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="12"/>
-        <v>350.59393956113496</v>
+        <v>350.59393956354512</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="13"/>
-        <v>36.118104993271672</v>
+        <v>36.11810496430234</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -7439,19 +7439,19 @@
       </c>
       <c r="Q9">
         <f t="shared" si="7"/>
-        <v>5.6797219768651885</v>
+        <v>5.679721976991468</v>
       </c>
       <c r="R9">
         <f t="shared" si="8"/>
-        <v>-2.1484923693254712</v>
+        <v>-2.1484923689019668</v>
       </c>
       <c r="T9">
         <f t="shared" si="9"/>
-        <v>0.26623618549022599</v>
+        <v>0.26623618604000976</v>
       </c>
       <c r="V9" s="7">
         <f t="shared" si="10"/>
-        <v>1.3050432545706441</v>
+        <v>1.3050432552881357</v>
       </c>
       <c r="W9">
         <f t="shared" si="11"/>
@@ -7462,11 +7462,11 @@
       </c>
       <c r="Z9" s="7">
         <f t="shared" si="12"/>
-        <v>348.09158763292891</v>
+        <v>348.09158763543087</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="13"/>
-        <v>26.826602903292958</v>
+        <v>26.826602877375421</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -7513,19 +7513,19 @@
       </c>
       <c r="Q10">
         <f t="shared" si="7"/>
-        <v>5.2775805855814246</v>
+        <v>5.2775805856987628</v>
       </c>
       <c r="R10">
         <f t="shared" si="8"/>
-        <v>-2.2962217542142689</v>
+        <v>-2.2962217537616443</v>
       </c>
       <c r="T10">
         <f t="shared" si="9"/>
-        <v>-0.28363459068233565</v>
+        <v>-0.28363459011237291</v>
       </c>
       <c r="V10" s="7">
         <f t="shared" si="10"/>
-        <v>0.75304176291451597</v>
+        <v>0.75304176334372175</v>
       </c>
       <c r="W10">
         <f t="shared" si="11"/>
@@ -7533,15 +7533,15 @@
       </c>
       <c r="Y10" s="7">
         <f>AVERAGE(AA13:AA30)</f>
-        <v>0.93107509923767695</v>
+        <v>0.93107509923768916</v>
       </c>
       <c r="Z10" s="7">
         <f t="shared" si="12"/>
-        <v>345.5892357047228</v>
+        <v>345.58923570731662</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="13"/>
-        <v>19.454841668492211</v>
+        <v>19.454841645610735</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -7584,19 +7584,19 @@
       </c>
       <c r="Q11">
         <f t="shared" si="7"/>
-        <v>4.8754391942976669</v>
+        <v>4.8754391944060647</v>
       </c>
       <c r="R11">
         <f t="shared" si="8"/>
-        <v>-2.4439511391030648</v>
+        <v>-2.4439511386213204</v>
       </c>
       <c r="T11">
         <f t="shared" si="9"/>
-        <v>-0.8335053668548893</v>
+        <v>-0.83350536626474714</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" si="10"/>
-        <v>0.43452344947752075</v>
+        <v>0.43452344973395141</v>
       </c>
       <c r="W11">
         <f t="shared" si="11"/>
@@ -7604,11 +7604,11 @@
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="12"/>
-        <v>343.08688377651674</v>
+        <v>343.08688377920237</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="13"/>
-        <v>13.705596603524064</v>
+        <v>13.705596583639128</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -7654,19 +7654,19 @@
       </c>
       <c r="Q12">
         <f t="shared" si="7"/>
-        <v>4.4732978030139092</v>
+        <v>4.4732978031133657</v>
       </c>
       <c r="R12">
         <f t="shared" si="8"/>
-        <v>-2.5916805239918599</v>
+        <v>-2.5916805234809956</v>
       </c>
       <c r="T12">
         <f t="shared" si="9"/>
-        <v>-1.3833761430274421</v>
+        <v>-1.3833761424171214</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="10"/>
-        <v>0.25073062005895308</v>
+        <v>0.25073062021197917</v>
       </c>
       <c r="W12">
         <f t="shared" si="11"/>
@@ -7674,19 +7674,19 @@
       </c>
       <c r="Z12" s="7">
         <f t="shared" si="12"/>
-        <v>340.58453184831069</v>
+        <v>340.58453185108817</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="13"/>
-        <v>9.3136772625703852</v>
+        <v>9.3136772456175621</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="5">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="C13" s="9">
-        <v>0.95599997927911406</v>
+        <v>0.91697957198198665</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -7725,19 +7725,19 @@
       </c>
       <c r="Q13">
         <f t="shared" si="7"/>
-        <v>4.0711564117301453</v>
+        <v>4.0711564118206613</v>
       </c>
       <c r="R13">
         <f t="shared" si="8"/>
-        <v>-2.7394099088806581</v>
+        <v>-2.7394099083406735</v>
       </c>
       <c r="T13">
         <f t="shared" si="9"/>
-        <v>-1.9332469192000041</v>
+        <v>-1.9332469185695036</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="10"/>
-        <v>0.14467767829500935</v>
+        <v>0.14467767838622869</v>
       </c>
       <c r="W13">
         <f t="shared" si="11"/>
@@ -7745,11 +7745,11 @@
       </c>
       <c r="Z13" s="7">
         <f t="shared" si="12"/>
-        <v>338.08217992010464</v>
+        <v>338.08217992297392</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="13"/>
-        <v>6.0435369401098997</v>
+        <v>6.0435369260024236</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -7791,19 +7791,19 @@
       </c>
       <c r="Q14">
         <f t="shared" si="7"/>
-        <v>3.6690150204463881</v>
+        <v>3.6690150205279628</v>
       </c>
       <c r="R14">
         <f t="shared" si="8"/>
-        <v>-2.8871392937694536</v>
+        <v>-2.8871392932003492</v>
       </c>
       <c r="T14">
         <f t="shared" si="9"/>
-        <v>-2.4831176953725569</v>
+        <v>-2.4831176947218778</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="10"/>
-        <v>8.3482546295753024E-2</v>
+        <v>8.3482546350073378E-2</v>
       </c>
       <c r="W14">
         <f t="shared" si="11"/>
@@ -7811,11 +7811,11 @@
       </c>
       <c r="Z14" s="7">
         <f t="shared" si="12"/>
-        <v>335.57982799189858</v>
+        <v>335.57982799485967</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="13"/>
-        <v>3.6870605406960113</v>
+        <v>3.687060529324417</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -7856,19 +7856,19 @@
       </c>
       <c r="Q15">
         <f t="shared" si="7"/>
-        <v>3.2668736291626304</v>
+        <v>3.2668736292352643</v>
       </c>
       <c r="R15">
         <f t="shared" si="8"/>
-        <v>-3.0348686786582491</v>
+        <v>-3.0348686780600245</v>
       </c>
       <c r="T15">
         <f t="shared" si="9"/>
-        <v>-3.0329884715451101</v>
+        <v>-3.0329884708742516</v>
       </c>
       <c r="V15" s="7">
         <f t="shared" si="10"/>
-        <v>4.8171463754149497E-2</v>
+        <v>4.8171463786465737E-2</v>
       </c>
       <c r="W15">
         <f t="shared" si="11"/>
@@ -7876,11 +7876,11 @@
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="12"/>
-        <v>333.07747606369253</v>
+        <v>333.07747606674548</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="13"/>
-        <v>2.0615166795741584</v>
+        <v>2.0615166708073285</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -7921,19 +7921,19 @@
       </c>
       <c r="Q16">
         <f t="shared" si="7"/>
-        <v>2.8647322378788664</v>
+        <v>2.864732237942559</v>
       </c>
       <c r="R16">
         <f t="shared" si="8"/>
-        <v>-3.1825980635470468</v>
+        <v>-3.1825980629197024</v>
       </c>
       <c r="T16">
         <f t="shared" si="9"/>
-        <v>-3.5828592477176717</v>
+        <v>-3.5828592470266347</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="10"/>
-        <v>2.7796108566173056E-2</v>
+        <v>2.7796108585381195E-2</v>
       </c>
       <c r="W16">
         <f t="shared" si="11"/>
@@ -7941,11 +7941,11 @@
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="12"/>
-        <v>330.57512413548642</v>
+        <v>330.57512413863117</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="13"/>
-        <v>1.0076610829793153</v>
+        <v>1.0076610766657723</v>
       </c>
     </row>
     <row r="17" spans="3:27">
@@ -7983,19 +7983,19 @@
       </c>
       <c r="Q17">
         <f t="shared" si="7"/>
-        <v>2.4625908465951092</v>
+        <v>2.4625908466498609</v>
       </c>
       <c r="R17">
         <f t="shared" si="8"/>
-        <v>-3.3303274484358436</v>
+        <v>-3.3303274477793789</v>
       </c>
       <c r="T17">
         <f t="shared" si="9"/>
-        <v>-4.1327300238902254</v>
+        <v>-4.1327300231790094</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="10"/>
-        <v>1.6039032057769499E-2</v>
+        <v>1.6039032069176715E-2</v>
       </c>
       <c r="W17">
         <f t="shared" si="11"/>
@@ -8003,11 +8003,11 @@
       </c>
       <c r="Z17" s="7">
         <f t="shared" si="12"/>
-        <v>328.07277220728037</v>
+        <v>328.07277221051697</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="13"/>
-        <v>0.38797945283227636</v>
+        <v>0.38797944880024055</v>
       </c>
     </row>
     <row r="18" spans="3:27">
@@ -8048,19 +8048,19 @@
       </c>
       <c r="Q18">
         <f t="shared" si="7"/>
-        <v>2.0604494553113515</v>
+        <v>2.0604494553571624</v>
       </c>
       <c r="R18">
         <f t="shared" si="8"/>
-        <v>-3.4780568333246391</v>
+        <v>-3.4780568326390546</v>
       </c>
       <c r="T18">
         <f t="shared" si="9"/>
-        <v>-4.6826008000627795</v>
+        <v>-4.6826007993313841</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="10"/>
-        <v>9.2549123823477582E-3</v>
+        <v>9.2549123891167585E-3</v>
       </c>
       <c r="W18">
         <f t="shared" si="11"/>
@@ -8068,11 +8068,11 @@
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="12"/>
-        <v>325.57042027907431</v>
+        <v>325.57042028240272</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="13"/>
-        <v>8.5058956303867575E-2</v>
+        <v>8.5058954362415035E-2</v>
       </c>
     </row>
     <row r="19" spans="3:27">
@@ -8113,19 +8113,19 @@
       </c>
       <c r="Q19">
         <f t="shared" si="7"/>
-        <v>1.6583080640275876</v>
+        <v>1.6583080640644574</v>
       </c>
       <c r="R19">
         <f t="shared" si="8"/>
-        <v>-3.6257862182134364</v>
+        <v>-3.6257862174987321</v>
       </c>
       <c r="T19">
         <f t="shared" si="9"/>
-        <v>-5.2324715762353406</v>
+        <v>-5.2324715754837658</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="10"/>
-        <v>5.3403099947943369E-3</v>
+        <v>5.3403099988079796E-3</v>
       </c>
       <c r="W19">
         <f t="shared" si="11"/>
@@ -8133,11 +8133,11 @@
       </c>
       <c r="Z19" s="7">
         <f t="shared" si="12"/>
-        <v>323.0680683508682</v>
+        <v>323.06806835428847</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="13"/>
-        <v>7.8406173506178806E-5</v>
+        <v>7.8406112935109067E-5</v>
       </c>
     </row>
     <row r="20" spans="3:27">
@@ -8175,19 +8175,19 @@
       </c>
       <c r="Q20">
         <f t="shared" si="7"/>
-        <v>1.2561666727438301</v>
+        <v>1.2561666727717591</v>
       </c>
       <c r="R20">
         <f t="shared" si="8"/>
-        <v>-3.7735156031022328</v>
+        <v>-3.7735156023584082</v>
       </c>
       <c r="T20">
         <f t="shared" si="9"/>
-        <v>-5.7823423524078938</v>
+        <v>-5.7823423516361405</v>
       </c>
       <c r="V20" s="7">
         <f t="shared" si="10"/>
-        <v>3.0814890149468851E-3</v>
+        <v>3.0814890173250344E-3</v>
       </c>
       <c r="W20">
         <f t="shared" si="11"/>
@@ -8195,11 +8195,11 @@
       </c>
       <c r="Z20" s="7">
         <f t="shared" si="12"/>
-        <v>320.56571642266215</v>
+        <v>320.56571642617428</v>
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="13"/>
-        <v>5.1408021894490077E-2</v>
+        <v>5.1408023487123103E-2</v>
       </c>
     </row>
     <row r="21" spans="3:27">
@@ -8240,19 +8240,19 @@
       </c>
       <c r="Q21">
         <f t="shared" si="7"/>
-        <v>0.85402528146007262</v>
+        <v>0.85402528147906054</v>
       </c>
       <c r="R21">
         <f t="shared" si="8"/>
-        <v>-3.9212449879910283</v>
+        <v>-3.9212449872180835</v>
       </c>
       <c r="T21">
         <f t="shared" si="9"/>
-        <v>-6.332213128580447</v>
+        <v>-6.3322131277885143</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="10"/>
-        <v>1.7780942601636389E-3</v>
+        <v>1.7780942615717701E-3</v>
       </c>
       <c r="W21">
         <f t="shared" si="11"/>
@@ -8260,11 +8260,11 @@
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="12"/>
-        <v>318.0633644944561</v>
+        <v>318.06336449806003</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="13"/>
-        <v>0.17331041164573308</v>
+        <v>0.17331041464640576</v>
       </c>
     </row>
     <row r="22" spans="3:27">
@@ -8305,19 +8305,19 @@
       </c>
       <c r="Q22">
         <f t="shared" si="7"/>
-        <v>0.45188389017630876</v>
+        <v>0.45188389018635566</v>
       </c>
       <c r="R22">
         <f t="shared" si="8"/>
-        <v>-4.0689743728798247</v>
+        <v>-4.0689743720777605</v>
       </c>
       <c r="T22">
         <f t="shared" si="9"/>
-        <v>-6.8820839047530074</v>
+        <v>-6.8820839039408961</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="10"/>
-        <v>1.0260037218017967E-3</v>
+        <v>1.0260037226350258E-3</v>
       </c>
       <c r="W22">
         <f t="shared" si="11"/>
@@ -8325,11 +8325,11 @@
       </c>
       <c r="Z22" s="7">
         <f t="shared" si="12"/>
-        <v>315.56101256624999</v>
+        <v>315.56101256994577</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="13"/>
-        <v>0.31473509949045803</v>
+        <v>0.31473510363722573</v>
       </c>
     </row>
     <row r="23" spans="3:27">
@@ -8367,19 +8367,19 @@
       </c>
       <c r="Q23">
         <f t="shared" si="7"/>
-        <v>4.974249889255123E-2</v>
+        <v>4.9742498893657179E-2</v>
       </c>
       <c r="R23">
         <f t="shared" si="8"/>
-        <v>-4.2167037577686211</v>
+        <v>-4.216703756937437</v>
       </c>
       <c r="T23">
         <f t="shared" si="9"/>
-        <v>-7.4319546809255606</v>
+        <v>-7.4319546800932716</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="10"/>
-        <v>5.9202915207333666E-4</v>
+        <v>5.9202915256607587E-4</v>
       </c>
       <c r="W23">
         <f t="shared" si="11"/>
@@ -8387,11 +8387,11 @@
       </c>
       <c r="Z23" s="7">
         <f t="shared" si="12"/>
-        <v>313.05866063804393</v>
+        <v>313.05866064183152</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="13"/>
-        <v>0.43819954540175543</v>
+        <v>0.43819955041627118</v>
       </c>
     </row>
     <row r="24" spans="3:27">
@@ -8429,19 +8429,19 @@
       </c>
       <c r="Q24">
         <f t="shared" si="7"/>
-        <v>-0.35239889239120625</v>
+        <v>-0.35239889239904132</v>
       </c>
       <c r="R24">
         <f t="shared" si="8"/>
-        <v>-4.3644331426574174</v>
+        <v>-4.3644331417971127</v>
       </c>
       <c r="T24">
         <f t="shared" si="9"/>
-        <v>-7.9818254570981146</v>
+        <v>-7.9818254562456454</v>
       </c>
       <c r="V24" s="7">
         <f t="shared" si="10"/>
-        <v>3.4161524900626328E-4</v>
+        <v>3.4161524929747977E-4</v>
       </c>
       <c r="W24">
         <f t="shared" si="11"/>
@@ -8449,11 +8449,11 @@
       </c>
       <c r="Z24" s="7">
         <f t="shared" si="12"/>
-        <v>310.55630870983788</v>
+        <v>310.55630871371733</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="13"/>
-        <v>0.51875017505225829</v>
+        <v>0.51875018064055223</v>
       </c>
     </row>
     <row r="25" spans="3:27">
@@ -8491,19 +8491,19 @@
       </c>
       <c r="Q25">
         <f t="shared" si="7"/>
-        <v>-0.75454028367497017</v>
+        <v>-0.75454028369174619</v>
       </c>
       <c r="R25">
         <f t="shared" si="8"/>
-        <v>-4.5121625275462147</v>
+        <v>-4.5121625266567902</v>
       </c>
       <c r="T25">
         <f t="shared" si="9"/>
-        <v>-8.5316962332706758</v>
+        <v>-8.5316962323980281</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="10"/>
-        <v>1.9712032413423165E-4</v>
+        <v>1.9712032430624823E-4</v>
       </c>
       <c r="W25">
         <f t="shared" si="11"/>
@@ -8511,11 +8511,11 @@
       </c>
       <c r="Z25" s="7">
         <f t="shared" si="12"/>
-        <v>308.05395678163183</v>
+        <v>308.05395678560308</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="13"/>
-        <v>0.54299745601328653</v>
+        <v>0.54299746186598719</v>
       </c>
     </row>
     <row r="26" spans="3:27">
@@ -8553,19 +8553,19 @@
       </c>
       <c r="Q26">
         <f t="shared" si="7"/>
-        <v>-1.1566816749587276</v>
+        <v>-1.1566816749844446</v>
       </c>
       <c r="R26">
         <f t="shared" si="8"/>
-        <v>-4.6598919124350111</v>
+        <v>-4.6598919115164668</v>
       </c>
       <c r="T26">
         <f t="shared" si="9"/>
-        <v>-9.0815670094432299</v>
+        <v>-9.0815670085504028</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="10"/>
-        <v>1.1374323101739647E-4</v>
+        <v>1.1374323111894951E-4</v>
       </c>
       <c r="W26">
         <f t="shared" si="11"/>
@@ -8573,11 +8573,11 @@
       </c>
       <c r="Z26" s="7">
         <f t="shared" si="12"/>
-        <v>305.55160485342572</v>
+        <v>305.55160485748883</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="13"/>
-        <v>0.50821953197325453</v>
+        <v>0.50821953776639861</v>
       </c>
     </row>
     <row r="27" spans="3:27">
@@ -8615,19 +8615,19 @@
       </c>
       <c r="Q27">
         <f t="shared" si="7"/>
-        <v>-1.5588230662424851</v>
+        <v>-1.5588230662771432</v>
       </c>
       <c r="R27">
         <f t="shared" si="8"/>
-        <v>-4.8076212973238075</v>
+        <v>-4.8076212963761424</v>
       </c>
       <c r="T27">
         <f t="shared" si="9"/>
-        <v>-9.631437785615784</v>
+        <v>-9.6314377847027774</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="10"/>
-        <v>6.5632616317467328E-5</v>
+        <v>6.5632616377390342E-5</v>
       </c>
       <c r="W27">
         <f t="shared" si="11"/>
@@ -8635,11 +8635,11 @@
       </c>
       <c r="Z27" s="7">
         <f t="shared" si="12"/>
-        <v>303.04925292521966</v>
+        <v>303.04925292937457</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="13"/>
-        <v>0.42152936090639115</v>
+        <v>0.42152936630156984</v>
       </c>
     </row>
     <row r="28" spans="3:27">
@@ -8677,19 +8677,19 @@
       </c>
       <c r="Q28">
         <f t="shared" si="7"/>
-        <v>-1.960964457526249</v>
+        <v>-1.9609644575698479</v>
       </c>
       <c r="R28">
         <f t="shared" si="8"/>
-        <v>-4.9553506822126039</v>
+        <v>-4.9553506812358199</v>
       </c>
       <c r="T28">
         <f t="shared" si="9"/>
-        <v>-10.181308561788345</v>
+        <v>-10.181308560855159</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="10"/>
-        <v>3.7871619138522769E-5</v>
+        <v>3.7871619173864033E-5</v>
       </c>
       <c r="W28">
         <f t="shared" si="11"/>
@@ -8697,11 +8697,11 @@
       </c>
       <c r="Z28" s="7">
         <f t="shared" si="12"/>
-        <v>300.54690099701361</v>
+        <v>300.54690100126032</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="13"/>
-        <v>0.29910070053454119</v>
+        <v>0.29910070517960652</v>
       </c>
     </row>
     <row r="29" spans="3:27">
@@ -8739,19 +8739,19 @@
       </c>
       <c r="Q29">
         <f t="shared" si="7"/>
-        <v>-2.3631058488100067</v>
+        <v>-2.3631058488625465</v>
       </c>
       <c r="R29">
         <f t="shared" si="8"/>
-        <v>-5.1030800671014012</v>
+        <v>-5.1030800660954965</v>
       </c>
       <c r="T29">
         <f t="shared" si="9"/>
-        <v>-10.731179337960899</v>
+        <v>-10.731179337007536</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="10"/>
-        <v>2.1852847206879107E-5</v>
+        <v>2.1852847227712818E-5</v>
       </c>
       <c r="W29">
         <f t="shared" si="11"/>
@@ -8759,11 +8759,11 @@
       </c>
       <c r="Z29" s="7">
         <f t="shared" si="12"/>
-        <v>298.04454906880756</v>
+        <v>298.04454907314613</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="13"/>
-        <v>0.16544864829644673</v>
+        <v>0.16544865182590957</v>
       </c>
     </row>
     <row r="30" spans="3:27">
@@ -8801,19 +8801,19 @@
       </c>
       <c r="Q30">
         <f t="shared" si="7"/>
-        <v>-2.765247240093764</v>
+        <v>-2.765247240155245</v>
       </c>
       <c r="R30">
         <f t="shared" si="8"/>
-        <v>-5.2508094519901958</v>
+        <v>-5.2508094509551713</v>
       </c>
       <c r="T30">
         <f t="shared" si="9"/>
-        <v>-11.28105011413345</v>
+        <v>-11.281050113159907</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="10"/>
-        <v>1.2609625411062715E-5</v>
+        <v>1.2609625423338728E-5</v>
       </c>
       <c r="W30">
         <f t="shared" si="11"/>
@@ -8821,11 +8821,11 @@
       </c>
       <c r="Z30" s="7">
         <f t="shared" si="12"/>
-        <v>295.5421971406015</v>
+        <v>295.54219714503188</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="13"/>
-        <v>5.2760776400532207E-2</v>
+        <v>5.2760778435821658E-2</v>
       </c>
     </row>
     <row r="31" spans="3:27">
@@ -8863,19 +8863,19 @@
       </c>
       <c r="Q31">
         <f t="shared" si="7"/>
-        <v>-3.1673886313775279</v>
+        <v>-3.1673886314479498</v>
       </c>
       <c r="R31">
         <f t="shared" si="8"/>
-        <v>-5.3985388368789931</v>
+        <v>-5.3985388358148487</v>
       </c>
       <c r="T31">
         <f t="shared" si="9"/>
-        <v>-11.830920890306013</v>
+        <v>-11.83092088931229</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="10"/>
-        <v>7.276061169606483E-6</v>
+        <v>7.276061176836868E-6</v>
       </c>
       <c r="W31">
         <f t="shared" si="11"/>
@@ -8883,11 +8883,11 @@
       </c>
       <c r="Z31" s="7">
         <f t="shared" si="12"/>
-        <v>293.03984521239539</v>
+        <v>293.03984521691763</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="13"/>
-        <v>2.7520814066628356E-4</v>
+        <v>2.752082907086216E-4</v>
       </c>
     </row>
     <row r="32" spans="3:27">
@@ -8925,19 +8925,19 @@
       </c>
       <c r="Q32">
         <f t="shared" si="7"/>
-        <v>-3.5695300226612856</v>
+        <v>-3.5695300227406483</v>
       </c>
       <c r="R32">
         <f t="shared" si="8"/>
-        <v>-5.5462682217677894</v>
+        <v>-5.5462682206745244</v>
       </c>
       <c r="T32">
         <f t="shared" si="9"/>
-        <v>-12.380791666478567</v>
+        <v>-12.380791665464663</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="10"/>
-        <v>4.1984646187355667E-6</v>
+        <v>4.1984646229924045E-6</v>
       </c>
       <c r="W32">
         <f t="shared" si="11"/>
@@ -8945,11 +8945,11 @@
       </c>
       <c r="Z32" s="7">
         <f t="shared" si="12"/>
-        <v>290.53749328418934</v>
+        <v>290.53749328880343</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="13"/>
-        <v>5.3702261973303113E-2</v>
+        <v>5.3702259834786055E-2</v>
       </c>
     </row>
     <row r="33" spans="7:27">
@@ -8987,19 +8987,19 @@
       </c>
       <c r="Q33">
         <f t="shared" si="7"/>
-        <v>-3.9716714139450429</v>
+        <v>-3.9716714140333469</v>
       </c>
       <c r="R33">
         <f t="shared" si="8"/>
-        <v>-5.6939976066565849</v>
+        <v>-5.6939976055342001</v>
       </c>
       <c r="T33">
         <f t="shared" si="9"/>
-        <v>-12.930662442651119</v>
+        <v>-12.930662441617038</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="10"/>
-        <v>2.4226164052064664E-6</v>
+        <v>2.4226164077116489E-6</v>
       </c>
       <c r="W33">
         <f t="shared" si="11"/>
@@ -9007,11 +9007,11 @@
       </c>
       <c r="Z33" s="7">
         <f t="shared" si="12"/>
-        <v>288.03514135598328</v>
+        <v>288.03514136068918</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="13"/>
-        <v>0.26468654713218498</v>
+        <v>0.26468654229003469</v>
       </c>
     </row>
     <row r="34" spans="7:27">
@@ -9049,19 +9049,19 @@
       </c>
       <c r="Q34">
         <f t="shared" si="7"/>
-        <v>-4.3738128052288072</v>
+        <v>-4.3738128053260512</v>
       </c>
       <c r="R34">
         <f t="shared" si="8"/>
-        <v>-5.8417269915453813</v>
+        <v>-5.8417269903938775</v>
       </c>
       <c r="T34">
         <f t="shared" si="9"/>
-        <v>-13.48053321882368</v>
+        <v>-13.48053321776942</v>
       </c>
       <c r="V34" s="7">
         <f t="shared" si="10"/>
-        <v>1.3979087070508678E-6</v>
+        <v>1.3979087085246279E-6</v>
       </c>
       <c r="W34">
         <f t="shared" si="11"/>
@@ -9069,11 +9069,11 @@
       </c>
       <c r="Z34" s="7">
         <f t="shared" si="12"/>
-        <v>285.53278942777717</v>
+        <v>285.53278943257493</v>
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="13"/>
-        <v>0.69030663082652588</v>
+        <v>0.6903066228541257</v>
       </c>
     </row>
     <row r="35" spans="7:27">
@@ -9111,19 +9111,19 @@
       </c>
       <c r="Q35">
         <f t="shared" si="7"/>
-        <v>-4.775954196512564</v>
+        <v>-4.7759541966187502</v>
       </c>
       <c r="R35">
         <f t="shared" si="8"/>
-        <v>-5.9894563764341786</v>
+        <v>-5.9894563752535541</v>
       </c>
       <c r="T35">
         <f t="shared" si="9"/>
-        <v>-14.030403994996234</v>
+        <v>-14.030403993921794</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="10"/>
-        <v>8.0662739220660942E-7</v>
+        <v>8.0662739307328231E-7</v>
       </c>
       <c r="W35">
         <f t="shared" si="11"/>
@@ -9131,11 +9131,11 @@
       </c>
       <c r="Z35" s="7">
         <f t="shared" si="12"/>
-        <v>283.03043749957112</v>
+        <v>283.03043750446068</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="13"/>
-        <v>1.392609614163512</v>
+        <v>1.3926096026232884</v>
       </c>
     </row>
     <row r="36" spans="7:27">
@@ -9173,19 +9173,19 @@
       </c>
       <c r="Q36">
         <f t="shared" si="7"/>
-        <v>-5.1780955877963217</v>
+        <v>-5.1780955879114483</v>
       </c>
       <c r="R36">
         <f t="shared" si="8"/>
-        <v>-6.1371857613229741</v>
+        <v>-6.1371857601132298</v>
       </c>
       <c r="T36">
         <f t="shared" si="9"/>
-        <v>-14.580274771168789</v>
+        <v>-14.580274770074169</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="10"/>
-        <v>4.6544366350696125E-7</v>
+        <v>4.6544366401644495E-7</v>
       </c>
       <c r="W36">
         <f t="shared" si="11"/>
@@ -9193,11 +9193,11 @@
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="12"/>
-        <v>280.52808557136507</v>
+        <v>280.52808557634648</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="13"/>
-        <v>2.438178153528713</v>
+        <v>2.4381781379720828</v>
       </c>
     </row>
     <row r="37" spans="7:27">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="Q37">
         <f t="shared" si="7"/>
-        <v>-5.5802369790800856</v>
+        <v>-5.5802369792041535</v>
       </c>
       <c r="R37">
         <f t="shared" si="8"/>
-        <v>-6.2849151462117714</v>
+        <v>-6.2849151449729073</v>
       </c>
       <c r="T37">
         <f t="shared" si="9"/>
-        <v>-15.130145547341348</v>
+        <v>-15.130145546226551</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="10"/>
-        <v>2.6857233710616492E-7</v>
+        <v>2.6857233740556857E-7</v>
       </c>
       <c r="W37">
         <f t="shared" si="11"/>
@@ -9255,11 +9255,11 @@
       </c>
       <c r="Z37" s="7">
         <f t="shared" si="12"/>
-        <v>278.02573364315901</v>
+        <v>278.02573364823223</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="13"/>
-        <v>3.897727647753952</v>
+        <v>3.8977276277221837</v>
       </c>
     </row>
     <row r="38" spans="7:27">
@@ -9297,19 +9297,19 @@
       </c>
       <c r="Q38">
         <f t="shared" si="7"/>
-        <v>-5.9823783703638433</v>
+        <v>-5.9823783704968516</v>
       </c>
       <c r="R38">
         <f t="shared" si="8"/>
-        <v>-6.4326445311005678</v>
+        <v>-6.4326445298325829</v>
       </c>
       <c r="T38">
         <f t="shared" si="9"/>
-        <v>-15.680016323513902</v>
+        <v>-15.680016322378926</v>
       </c>
       <c r="V38" s="7">
         <f t="shared" si="10"/>
-        <v>1.5497278384925112E-7</v>
+        <v>1.5497278402514158E-7</v>
       </c>
       <c r="W38">
         <f t="shared" si="11"/>
@@ -9317,11 +9317,11 @@
       </c>
       <c r="Z38" s="7">
         <f t="shared" si="12"/>
-        <v>275.52338171495296</v>
+        <v>275.52338172011798</v>
       </c>
       <c r="AA38" s="7">
         <f t="shared" si="13"/>
-        <v>5.8457314803771432</v>
+        <v>5.8457314554012241</v>
       </c>
     </row>
     <row r="39" spans="7:27">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="Q39">
         <f t="shared" si="7"/>
-        <v>-6.384519761647601</v>
+        <v>-6.3845197617895506</v>
       </c>
       <c r="R39">
         <f t="shared" si="8"/>
-        <v>-6.5803739159893633</v>
+        <v>-6.5803739146922595</v>
       </c>
       <c r="T39">
         <f t="shared" si="9"/>
-        <v>-16.229887099686454</v>
+        <v>-16.2298870985313</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="10"/>
-        <v>8.9423073101133106E-8</v>
+        <v>8.9423073204430534E-8</v>
       </c>
       <c r="W39">
         <f t="shared" si="11"/>
@@ -9379,11 +9379,11 @@
       </c>
       <c r="Z39" s="7">
         <f t="shared" si="12"/>
-        <v>273.02102978674691</v>
+        <v>273.02102979200379</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="13"/>
-        <v>8.3600723619046864</v>
+        <v>8.3600723315054264</v>
       </c>
     </row>
     <row r="40" spans="7:27">
@@ -9421,19 +9421,19 @@
       </c>
       <c r="Q40">
         <f t="shared" si="7"/>
-        <v>-6.786661152931365</v>
+        <v>-6.7866611530822549</v>
       </c>
       <c r="R40">
         <f t="shared" si="8"/>
-        <v>-6.7281033008781606</v>
+        <v>-6.7281032995519361</v>
       </c>
       <c r="T40">
         <f t="shared" si="9"/>
-        <v>-16.779757875859019</v>
+        <v>-16.779757874683682</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="10"/>
-        <v>5.1599292496603993E-8</v>
+        <v>5.159929255725056E-8</v>
       </c>
       <c r="W40">
         <f t="shared" si="11"/>
@@ -9441,11 +9441,11 @@
       </c>
       <c r="Z40" s="7">
         <f t="shared" si="12"/>
-        <v>270.51867785854074</v>
+        <v>270.51867786388948</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="13"/>
-        <v>11.521717960337661</v>
+        <v>11.521717924026513</v>
       </c>
     </row>
     <row r="41" spans="7:27">
@@ -9483,19 +9483,19 @@
       </c>
       <c r="Q41">
         <f t="shared" si="7"/>
-        <v>-7.1888025442151227</v>
+        <v>-7.1888025443749539</v>
       </c>
       <c r="R41">
         <f t="shared" si="8"/>
-        <v>-6.8758326857669569</v>
+        <v>-6.8758326844116127</v>
       </c>
       <c r="T41">
         <f t="shared" si="9"/>
-        <v>-17.329628652031573</v>
+        <v>-17.329628650836057</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="10"/>
-        <v>2.9774049289706018E-8</v>
+        <v>2.9774049325301387E-8</v>
       </c>
       <c r="W41">
         <f t="shared" si="11"/>
@@ -9503,11 +9503,11 @@
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="12"/>
-        <v>268.01632593033469</v>
+        <v>268.01632593577528</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="13"/>
-        <v>15.414419140373655</v>
+        <v>15.414419097652777</v>
       </c>
     </row>
     <row r="42" spans="7:27">
@@ -9545,19 +9545,19 @@
       </c>
       <c r="Q42">
         <f t="shared" si="7"/>
-        <v>-7.5909439354988795</v>
+        <v>-7.590943935667652</v>
       </c>
       <c r="R42">
         <f t="shared" si="8"/>
-        <v>-7.0235620706557542</v>
+        <v>-7.0235620692712901</v>
       </c>
       <c r="T42">
         <f t="shared" si="9"/>
-        <v>-17.879499428204124</v>
+        <v>-17.879499426988435</v>
       </c>
       <c r="V42" s="7">
         <f t="shared" si="10"/>
-        <v>1.7180352059365762E-8</v>
+        <v>1.7180352080251725E-8</v>
       </c>
       <c r="W42">
         <f t="shared" si="11"/>
@@ -9565,11 +9565,11 @@
       </c>
       <c r="Z42" s="7">
         <f t="shared" si="12"/>
-        <v>265.51397400212869</v>
+        <v>265.51397400766103</v>
       </c>
       <c r="AA42" s="7">
         <f t="shared" si="13"/>
-        <v>20.124429253576761</v>
+        <v>20.124429203940299</v>
       </c>
     </row>
     <row r="43" spans="7:27">
@@ -9607,19 +9607,19 @@
       </c>
       <c r="Q43">
         <f t="shared" si="7"/>
-        <v>-7.9930853267826434</v>
+        <v>-7.9930853269603572</v>
       </c>
       <c r="R43">
         <f t="shared" si="8"/>
-        <v>-7.1712914555445515</v>
+        <v>-7.1712914541309667</v>
       </c>
       <c r="T43">
         <f t="shared" si="9"/>
-        <v>-18.429370204376688</v>
+        <v>-18.429370203140817</v>
       </c>
       <c r="V43" s="7">
         <f t="shared" si="10"/>
-        <v>9.9134818382193762E-9</v>
+        <v>9.9134818504711701E-9</v>
       </c>
       <c r="W43">
         <f t="shared" si="11"/>
@@ -9627,11 +9627,11 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="12"/>
-        <v>263.01162207392258</v>
+        <v>263.01162207954678</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="13"/>
-        <v>25.740243034238294</v>
+        <v>25.740242977169697</v>
       </c>
     </row>
     <row r="44" spans="7:27">
@@ -9669,19 +9669,19 @@
       </c>
       <c r="Q44">
         <f t="shared" si="7"/>
-        <v>-8.395226718066402</v>
+        <v>-8.3952267182530562</v>
       </c>
       <c r="R44">
         <f t="shared" si="8"/>
-        <v>-7.3190208404333452</v>
+        <v>-7.3190208389906406</v>
       </c>
       <c r="T44">
         <f t="shared" si="9"/>
-        <v>-18.979240980549239</v>
+        <v>-18.979240979293188</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="10"/>
-        <v>5.7203206207367369E-9</v>
+        <v>5.7203206279217526E-9</v>
       </c>
       <c r="W44">
         <f t="shared" si="11"/>
@@ -9689,11 +9689,11 @@
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="12"/>
-        <v>260.50927014571653</v>
+        <v>260.50927015143259</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="13"/>
-        <v>32.352353759482831</v>
+        <v>32.352353694457918</v>
       </c>
     </row>
     <row r="45" spans="7:27">
@@ -9731,19 +9731,19 @@
       </c>
       <c r="Q45">
         <f t="shared" si="7"/>
-        <v>-8.7973681093501579</v>
+        <v>-8.7973681095457543</v>
       </c>
       <c r="R45">
         <f t="shared" si="8"/>
-        <v>-7.4667502253221416</v>
+        <v>-7.4667502238503172</v>
       </c>
       <c r="T45">
         <f t="shared" si="9"/>
-        <v>-19.52911175672179</v>
+        <v>-19.529111755445562</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="10"/>
-        <v>3.3007644073016575E-9</v>
+        <v>3.3007644115141823E-9</v>
       </c>
       <c r="W45">
         <f t="shared" si="11"/>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="Z45" s="7">
         <f t="shared" si="12"/>
-        <v>258.00691821751047</v>
+        <v>258.00691822331834</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="13"/>
-        <v>40.05302742804664</v>
+        <v>40.053027354533661</v>
       </c>
     </row>
     <row r="46" spans="7:27">
@@ -9793,19 +9793,19 @@
       </c>
       <c r="Q46">
         <f t="shared" si="7"/>
-        <v>-9.1995095006339156</v>
+        <v>-9.1995095008384524</v>
       </c>
       <c r="R46">
         <f t="shared" si="8"/>
-        <v>-7.6144796102109371</v>
+        <v>-7.6144796087099929</v>
       </c>
       <c r="T46">
         <f t="shared" si="9"/>
-        <v>-20.078982532894344</v>
+        <v>-20.078982531597937</v>
       </c>
       <c r="V46" s="7">
         <f t="shared" si="10"/>
-        <v>1.9046215054823654E-9</v>
+        <v>1.9046215079515293E-9</v>
       </c>
       <c r="W46">
         <f t="shared" si="11"/>
@@ -9813,11 +9813,11 @@
       </c>
       <c r="Z46" s="7">
         <f t="shared" si="12"/>
-        <v>255.50456628930442</v>
+        <v>255.50456629520411</v>
       </c>
       <c r="AA46" s="7">
         <f t="shared" si="13"/>
-        <v>48.936092800735324</v>
+        <v>48.9360927181935</v>
       </c>
     </row>
     <row r="47" spans="7:27">
@@ -9855,19 +9855,19 @@
       </c>
       <c r="Q47">
         <f t="shared" si="7"/>
-        <v>-9.6016508919176804</v>
+        <v>-9.6016508921311576</v>
       </c>
       <c r="R47">
         <f t="shared" si="8"/>
-        <v>-7.7622089950997344</v>
+        <v>-7.7622089935696703</v>
       </c>
       <c r="T47">
         <f t="shared" si="9"/>
-        <v>-20.628853309066905</v>
+        <v>-20.628853307750319</v>
       </c>
       <c r="V47" s="7">
         <f t="shared" si="10"/>
-        <v>1.0990130259285607E-9</v>
+        <v>1.0990130273755058E-9</v>
       </c>
       <c r="W47">
         <f t="shared" si="11"/>
@@ -9875,11 +9875,11 @@
       </c>
       <c r="Z47" s="7">
         <f t="shared" si="12"/>
-        <v>253.00221436109831</v>
+        <v>253.00221436708983</v>
       </c>
       <c r="AA47" s="7">
         <f t="shared" si="13"/>
-        <v>59.096746227477759</v>
+        <v>59.096746135358792</v>
       </c>
     </row>
     <row r="48" spans="7:27">
@@ -9917,19 +9917,19 @@
       </c>
       <c r="Q48">
         <f t="shared" si="7"/>
-        <v>-10.003792283201443</v>
+        <v>-10.003792283423863</v>
       </c>
       <c r="R48">
         <f t="shared" si="8"/>
-        <v>-7.9099383799885326</v>
+        <v>-7.9099383784293478</v>
       </c>
       <c r="T48">
         <f t="shared" si="9"/>
-        <v>-21.178724085239466</v>
+        <v>-21.178724083902701</v>
       </c>
       <c r="V48" s="7">
         <f t="shared" si="10"/>
-        <v>6.3415729985404923E-10</v>
+        <v>6.3415730070176874E-10</v>
       </c>
       <c r="W48">
         <f t="shared" si="11"/>
@@ -9937,11 +9937,11 @@
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="12"/>
-        <v>250.49986243289226</v>
+        <v>250.49986243897558</v>
       </c>
       <c r="AA48" s="7">
         <f t="shared" si="13"/>
-        <v>70.631370261634459</v>
+        <v>70.631370159382911</v>
       </c>
     </row>
     <row r="49" spans="7:27">
@@ -9979,19 +9979,19 @@
       </c>
       <c r="Q49">
         <f t="shared" si="7"/>
-        <v>-10.405933674485196</v>
+        <v>-10.405933674716554</v>
       </c>
       <c r="R49">
         <f t="shared" si="8"/>
-        <v>-8.0576677648773281</v>
+        <v>-8.0576677632890235</v>
       </c>
       <c r="T49">
         <f t="shared" si="9"/>
-        <v>-21.728594861412013</v>
+        <v>-21.728594860055068</v>
       </c>
       <c r="V49" s="7">
         <f t="shared" si="10"/>
-        <v>3.6592421697495479E-10</v>
+        <v>3.6592421747149374E-10</v>
       </c>
       <c r="W49">
         <f t="shared" si="11"/>
@@ -9999,11 +9999,11 @@
       </c>
       <c r="Z49" s="7">
         <f t="shared" si="12"/>
-        <v>247.9975105046862</v>
+        <v>247.99751051086139</v>
       </c>
       <c r="AA49" s="7">
         <f t="shared" si="13"/>
-        <v>83.637365132302861</v>
+        <v>83.637365019354448</v>
       </c>
     </row>
     <row r="50" spans="7:27">
@@ -10041,19 +10041,19 @@
       </c>
       <c r="Q50">
         <f t="shared" si="7"/>
-        <v>-10.808075065768959</v>
+        <v>-10.808075066009259</v>
       </c>
       <c r="R50">
         <f t="shared" si="8"/>
-        <v>-8.2053971497661227</v>
+        <v>-8.2053971481486982</v>
       </c>
       <c r="T50">
         <f t="shared" si="9"/>
-        <v>-22.278465637584574</v>
+        <v>-22.27846563620745</v>
       </c>
       <c r="V50" s="7">
         <f t="shared" si="10"/>
-        <v>2.1114719108263672E-10</v>
+        <v>2.1114719137341262E-10</v>
       </c>
       <c r="W50">
         <f t="shared" si="11"/>
@@ -10061,11 +10061,11 @@
       </c>
       <c r="Z50" s="7">
         <f t="shared" si="12"/>
-        <v>245.49515857648012</v>
+        <v>245.49515858274714</v>
       </c>
       <c r="AA50" s="7">
         <f t="shared" si="13"/>
-        <v>98.212992210222183</v>
+        <v>98.212992086006849</v>
       </c>
     </row>
     <row r="51" spans="7:27">
@@ -10103,19 +10103,19 @@
       </c>
       <c r="Q51">
         <f t="shared" si="7"/>
-        <v>-11.210216457052724</v>
+        <v>-11.210216457301964</v>
       </c>
       <c r="R51">
         <f t="shared" si="8"/>
-        <v>-8.3531265346549208</v>
+        <v>-8.3531265330083766</v>
       </c>
       <c r="T51">
         <f t="shared" si="9"/>
-        <v>-22.828336413757135</v>
+        <v>-22.828336412359832</v>
       </c>
       <c r="V51" s="7">
         <f t="shared" si="10"/>
-        <v>1.2183707509344467E-10</v>
+        <v>1.2183707526368805E-10</v>
       </c>
       <c r="W51">
         <f t="shared" si="11"/>
@@ -10123,11 +10123,11 @@
       </c>
       <c r="Z51" s="7">
         <f t="shared" si="12"/>
-        <v>242.99280664827404</v>
+        <v>242.99280665463289</v>
       </c>
       <c r="AA51" s="7">
         <f t="shared" si="13"/>
-        <v>114.45722866297054</v>
+        <v>114.45722852691071</v>
       </c>
     </row>
     <row r="52" spans="7:27">
@@ -10165,19 +10165,19 @@
       </c>
       <c r="Q52">
         <f t="shared" si="7"/>
-        <v>-11.612357848336474</v>
+        <v>-11.612357848594655</v>
       </c>
       <c r="R52">
         <f t="shared" si="8"/>
-        <v>-8.5008559195437137</v>
+        <v>-8.5008559178680496</v>
       </c>
       <c r="T52">
         <f t="shared" si="9"/>
-        <v>-23.378207189929679</v>
+        <v>-23.378207188512196</v>
       </c>
       <c r="V52" s="7">
         <f t="shared" si="10"/>
-        <v>7.0302961603293752E-11</v>
+        <v>7.0302961702947005E-11</v>
       </c>
       <c r="W52">
         <f t="shared" si="11"/>
@@ -10185,11 +10185,11 @@
       </c>
       <c r="Z52" s="7">
         <f t="shared" si="12"/>
-        <v>240.49045472006802</v>
+        <v>240.49045472651869</v>
       </c>
       <c r="AA52" s="7">
         <f t="shared" si="13"/>
-        <v>132.46963255080266</v>
+        <v>132.46963240231395</v>
       </c>
     </row>
     <row r="53" spans="7:27">
@@ -10227,19 +10227,19 @@
       </c>
       <c r="Q53">
         <f t="shared" si="7"/>
-        <v>-12.014499239620237</v>
+        <v>-12.01449923988736</v>
       </c>
       <c r="R53">
         <f t="shared" si="8"/>
-        <v>-8.6485853044325136</v>
+        <v>-8.6485853027277297</v>
       </c>
       <c r="T53">
         <f t="shared" si="9"/>
-        <v>-23.928077966102244</v>
+        <v>-23.928077964664581</v>
       </c>
       <c r="V53" s="7">
         <f t="shared" si="10"/>
-        <v>4.0566522188778452E-11</v>
+        <v>4.0566522247099423E-11</v>
       </c>
       <c r="W53">
         <f t="shared" si="11"/>
@@ -10247,11 +10247,11 @@
       </c>
       <c r="Z53" s="7">
         <f t="shared" si="12"/>
-        <v>237.98810279186191</v>
+        <v>237.98810279840444</v>
       </c>
       <c r="AA53" s="7">
         <f t="shared" si="13"/>
-        <v>152.35021766605649</v>
+        <v>152.35021750454715</v>
       </c>
     </row>
     <row r="54" spans="7:27">
@@ -10289,19 +10289,19 @@
       </c>
       <c r="Q54">
         <f t="shared" si="7"/>
-        <v>-12.416640630904002</v>
+        <v>-12.416640631180066</v>
       </c>
       <c r="R54">
         <f t="shared" si="8"/>
-        <v>-8.79631468932131</v>
+        <v>-8.7963146875874063</v>
       </c>
       <c r="T54">
         <f t="shared" si="9"/>
-        <v>-24.477948742274805</v>
+        <v>-24.477948740816963</v>
       </c>
       <c r="V54" s="7">
         <f t="shared" si="10"/>
-        <v>2.3407871943983096E-11</v>
+        <v>2.340787197810807E-11</v>
       </c>
       <c r="W54">
         <f t="shared" si="11"/>
@@ -10309,11 +10309,11 @@
       </c>
       <c r="Z54" s="7">
         <f t="shared" si="12"/>
-        <v>235.48575086365582</v>
+        <v>235.48575087029016</v>
       </c>
       <c r="AA54" s="7">
         <f t="shared" si="13"/>
-        <v>174.19933746686047</v>
+        <v>174.19933729173442</v>
       </c>
     </row>
     <row r="55" spans="7:27">
@@ -10351,19 +10351,19 @@
       </c>
       <c r="Q55">
         <f t="shared" si="7"/>
-        <v>-12.818782022187753</v>
+        <v>-12.818782022472758</v>
       </c>
       <c r="R55">
         <f t="shared" si="8"/>
-        <v>-8.9440440742101064</v>
+        <v>-8.9440440724470811</v>
       </c>
       <c r="T55">
         <f t="shared" si="9"/>
-        <v>-25.027819518447352</v>
+        <v>-25.02781951696933</v>
       </c>
       <c r="V55" s="7">
         <f t="shared" si="10"/>
-        <v>1.3506912581662896E-11</v>
+        <v>1.3506912601626399E-11</v>
       </c>
       <c r="W55">
         <f t="shared" si="11"/>
@@ -10371,11 +10371,11 @@
       </c>
       <c r="Z55" s="7">
         <f t="shared" si="12"/>
-        <v>232.9833989354498</v>
+        <v>232.98339894217597</v>
       </c>
       <c r="AA55" s="7">
         <f t="shared" si="13"/>
-        <v>198.11757750030708</v>
+        <v>198.11757731095972</v>
       </c>
     </row>
     <row r="56" spans="7:27">
@@ -10413,19 +10413,19 @@
       </c>
       <c r="Q56">
         <f t="shared" si="7"/>
-        <v>-13.220923413471517</v>
+        <v>-13.220923413765462</v>
       </c>
       <c r="R56">
         <f t="shared" si="8"/>
-        <v>-9.0917734590989028</v>
+        <v>-9.0917734573067595</v>
       </c>
       <c r="T56">
         <f t="shared" si="9"/>
-        <v>-25.577690294619913</v>
+        <v>-25.577690293121712</v>
       </c>
       <c r="V56" s="7">
         <f t="shared" si="10"/>
-        <v>7.7938177347033673E-12</v>
+        <v>7.7938177463800701E-12</v>
       </c>
       <c r="W56">
         <f t="shared" si="11"/>
@@ -10433,11 +10433,11 @@
       </c>
       <c r="Z56" s="7">
         <f t="shared" si="12"/>
-        <v>230.48104700724372</v>
+        <v>230.48104701406172</v>
       </c>
       <c r="AA56" s="7">
         <f t="shared" si="13"/>
-        <v>224.20565575134538</v>
+        <v>224.2056555471668</v>
       </c>
     </row>
     <row r="57" spans="7:27">
@@ -10475,19 +10475,19 @@
       </c>
       <c r="Q57">
         <f t="shared" si="7"/>
-        <v>-13.62306480475528</v>
+        <v>-13.623064805058167</v>
       </c>
       <c r="R57">
         <f t="shared" si="8"/>
-        <v>-9.2395028439877009</v>
+        <v>-9.2395028421664378</v>
       </c>
       <c r="T57">
         <f t="shared" si="9"/>
-        <v>-26.127561070792474</v>
+        <v>-26.127561069274098</v>
       </c>
       <c r="V57" s="7">
         <f t="shared" si="10"/>
-        <v>4.4972227749695196E-12</v>
+        <v>4.4972227817979965E-12</v>
       </c>
       <c r="W57">
         <f t="shared" si="11"/>
@@ -10495,11 +10495,11 @@
       </c>
       <c r="Z57" s="7">
         <f t="shared" si="12"/>
-        <v>227.97869507903761</v>
+        <v>227.97869508594744</v>
       </c>
       <c r="AA57" s="7">
         <f t="shared" si="13"/>
-        <v>252.56433039188857</v>
+        <v>252.5643301722628</v>
       </c>
     </row>
     <row r="58" spans="7:27">
@@ -10537,19 +10537,19 @@
       </c>
       <c r="Q58">
         <f t="shared" si="7"/>
-        <v>-14.025206196039033</v>
+        <v>-14.02520619635086</v>
       </c>
       <c r="R58">
         <f t="shared" si="8"/>
-        <v>-9.3872322288764956</v>
+        <v>-9.3872322270261108</v>
       </c>
       <c r="T58">
         <f t="shared" si="9"/>
-        <v>-26.677431846965021</v>
+        <v>-26.677431845426462</v>
       </c>
       <c r="V58" s="7">
         <f t="shared" si="10"/>
-        <v>2.5950071423468561E-12</v>
+        <v>2.5950071463394288E-12</v>
       </c>
       <c r="W58">
         <f t="shared" si="11"/>
@@ -10557,11 +10557,11 @@
       </c>
       <c r="Z58" s="7">
         <f t="shared" si="12"/>
-        <v>225.47634315083158</v>
+        <v>225.47634315783324</v>
       </c>
       <c r="AA58" s="7">
         <f t="shared" si="13"/>
-        <v>283.29431444015381</v>
+        <v>283.29431420445906</v>
       </c>
     </row>
     <row r="59" spans="7:27">
@@ -10599,19 +10599,19 @@
       </c>
       <c r="Q59">
         <f t="shared" si="7"/>
-        <v>-14.427347587322796</v>
+        <v>-14.427347587643565</v>
       </c>
       <c r="R59">
         <f t="shared" si="8"/>
-        <v>-9.5349616137652937</v>
+        <v>-9.5349616118857892</v>
       </c>
       <c r="T59">
         <f t="shared" si="9"/>
-        <v>-27.227302623137582</v>
+        <v>-27.227302621578843</v>
       </c>
       <c r="V59" s="7">
         <f t="shared" si="10"/>
-        <v>1.4973823636914989E-12</v>
+        <v>1.497382366025527E-12</v>
       </c>
       <c r="W59">
         <f t="shared" si="11"/>
@@ -10619,11 +10619,11 @@
       </c>
       <c r="Z59" s="7">
         <f t="shared" si="12"/>
-        <v>222.9739912226255</v>
+        <v>222.97399122971899</v>
       </c>
       <c r="AA59" s="7">
         <f t="shared" si="13"/>
-        <v>316.49619687317261</v>
+        <v>316.4961966207814</v>
       </c>
     </row>
     <row r="60" spans="7:27">
@@ -10661,19 +10661,19 @@
       </c>
       <c r="Q60">
         <f t="shared" si="7"/>
-        <v>-14.829488978606559</v>
+        <v>-14.829488978936268</v>
       </c>
       <c r="R60">
         <f t="shared" si="8"/>
-        <v>-9.6826909986540901</v>
+        <v>-9.6826909967454657</v>
       </c>
       <c r="T60">
         <f t="shared" si="9"/>
-        <v>-27.777173399310144</v>
+        <v>-27.777173397731225</v>
       </c>
       <c r="V60" s="7">
         <f t="shared" si="10"/>
-        <v>8.6402611634686875E-13</v>
+        <v>8.6402611771109547E-13</v>
       </c>
       <c r="W60">
         <f t="shared" si="11"/>
@@ -10681,11 +10681,11 @@
       </c>
       <c r="Z60" s="7">
         <f t="shared" si="12"/>
-        <v>220.47163929441939</v>
+        <v>220.47163930160474</v>
       </c>
       <c r="AA60" s="7">
         <f t="shared" si="13"/>
-        <v>352.27036976604063</v>
+        <v>352.27036949631889</v>
       </c>
     </row>
     <row r="61" spans="7:27">
@@ -10723,19 +10723,19 @@
       </c>
       <c r="Q61">
         <f t="shared" si="7"/>
-        <v>-15.231630369890311</v>
+        <v>-15.231630370228961</v>
       </c>
       <c r="R61">
         <f t="shared" si="8"/>
-        <v>-9.8304203835428847</v>
+        <v>-9.8304203816051405</v>
       </c>
       <c r="T61">
         <f t="shared" si="9"/>
-        <v>-28.32704417548269</v>
+        <v>-28.327044173883593</v>
       </c>
       <c r="V61" s="7">
         <f t="shared" si="10"/>
-        <v>4.9856412619220022E-13</v>
+        <v>4.9856412698945299E-13</v>
       </c>
       <c r="W61">
         <f t="shared" si="11"/>
@@ -10743,11 +10743,11 @@
       </c>
       <c r="Z61" s="7">
         <f t="shared" si="12"/>
-        <v>217.96928736621336</v>
+        <v>217.96928737349054</v>
       </c>
       <c r="AA61" s="7">
         <f t="shared" si="13"/>
-        <v>390.71696106000616</v>
+        <v>390.7169607723165</v>
       </c>
     </row>
     <row r="62" spans="7:27">
@@ -10785,19 +10785,19 @@
       </c>
       <c r="Q62">
         <f t="shared" si="7"/>
-        <v>-15.633771761174074</v>
+        <v>-15.633771761521666</v>
       </c>
       <c r="R62">
         <f t="shared" si="8"/>
-        <v>-9.9781497684316811</v>
+        <v>-9.9781497664648171</v>
       </c>
       <c r="T62">
         <f t="shared" si="9"/>
-        <v>-28.876914951655248</v>
+        <v>-28.876914950035975</v>
       </c>
       <c r="V62" s="7">
         <f t="shared" si="10"/>
-        <v>2.8768365124972796E-13</v>
+        <v>2.8768365171556651E-13</v>
       </c>
       <c r="W62">
         <f t="shared" si="11"/>
@@ -10805,11 +10805,11 @@
       </c>
       <c r="Z62" s="7">
         <f t="shared" si="12"/>
-        <v>215.46693543800731</v>
+        <v>215.46693544537629</v>
       </c>
       <c r="AA62" s="7">
         <f t="shared" si="13"/>
-        <v>431.93577258795278</v>
+        <v>431.93577228165276</v>
       </c>
     </row>
   </sheetData>
@@ -10935,19 +10935,19 @@
       </c>
       <c r="Q2">
         <f>-0.5*$A$13*$C$13*I2</f>
-        <v>4.5369412251132326</v>
+        <v>4.5369412294185834</v>
       </c>
       <c r="R2">
         <f>-(1 - 0.5*$A$13*$C$13)*M2</f>
-        <v>-2.449500192819547</v>
+        <v>-2.4495001906645819</v>
       </c>
       <c r="T2">
         <f>P2 + Q2 + R2</f>
-        <v>-1.1775523897558058</v>
+        <v>-1.1775523832954899</v>
       </c>
       <c r="V2" s="7">
         <f>EXP(T2)</f>
-        <v>0.30803175836306385</v>
+        <v>0.3080317603530463</v>
       </c>
       <c r="W2">
         <f>$C$7/G2</f>
@@ -10955,11 +10955,11 @@
       </c>
       <c r="Z2" s="7">
         <f>$Y$4*LN(V2) + $Y$7</f>
-        <v>380.16036055037807</v>
+        <v>380.16036057281474</v>
       </c>
       <c r="AA2" s="7">
         <f>(Z2 - W2)^2</f>
-        <v>51.270763211410575</v>
+        <v>51.270763532719812</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -11003,19 +11003,19 @@
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q62" si="7">-0.5*$A$13*$C$13*I3</f>
-        <v>4.3215513695055581</v>
+        <v>4.3215513736065141</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R62" si="8">-(1 - 0.5*$A$13*$C$13)*M3</f>
-        <v>-3.6943396147621121</v>
+        <v>-3.6943396115119906</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T62" si="9">P3 + Q3 + R3</f>
-        <v>-2.6377816673060455</v>
+        <v>-2.6377816599549679</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:V62" si="10">EXP(T3)</f>
-        <v>7.1519748308033648E-2</v>
+        <v>7.1519748833780858E-2</v>
       </c>
       <c r="W3">
         <f t="shared" ref="W3:W62" si="11">$C$7/G3</f>
@@ -11026,11 +11026,11 @@
       </c>
       <c r="Z3" s="7">
         <f t="shared" ref="Z3:Z62" si="12">$Y$4*LN(V3) + $Y$7</f>
-        <v>375.08898426944609</v>
+        <v>375.0889842949764</v>
       </c>
       <c r="AA3" s="7">
         <f t="shared" ref="AA3:AA62" si="13">(Z3 - W3)^2</f>
-        <v>33.432143560091376</v>
+        <v>33.432143855326636</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -11077,19 +11077,19 @@
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>4.1061615138978844</v>
+        <v>4.1061615177944448</v>
       </c>
       <c r="R4">
         <f t="shared" si="8"/>
-        <v>-5.0493320726007811</v>
+        <v>-5.0493320681585958</v>
       </c>
       <c r="T4">
         <f t="shared" si="9"/>
-        <v>-4.2081639807523885</v>
+        <v>-4.2081639724136419</v>
       </c>
       <c r="V4" s="7">
         <f t="shared" si="10"/>
-        <v>1.4873651594740619E-2</v>
+        <v>1.4873651718768232E-2</v>
       </c>
       <c r="W4">
         <f t="shared" si="11"/>
@@ -11100,11 +11100,11 @@
       </c>
       <c r="Z4" s="7">
         <f t="shared" si="12"/>
-        <v>369.63504649484696</v>
+        <v>369.63504652380743</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" si="13"/>
-        <v>15.592800189860736</v>
+        <v>15.592800418577331</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -11147,19 +11147,19 @@
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>3.8907716582902103</v>
+        <v>3.8907716619823756</v>
       </c>
       <c r="R5">
         <f t="shared" si="8"/>
-        <v>-6.518877254009519</v>
+        <v>-6.5188772482744906</v>
       </c>
       <c r="T5">
         <f t="shared" si="9"/>
-        <v>-5.8930990177688001</v>
+        <v>-5.8930990083416059</v>
       </c>
       <c r="V5" s="7">
         <f t="shared" si="10"/>
-        <v>2.7584150601495864E-3</v>
+        <v>2.7584150861537011E-3</v>
       </c>
       <c r="W5">
         <f t="shared" si="11"/>
@@ -11167,11 +11167,11 @@
       </c>
       <c r="Z5" s="7">
         <f t="shared" si="12"/>
-        <v>363.78326711128898</v>
+        <v>363.78326714402959</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="13"/>
-        <v>2.7137448281202503</v>
+        <v>2.7137449359904156</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -11215,19 +11215,19 @@
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>3.6753818026825362</v>
+        <v>3.6753818061703063</v>
       </c>
       <c r="R6">
         <f t="shared" si="8"/>
-        <v>-8.1056472306288772</v>
+        <v>-8.1056472234978756</v>
       </c>
       <c r="T6">
         <f t="shared" si="9"/>
-        <v>-7.6952588499958328</v>
+        <v>-7.6952588393770611</v>
       </c>
       <c r="V6" s="7">
         <f t="shared" si="10"/>
-        <v>4.5497920197831097E-4</v>
+        <v>4.5497920680963126E-4</v>
       </c>
       <c r="W6">
         <f t="shared" si="11"/>
@@ -11238,11 +11238,11 @@
       </c>
       <c r="Z6" s="7">
         <f t="shared" si="12"/>
-        <v>357.52436601396448</v>
+        <v>357.52436605084347</v>
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="13"/>
-        <v>1.2757253863870723</v>
+        <v>1.2757253030789069</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -11289,19 +11289,19 @@
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>3.4599919470748621</v>
+        <v>3.459991950358237</v>
       </c>
       <c r="R7">
         <f t="shared" si="8"/>
-        <v>-9.5260411363193551</v>
+        <v>-9.526041127938754</v>
       </c>
       <c r="T7">
         <f t="shared" si="9"/>
-        <v>-9.3310426112939844</v>
+        <v>-9.3310425996300079</v>
       </c>
       <c r="V7" s="7">
         <f t="shared" si="10"/>
-        <v>8.8629782495154997E-5</v>
+        <v>8.8629783528930696E-5</v>
       </c>
       <c r="W7">
         <f t="shared" si="11"/>
@@ -11312,11 +11312,11 @@
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="12"/>
-        <v>351.84328901097598</v>
+        <v>351.84328905148499</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="13"/>
-        <v>11.524709319687712</v>
+        <v>11.524709044647251</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -11359,19 +11359,19 @@
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>3.244602091467188</v>
+        <v>3.2446020945461678</v>
       </c>
       <c r="R8">
         <f t="shared" si="8"/>
-        <v>-10.282923095962946</v>
+        <v>-10.282923086916472</v>
       </c>
       <c r="T8">
         <f t="shared" si="9"/>
-        <v>-10.303314426545249</v>
+        <v>-10.303314414419797</v>
       </c>
       <c r="V8" s="7">
         <f t="shared" si="10"/>
-        <v>3.3521805295200755E-5</v>
+        <v>3.3521805701667825E-5</v>
       </c>
       <c r="W8">
         <f t="shared" si="11"/>
@@ -11379,11 +11379,11 @@
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="12"/>
-        <v>348.46658899660838</v>
+        <v>348.46658903872003</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="13"/>
-        <v>11.697791681951344</v>
+        <v>11.697791393890517</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -11427,19 +11427,19 @@
       </c>
       <c r="Q9">
         <f t="shared" si="7"/>
-        <v>3.0292122358595139</v>
+        <v>3.0292122387340985</v>
       </c>
       <c r="R9">
         <f t="shared" si="8"/>
-        <v>-11.039805055606534</v>
+        <v>-11.039805045894187</v>
       </c>
       <c r="T9">
         <f t="shared" si="9"/>
-        <v>-11.27558624179651</v>
+        <v>-11.27558622920958</v>
       </c>
       <c r="V9" s="7">
         <f t="shared" si="10"/>
-        <v>1.2678711361057238E-5</v>
+        <v>1.2678711520643298E-5</v>
       </c>
       <c r="W9">
         <f t="shared" si="11"/>
@@ -11450,11 +11450,11 @@
       </c>
       <c r="Z9" s="7">
         <f t="shared" si="12"/>
-        <v>345.08988898224072</v>
+        <v>345.08988902595513</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="13"/>
-        <v>12.307760940403069</v>
+        <v>12.307760633681639</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -11501,19 +11501,19 @@
       </c>
       <c r="Q10">
         <f t="shared" si="7"/>
-        <v>2.8138223802518398</v>
+        <v>2.8138223829220292</v>
       </c>
       <c r="R10">
         <f t="shared" si="8"/>
-        <v>-11.796687015250129</v>
+        <v>-11.796687004871909</v>
       </c>
       <c r="T10">
         <f t="shared" si="9"/>
-        <v>-12.247858057047781</v>
+        <v>-12.247858043999372</v>
       </c>
       <c r="V10" s="7">
         <f t="shared" si="10"/>
-        <v>4.7953778253110561E-6</v>
+        <v>4.7953778878831053E-6</v>
       </c>
       <c r="W10">
         <f t="shared" si="11"/>
@@ -11521,15 +11521,15 @@
       </c>
       <c r="Y10" s="7">
         <f>AVERAGE(AA2:AA9)</f>
-        <v>17.476929889739015</v>
+        <v>17.476929889739061</v>
       </c>
       <c r="Z10" s="7">
         <f t="shared" si="12"/>
-        <v>341.71318896787307</v>
+        <v>341.71318901319017</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="13"/>
-        <v>13.374975810771813</v>
+        <v>13.374975479306043</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -11572,19 +11572,19 @@
       </c>
       <c r="Q11">
         <f t="shared" si="7"/>
-        <v>2.5984325246441657</v>
+        <v>2.5984325271099604</v>
       </c>
       <c r="R11">
         <f t="shared" si="8"/>
-        <v>-12.553568974893716</v>
+        <v>-12.553568963849626</v>
       </c>
       <c r="T11">
         <f t="shared" si="9"/>
-        <v>-13.220129872299042</v>
+        <v>-13.220129858789157</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" si="10"/>
-        <v>1.8137212712418483E-6</v>
+        <v>1.8137212957450137E-6</v>
       </c>
       <c r="W11">
         <f t="shared" si="11"/>
@@ -11592,11 +11592,11 @@
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="12"/>
-        <v>338.33648895350541</v>
+        <v>338.33648900042527</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="13"/>
-        <v>14.940898995294379</v>
+        <v>14.940898632571363</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -11642,19 +11642,19 @@
       </c>
       <c r="Q12">
         <f t="shared" si="7"/>
-        <v>2.3830426690364916</v>
+        <v>2.3830426712978912</v>
       </c>
       <c r="R12">
         <f t="shared" si="8"/>
-        <v>-13.310450934537306</v>
+        <v>-13.310450922827343</v>
       </c>
       <c r="T12">
         <f t="shared" si="9"/>
-        <v>-14.192401687550305</v>
+        <v>-14.192401673578942</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="10"/>
-        <v>6.8599075392808256E-7</v>
+        <v>6.8599076351230822E-7</v>
       </c>
       <c r="W12">
         <f t="shared" si="11"/>
@@ -11662,19 +11662,19 @@
       </c>
       <c r="Z12" s="7">
         <f t="shared" si="12"/>
-        <v>334.95978893913781</v>
+        <v>334.95978898766032</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="13"/>
-        <v>17.066153708370567</v>
+        <v>17.066153307465942</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="5">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="C13" s="9">
-        <v>0.51178759167831833</v>
+        <v>0.49089830268790058</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -11713,19 +11713,19 @@
       </c>
       <c r="Q13">
         <f t="shared" si="7"/>
-        <v>2.1676528134288144</v>
+        <v>2.1676528154858183</v>
       </c>
       <c r="R13">
         <f t="shared" si="8"/>
-        <v>-14.067332894180904</v>
+        <v>-14.067332881805068</v>
       </c>
       <c r="T13">
         <f t="shared" si="9"/>
-        <v>-15.16467350280158</v>
+        <v>-15.164673488368742</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="10"/>
-        <v>2.594573498896038E-7</v>
+        <v>2.5945735363430999E-7</v>
       </c>
       <c r="W13">
         <f t="shared" si="11"/>
@@ -11733,11 +11733,11 @@
       </c>
       <c r="Z13" s="7">
         <f t="shared" si="12"/>
-        <v>331.5830889247701</v>
+        <v>331.58308897489536</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="13"/>
-        <v>19.828737975731574</v>
+        <v>19.828737529321263</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -11779,19 +11779,19 @@
       </c>
       <c r="Q14">
         <f t="shared" si="7"/>
-        <v>1.9522629578211403</v>
+        <v>1.9522629596737491</v>
       </c>
       <c r="R14">
         <f t="shared" si="8"/>
-        <v>-14.82421485382449</v>
+        <v>-14.824214840782782</v>
       </c>
       <c r="T14">
         <f t="shared" si="9"/>
-        <v>-16.136945318052842</v>
+        <v>-16.136945303158523</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="10"/>
-        <v>9.8132687687500087E-8</v>
+        <v>9.8132689149119627E-8</v>
       </c>
       <c r="W14">
         <f t="shared" si="11"/>
@@ -11799,11 +11799,11 @@
       </c>
       <c r="Z14" s="7">
         <f t="shared" si="12"/>
-        <v>328.2063889104025</v>
+        <v>328.20638896213046</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="13"/>
-        <v>23.322383580630287</v>
+        <v>23.322383081007935</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -11844,19 +11844,19 @@
       </c>
       <c r="Q15">
         <f t="shared" si="7"/>
-        <v>1.7368731022134662</v>
+        <v>1.7368731038616798</v>
       </c>
       <c r="R15">
         <f t="shared" si="8"/>
-        <v>-15.581096813468083</v>
+        <v>-15.581096799760502</v>
       </c>
       <c r="T15">
         <f t="shared" si="9"/>
-        <v>-17.109217133304107</v>
+        <v>-17.109217117948312</v>
       </c>
       <c r="V15" s="7">
         <f t="shared" si="10"/>
-        <v>3.7116020790584137E-8</v>
+        <v>3.7116021360530141E-8</v>
       </c>
       <c r="W15">
         <f t="shared" si="11"/>
@@ -11864,11 +11864,11 @@
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="12"/>
-        <v>324.82968889603484</v>
+        <v>324.8296889493655</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="13"/>
-        <v>27.655047689055113</v>
+        <v>27.655047128143789</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -11909,19 +11909,19 @@
       </c>
       <c r="Q16">
         <f t="shared" si="7"/>
-        <v>1.5214832466057922</v>
+        <v>1.5214832480496108</v>
       </c>
       <c r="R16">
         <f t="shared" si="8"/>
-        <v>-16.337978773111669</v>
+        <v>-16.337978758738217</v>
       </c>
       <c r="T16">
         <f t="shared" si="9"/>
-        <v>-18.081488948555368</v>
+        <v>-18.081488932738097</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="10"/>
-        <v>1.403812564182479E-8</v>
+        <v>1.4038125863869629E-8</v>
       </c>
       <c r="W16">
         <f t="shared" si="11"/>
@@ -11929,11 +11929,11 @@
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="12"/>
-        <v>321.45298888166724</v>
+        <v>321.4529889366006</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="13"/>
-        <v>32.94752623499236</v>
+        <v>32.94752560435802</v>
       </c>
     </row>
     <row r="17" spans="3:27">
@@ -11971,19 +11971,19 @@
       </c>
       <c r="Q17">
         <f t="shared" si="7"/>
-        <v>1.3060933909981181</v>
+        <v>1.3060933922375415</v>
       </c>
       <c r="R17">
         <f t="shared" si="8"/>
-        <v>-17.094860732755265</v>
+        <v>-17.094860717715939</v>
       </c>
       <c r="T17">
         <f t="shared" si="9"/>
-        <v>-19.05376076380664</v>
+        <v>-19.053760747527889</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="10"/>
-        <v>5.3095393131596276E-9</v>
+        <v>5.3095393995922956E-9</v>
       </c>
       <c r="W17">
         <f t="shared" si="11"/>
@@ -11991,11 +11991,11 @@
       </c>
       <c r="Z17" s="7">
         <f t="shared" si="12"/>
-        <v>318.07628886729952</v>
+        <v>318.07628892383565</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="13"/>
-        <v>39.33217909754277</v>
+        <v>39.332178388405971</v>
       </c>
     </row>
     <row r="18" spans="3:27">
@@ -12036,19 +12036,19 @@
       </c>
       <c r="Q18">
         <f t="shared" si="7"/>
-        <v>1.0907035353904442</v>
+        <v>1.0907035364254722</v>
       </c>
       <c r="R18">
         <f t="shared" si="8"/>
-        <v>-17.851742692398851</v>
+        <v>-17.851742676693654</v>
       </c>
       <c r="T18">
         <f t="shared" si="9"/>
-        <v>-20.026032579057897</v>
+        <v>-20.026032562317674</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="10"/>
-        <v>2.008188873448741E-9</v>
+        <v>2.0081889070662718E-9</v>
       </c>
       <c r="W18">
         <f t="shared" si="11"/>
@@ -12056,11 +12056,11 @@
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="12"/>
-        <v>314.69958885293192</v>
+        <v>314.69958891107069</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="13"/>
-        <v>46.951757963929218</v>
+        <v>46.951757167179828</v>
       </c>
     </row>
     <row r="19" spans="3:27">
@@ -12101,19 +12101,19 @@
       </c>
       <c r="Q19">
         <f t="shared" si="7"/>
-        <v>0.87531367978277008</v>
+        <v>0.87531368061340298</v>
       </c>
       <c r="R19">
         <f t="shared" si="8"/>
-        <v>-18.608624652042444</v>
+        <v>-18.608624635671376</v>
       </c>
       <c r="T19">
         <f t="shared" si="9"/>
-        <v>-20.998304394309166</v>
+        <v>-20.998304377107466</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="10"/>
-        <v>7.595428366916843E-10</v>
+        <v>7.5954284975711219E-10</v>
       </c>
       <c r="W19">
         <f t="shared" si="11"/>
@@ -12121,11 +12121,11 @@
       </c>
       <c r="Z19" s="7">
         <f t="shared" si="12"/>
-        <v>311.32288883856427</v>
+        <v>311.32288889830579</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="13"/>
-        <v>55.958328555086027</v>
+        <v>55.958327661289516</v>
       </c>
     </row>
     <row r="20" spans="3:27">
@@ -12163,19 +12163,19 @@
       </c>
       <c r="Q20">
         <f t="shared" si="7"/>
-        <v>0.65992382417509599</v>
+        <v>0.65992382480133371</v>
       </c>
       <c r="R20">
         <f t="shared" si="8"/>
-        <v>-19.365506611686033</v>
+        <v>-19.365506594649091</v>
       </c>
       <c r="T20">
         <f t="shared" si="9"/>
-        <v>-21.970576209560427</v>
+        <v>-21.970576191897248</v>
       </c>
       <c r="V20" s="7">
         <f t="shared" si="10"/>
-        <v>2.8727642523928175E-10</v>
+        <v>2.8727643031349683E-10</v>
       </c>
       <c r="W20">
         <f t="shared" si="11"/>
@@ -12183,11 +12183,11 @@
       </c>
       <c r="Z20" s="7">
         <f t="shared" si="12"/>
-        <v>307.94618882419661</v>
+        <v>307.94618888554089</v>
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="13"/>
-        <v>66.512279601277427</v>
+        <v>66.512278600690124</v>
       </c>
     </row>
     <row r="21" spans="3:27">
@@ -12228,19 +12228,19 @@
       </c>
       <c r="Q21">
         <f t="shared" si="7"/>
-        <v>0.444533968567422</v>
+        <v>0.44453396898926451</v>
       </c>
       <c r="R21">
         <f t="shared" si="8"/>
-        <v>-20.122388571329623</v>
+        <v>-20.122388553626809</v>
       </c>
       <c r="T21">
         <f t="shared" si="9"/>
-        <v>-22.942848024811692</v>
+        <v>-22.942848006687036</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="10"/>
-        <v>1.0865449650966854E-10</v>
+        <v>1.0865449847899388E-10</v>
       </c>
       <c r="W21">
         <f t="shared" si="11"/>
@@ -12248,11 +12248,11 @@
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="12"/>
-        <v>304.56948880982901</v>
+        <v>304.56948887277593</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="13"/>
-        <v>78.781411601336345</v>
+        <v>78.781410483916474</v>
       </c>
     </row>
     <row r="22" spans="3:27">
@@ -12294,19 +12294,19 @@
       </c>
       <c r="Q22">
         <f t="shared" si="7"/>
-        <v>0.22914411295974793</v>
+        <v>0.2291441131771953</v>
       </c>
       <c r="R22">
         <f t="shared" si="8"/>
-        <v>-20.879270530973212</v>
+        <v>-20.879270512604524</v>
       </c>
       <c r="T22">
         <f t="shared" si="9"/>
-        <v>-23.915119840062957</v>
+        <v>-23.915119821476821</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="10"/>
-        <v>4.1095608878926082E-11</v>
+        <v>4.1095609642734636E-11</v>
       </c>
       <c r="W22">
         <f t="shared" si="11"/>
@@ -12314,11 +12314,11 @@
       </c>
       <c r="Z22" s="7">
         <f t="shared" si="12"/>
-        <v>301.19278879546135</v>
+        <v>301.19278886001098</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="13"/>
-        <v>92.940098986692888</v>
+        <v>92.940097742105834</v>
       </c>
     </row>
     <row r="23" spans="3:27">
@@ -12356,19 +12356,19 @@
       </c>
       <c r="Q23">
         <f t="shared" si="7"/>
-        <v>1.3754257352073888E-2</v>
+        <v>1.3754257365126053E-2</v>
       </c>
       <c r="R23">
         <f t="shared" si="8"/>
-        <v>-21.636152490616801</v>
+        <v>-21.636152471582243</v>
       </c>
       <c r="T23">
         <f t="shared" si="9"/>
-        <v>-24.887391655314218</v>
+        <v>-24.887391636266607</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="10"/>
-        <v>1.554329662720763E-11</v>
+        <v>1.5543296923270308E-11</v>
       </c>
       <c r="W23">
         <f t="shared" si="11"/>
@@ -12376,11 +12376,11 @@
       </c>
       <c r="Z23" s="7">
         <f t="shared" si="12"/>
-        <v>297.81608878109375</v>
+        <v>297.81608884724608</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="13"/>
-        <v>109.16851984619419</v>
+        <v>109.16851846382573</v>
       </c>
     </row>
     <row r="24" spans="3:27">
@@ -12418,19 +12418,19 @@
       </c>
       <c r="Q24">
         <f t="shared" si="7"/>
-        <v>-0.20163559825560015</v>
+        <v>-0.20163559844694318</v>
       </c>
       <c r="R24">
         <f t="shared" si="8"/>
-        <v>-22.393034450260387</v>
+        <v>-22.393034430559958</v>
       </c>
       <c r="T24">
         <f t="shared" si="9"/>
-        <v>-25.859663470565479</v>
+        <v>-25.859663451056392</v>
       </c>
       <c r="V24" s="7">
         <f t="shared" si="10"/>
-        <v>5.878829311256514E-12</v>
+        <v>5.8788294259471117E-12</v>
       </c>
       <c r="W24">
         <f t="shared" si="11"/>
@@ -12438,11 +12438,11 @@
       </c>
       <c r="Z24" s="7">
         <f t="shared" si="12"/>
-        <v>294.4393887667261</v>
+        <v>294.43938883448118</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="13"/>
-        <v>127.65194785487705</v>
+        <v>127.65194632384039</v>
       </c>
     </row>
     <row r="25" spans="3:27">
@@ -12480,19 +12480,19 @@
       </c>
       <c r="Q25">
         <f t="shared" si="7"/>
-        <v>-0.41702545386327422</v>
+        <v>-0.41702545425901238</v>
       </c>
       <c r="R25">
         <f t="shared" si="8"/>
-        <v>-23.14991640990398</v>
+        <v>-23.149916389537676</v>
       </c>
       <c r="T25">
         <f t="shared" si="9"/>
-        <v>-26.831935285816748</v>
+        <v>-26.83193526584618</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="10"/>
-        <v>2.2235073356569755E-12</v>
+        <v>2.2235073800616795E-12</v>
       </c>
       <c r="W25">
         <f t="shared" si="11"/>
@@ -12500,11 +12500,11 @@
       </c>
       <c r="Z25" s="7">
         <f t="shared" si="12"/>
-        <v>291.06268875235844</v>
+        <v>291.06268882171622</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="13"/>
-        <v>148.58010149366874</v>
+        <v>148.58009980281705</v>
       </c>
     </row>
     <row r="26" spans="3:27">
@@ -12542,19 +12542,19 @@
       </c>
       <c r="Q26">
         <f t="shared" si="7"/>
-        <v>-0.63241530947094826</v>
+        <v>-0.63241531007108165</v>
       </c>
       <c r="R26">
         <f t="shared" si="8"/>
-        <v>-23.906798369547577</v>
+        <v>-23.906798348515402</v>
       </c>
       <c r="T26">
         <f t="shared" si="9"/>
-        <v>-27.804207101068016</v>
+        <v>-27.804207080635976</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="10"/>
-        <v>8.4098119029478641E-13</v>
+        <v>8.4098120747774798E-13</v>
       </c>
       <c r="W26">
         <f t="shared" si="11"/>
@@ -12562,11 +12562,11 @@
       </c>
       <c r="Z26" s="7">
         <f t="shared" si="12"/>
-        <v>287.68598873799078</v>
+        <v>287.68598880895127</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="13"/>
-        <v>172.14654605195435</v>
+        <v>172.14654418988559</v>
       </c>
     </row>
     <row r="27" spans="3:27">
@@ -12604,19 +12604,19 @@
       </c>
       <c r="Q27">
         <f t="shared" si="7"/>
-        <v>-0.84780516507862225</v>
+        <v>-0.84780516588315091</v>
       </c>
       <c r="R27">
         <f t="shared" si="8"/>
-        <v>-24.663680329191163</v>
+        <v>-24.663680307493113</v>
       </c>
       <c r="T27">
         <f t="shared" si="9"/>
-        <v>-28.776478916319277</v>
+        <v>-28.776478895425754</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="10"/>
-        <v>3.1807826809830204E-13</v>
+        <v>3.1807827474407783E-13</v>
       </c>
       <c r="W27">
         <f t="shared" si="11"/>
@@ -12624,11 +12624,11 @@
       </c>
       <c r="Z27" s="7">
         <f t="shared" si="12"/>
-        <v>284.30928872362313</v>
+        <v>284.30928879618637</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="13"/>
-        <v>198.54814427421215</v>
+        <v>198.54814222927683</v>
       </c>
     </row>
     <row r="28" spans="3:27">
@@ -12666,19 +12666,19 @@
       </c>
       <c r="Q28">
         <f t="shared" si="7"/>
-        <v>-1.0631950206862963</v>
+        <v>-1.0631950216952202</v>
       </c>
       <c r="R28">
         <f t="shared" si="8"/>
-        <v>-25.420562288834752</v>
+        <v>-25.420562266470832</v>
       </c>
       <c r="T28">
         <f t="shared" si="9"/>
-        <v>-29.748750731570539</v>
+        <v>-29.748750710215543</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="10"/>
-        <v>1.2030445603777559E-13</v>
+        <v>1.2030445860687677E-13</v>
       </c>
       <c r="W28">
         <f t="shared" si="11"/>
@@ -12686,11 +12686,11 @@
       </c>
       <c r="Z28" s="7">
         <f t="shared" si="12"/>
-        <v>280.93258870925553</v>
+        <v>280.93258878342141</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="13"/>
-        <v>227.98455184931672</v>
+        <v>227.98454960963207</v>
       </c>
     </row>
     <row r="29" spans="3:27">
@@ -12728,19 +12728,19 @@
       </c>
       <c r="Q29">
         <f t="shared" si="7"/>
-        <v>-1.2785848762939704</v>
+        <v>-1.2785848775072892</v>
       </c>
       <c r="R29">
         <f t="shared" si="8"/>
-        <v>-26.177444248478341</v>
+        <v>-26.17744422544855</v>
       </c>
       <c r="T29">
         <f t="shared" si="9"/>
-        <v>-30.721022546821803</v>
+        <v>-30.721022525005331</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="10"/>
-        <v>4.5501889296228487E-14</v>
+        <v>4.5501890288919204E-14</v>
       </c>
       <c r="W29">
         <f t="shared" si="11"/>
@@ -12748,11 +12748,11 @@
       </c>
       <c r="Z29" s="7">
         <f t="shared" si="12"/>
-        <v>277.55588869488787</v>
+        <v>277.55588877065651</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="13"/>
-        <v>260.65775424917996</v>
+        <v>260.65775180262597</v>
       </c>
     </row>
     <row r="30" spans="3:27">
@@ -12790,19 +12790,19 @@
       </c>
       <c r="Q30">
         <f t="shared" si="7"/>
-        <v>-1.4939747319016445</v>
+        <v>-1.4939747333193585</v>
       </c>
       <c r="R30">
         <f t="shared" si="8"/>
-        <v>-26.934326208121931</v>
+        <v>-26.934326184426265</v>
       </c>
       <c r="T30">
         <f t="shared" si="9"/>
-        <v>-31.693294362073068</v>
+        <v>-31.693294339795116</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="10"/>
-        <v>1.7209852383822929E-14</v>
+        <v>1.7209852767223197E-14</v>
       </c>
       <c r="W30">
         <f t="shared" si="11"/>
@@ -12810,11 +12810,11 @@
       </c>
       <c r="Z30" s="7">
         <f t="shared" si="12"/>
-        <v>274.17918868052027</v>
+        <v>274.17918875789155</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="13"/>
-        <v>296.77164170511276</v>
+        <v>296.77163903935309</v>
       </c>
     </row>
     <row r="31" spans="3:27">
@@ -12852,19 +12852,19 @@
       </c>
       <c r="Q31">
         <f t="shared" si="7"/>
-        <v>-1.7093645875093184</v>
+        <v>-1.7093645891314277</v>
       </c>
       <c r="R31">
         <f t="shared" si="8"/>
-        <v>-27.691208167765524</v>
+        <v>-27.691208143403987</v>
       </c>
       <c r="T31">
         <f t="shared" si="9"/>
-        <v>-32.665566177324337</v>
+        <v>-32.665566154584909</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="10"/>
-        <v>6.5091587108565196E-15</v>
+        <v>6.5091588588710679E-15</v>
       </c>
       <c r="W31">
         <f t="shared" si="11"/>
@@ -12872,11 +12872,11 @@
       </c>
       <c r="Z31" s="7">
         <f t="shared" si="12"/>
-        <v>270.80248866615261</v>
+        <v>270.80248874512665</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="13"/>
-        <v>336.53161936797267</v>
+        <v>336.53161647044703</v>
       </c>
     </row>
     <row r="32" spans="3:27">
@@ -12914,19 +12914,19 @@
       </c>
       <c r="Q32">
         <f t="shared" si="7"/>
-        <v>-1.9247544431169925</v>
+        <v>-1.924754444943497</v>
       </c>
       <c r="R32">
         <f t="shared" si="8"/>
-        <v>-28.448090127409113</v>
+        <v>-28.448090102381702</v>
       </c>
       <c r="T32">
         <f t="shared" si="9"/>
-        <v>-33.637837992575598</v>
+        <v>-33.637837969374687</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="10"/>
-        <v>2.4619122917606277E-15</v>
+        <v>2.4619123488792371E-15</v>
       </c>
       <c r="W32">
         <f t="shared" si="11"/>
@@ -12934,11 +12934,11 @@
       </c>
       <c r="Z32" s="7">
         <f t="shared" si="12"/>
-        <v>267.42578865178496</v>
+        <v>267.42578873236175</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="13"/>
-        <v>380.14424993385643</v>
+        <v>380.14424679179837</v>
       </c>
     </row>
     <row r="33" spans="7:27">
@@ -12976,19 +12976,19 @@
       </c>
       <c r="Q33">
         <f t="shared" si="7"/>
-        <v>-2.1401442987246666</v>
+        <v>-2.1401443007555661</v>
       </c>
       <c r="R33">
         <f t="shared" si="8"/>
-        <v>-29.204972087052703</v>
+        <v>-29.20497206135942</v>
       </c>
       <c r="T33">
         <f t="shared" si="9"/>
-        <v>-34.610109807826859</v>
+        <v>-34.610109784164479</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="10"/>
-        <v>9.3115138246867483E-16</v>
+        <v>9.3115140450193344E-16</v>
       </c>
       <c r="W33">
         <f t="shared" si="11"/>
@@ -12996,11 +12996,11 @@
       </c>
       <c r="Z33" s="7">
         <f t="shared" si="12"/>
-        <v>264.0490886374173</v>
+        <v>264.04908871959674</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="13"/>
-        <v>427.81692623315644</v>
+        <v>427.81692283360081</v>
       </c>
     </row>
     <row r="34" spans="7:27">
@@ -13038,19 +13038,19 @@
       </c>
       <c r="Q34">
         <f t="shared" si="7"/>
-        <v>-2.3555341543323407</v>
+        <v>-2.3555341565676353</v>
       </c>
       <c r="R34">
         <f t="shared" si="8"/>
-        <v>-29.961854046696292</v>
+        <v>-29.961854020337139</v>
       </c>
       <c r="T34">
         <f t="shared" si="9"/>
-        <v>-35.58238162307812</v>
+        <v>-35.582381598954264</v>
       </c>
       <c r="V34" s="7">
         <f t="shared" si="10"/>
-        <v>3.5218269146918381E-16</v>
+        <v>3.5218269996518869E-16</v>
       </c>
       <c r="W34">
         <f t="shared" si="11"/>
@@ -13058,11 +13058,11 @@
       </c>
       <c r="Z34" s="7">
         <f t="shared" si="12"/>
-        <v>260.6723886230497</v>
+        <v>260.67238870683184</v>
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="13"/>
-        <v>479.75757147844433</v>
+        <v>479.75756780822206</v>
       </c>
     </row>
     <row r="35" spans="7:27">
@@ -13100,19 +13100,19 @@
       </c>
       <c r="Q35">
         <f t="shared" si="7"/>
-        <v>-2.5709240099400179</v>
+        <v>-2.5709240123797081</v>
       </c>
       <c r="R35">
         <f t="shared" si="8"/>
-        <v>-30.718736006339888</v>
+        <v>-30.718735979314861</v>
       </c>
       <c r="T35">
         <f t="shared" si="9"/>
-        <v>-36.554653438329396</v>
+        <v>-36.554653413744063</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="10"/>
-        <v>1.3320352684398145E-16</v>
+        <v>1.3320353011883453E-16</v>
       </c>
       <c r="W35">
         <f t="shared" si="11"/>
@@ -13120,11 +13120,11 @@
       </c>
       <c r="Z35" s="7">
         <f t="shared" si="12"/>
-        <v>257.29568860868198</v>
+        <v>257.29568869406688</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="13"/>
-        <v>536.17436504814782</v>
+        <v>536.17436109389826</v>
       </c>
     </row>
     <row r="36" spans="7:27">
@@ -13162,19 +13162,19 @@
       </c>
       <c r="Q36">
         <f t="shared" si="7"/>
-        <v>-2.786313865547692</v>
+        <v>-2.7863138681917774</v>
       </c>
       <c r="R36">
         <f t="shared" si="8"/>
-        <v>-31.475617965983481</v>
+        <v>-31.475617938292583</v>
       </c>
       <c r="T36">
         <f t="shared" si="9"/>
-        <v>-37.526925253580664</v>
+        <v>-37.526925228533855</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="10"/>
-        <v>5.0380612089870265E-17</v>
+        <v>5.0380613351743854E-17</v>
       </c>
       <c r="W36">
         <f t="shared" si="11"/>
@@ -13182,11 +13182,11 @@
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="12"/>
-        <v>253.91898859431436</v>
+        <v>253.91898868130193</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="13"/>
-        <v>597.27549184909083</v>
+        <v>597.27548759727404</v>
       </c>
     </row>
     <row r="37" spans="7:27">
@@ -13224,19 +13224,19 @@
       </c>
       <c r="Q37">
         <f t="shared" si="7"/>
-        <v>-3.0017037211553661</v>
+        <v>-3.0017037240038467</v>
       </c>
       <c r="R37">
         <f t="shared" si="8"/>
-        <v>-32.232499925627067</v>
+        <v>-32.232499897270294</v>
       </c>
       <c r="T37">
         <f t="shared" si="9"/>
-        <v>-38.499197068831926</v>
+        <v>-38.499197043323633</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="10"/>
-        <v>1.9055096623101793E-17</v>
+        <v>1.9055097109164775E-17</v>
       </c>
       <c r="W37">
         <f t="shared" si="11"/>
@@ -13244,11 +13244,11 @@
       </c>
       <c r="Z37" s="7">
         <f t="shared" si="12"/>
-        <v>250.54228857994673</v>
+        <v>250.54228866853703</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="13"/>
-        <v>663.26891345379056</v>
+        <v>663.26890889068022</v>
       </c>
     </row>
     <row r="38" spans="7:27">
@@ -13286,19 +13286,19 @@
       </c>
       <c r="Q38">
         <f t="shared" si="7"/>
-        <v>-3.2170935767630402</v>
+        <v>-3.2170935798159159</v>
       </c>
       <c r="R38">
         <f t="shared" si="8"/>
-        <v>-32.989381885270653</v>
+        <v>-32.989381856248016</v>
       </c>
       <c r="T38">
         <f t="shared" si="9"/>
-        <v>-39.471468884083187</v>
+        <v>-39.471468858113425</v>
       </c>
       <c r="V38" s="7">
         <f t="shared" si="10"/>
-        <v>7.2070721703032093E-18</v>
+        <v>7.2070723574691566E-18</v>
       </c>
       <c r="W38">
         <f t="shared" si="11"/>
@@ -13306,11 +13306,11 @@
       </c>
       <c r="Z38" s="7">
         <f t="shared" si="12"/>
-        <v>247.1655885655791</v>
+        <v>247.16558865577207</v>
       </c>
       <c r="AA38" s="7">
         <f t="shared" si="13"/>
-        <v>734.36215934826805</v>
+        <v>734.36215445996834</v>
       </c>
     </row>
     <row r="39" spans="7:27">
@@ -13348,19 +13348,19 @@
       </c>
       <c r="Q39">
         <f t="shared" si="7"/>
-        <v>-3.4324834323707143</v>
+        <v>-3.4324834356279852</v>
       </c>
       <c r="R39">
         <f t="shared" si="8"/>
-        <v>-33.746263844914253</v>
+        <v>-33.746263815225738</v>
       </c>
       <c r="T39">
         <f t="shared" si="9"/>
-        <v>-40.443740699334455</v>
+        <v>-40.443740672903218</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="10"/>
-        <v>2.7258790808221849E-18</v>
+        <v>2.7258791528705435E-18</v>
       </c>
       <c r="W39">
         <f t="shared" si="11"/>
@@ -13368,11 +13368,11 @@
       </c>
       <c r="Z39" s="7">
         <f t="shared" si="12"/>
-        <v>243.78888855121144</v>
+        <v>243.78888864300714</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="13"/>
-        <v>810.76213675499775</v>
+        <v>810.76213152743742</v>
       </c>
     </row>
     <row r="40" spans="7:27">
@@ -13410,19 +13410,19 @@
       </c>
       <c r="Q40">
         <f t="shared" si="7"/>
-        <v>-3.6478732879783884</v>
+        <v>-3.6478732914400545</v>
       </c>
       <c r="R40">
         <f t="shared" si="8"/>
-        <v>-34.503145804557839</v>
+        <v>-34.503145774203453</v>
       </c>
       <c r="T40">
         <f t="shared" si="9"/>
-        <v>-41.416012514585717</v>
+        <v>-41.416012487692996</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="10"/>
-        <v>1.030989642906746E-18</v>
+        <v>1.0309896706328632E-18</v>
       </c>
       <c r="W40">
         <f t="shared" si="11"/>
@@ -13430,11 +13430,11 @@
       </c>
       <c r="Z40" s="7">
         <f t="shared" si="12"/>
-        <v>240.41218853684381</v>
+        <v>240.41218863024224</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="13"/>
-        <v>892.67495761370003</v>
+        <v>892.67495203264593</v>
       </c>
     </row>
     <row r="41" spans="7:27">
@@ -13472,19 +13472,19 @@
       </c>
       <c r="Q41">
         <f t="shared" si="7"/>
-        <v>-3.8632631435860625</v>
+        <v>-3.8632631472521237</v>
       </c>
       <c r="R41">
         <f t="shared" si="8"/>
-        <v>-35.260027764201425</v>
+        <v>-35.260027733181168</v>
       </c>
       <c r="T41">
         <f t="shared" si="9"/>
-        <v>-42.388284329836978</v>
+        <v>-42.388284302482781</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="10"/>
-        <v>3.8994379877642033E-19</v>
+        <v>3.8994380944302001E-19</v>
       </c>
       <c r="W41">
         <f t="shared" si="11"/>
@@ -13492,11 +13492,11 @@
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="12"/>
-        <v>237.03548852247619</v>
+        <v>237.03548861747731</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="13"/>
-        <v>980.30578141156013</v>
+        <v>980.30577546262089</v>
       </c>
     </row>
     <row r="42" spans="7:27">
@@ -13534,19 +13534,19 @@
       </c>
       <c r="Q42">
         <f t="shared" si="7"/>
-        <v>-4.0786529991937366</v>
+        <v>-4.0786530030641925</v>
       </c>
       <c r="R42">
         <f t="shared" si="8"/>
-        <v>-36.016909723845018</v>
+        <v>-36.016909692158883</v>
       </c>
       <c r="T42">
         <f t="shared" si="9"/>
-        <v>-43.360556145088246</v>
+        <v>-43.360556117272566</v>
       </c>
       <c r="V42" s="7">
         <f t="shared" si="10"/>
-        <v>1.4748563892017482E-19</v>
+        <v>1.4748564302258828E-19</v>
       </c>
       <c r="W42">
         <f t="shared" si="11"/>
@@ -13554,11 +13554,11 @@
       </c>
       <c r="Z42" s="7">
         <f t="shared" si="12"/>
-        <v>233.65878850810853</v>
+        <v>233.65878860471238</v>
       </c>
       <c r="AA42" s="7">
         <f t="shared" si="13"/>
-        <v>1073.8586726542594</v>
+        <v>1073.8586663228846</v>
       </c>
     </row>
     <row r="43" spans="7:27">
@@ -13596,19 +13596,19 @@
       </c>
       <c r="Q43">
         <f t="shared" si="7"/>
-        <v>-4.2940428548014102</v>
+        <v>-4.2940428588762618</v>
       </c>
       <c r="R43">
         <f t="shared" si="8"/>
-        <v>-36.773791683488611</v>
+        <v>-36.773791651136612</v>
       </c>
       <c r="T43">
         <f t="shared" si="9"/>
-        <v>-44.332827960339515</v>
+        <v>-44.332827932062365</v>
       </c>
       <c r="V43" s="7">
         <f t="shared" si="10"/>
-        <v>5.5782432637591455E-20</v>
+        <v>5.5782434214959665E-20</v>
       </c>
       <c r="W43">
         <f t="shared" si="11"/>
@@ -13616,11 +13616,11 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="12"/>
-        <v>230.28208849374087</v>
+        <v>230.2820885919474</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="13"/>
-        <v>1173.5364718613532</v>
+        <v>1173.5364651328473</v>
       </c>
     </row>
     <row r="44" spans="7:27">
@@ -13658,19 +13658,19 @@
       </c>
       <c r="Q44">
         <f t="shared" si="7"/>
-        <v>-4.5094327104090848</v>
+        <v>-4.5094327146883311</v>
       </c>
       <c r="R44">
         <f t="shared" si="8"/>
-        <v>-37.530673643132197</v>
+        <v>-37.53067361011432</v>
       </c>
       <c r="T44">
         <f t="shared" si="9"/>
-        <v>-45.305099775590776</v>
+        <v>-45.305099746852143</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="10"/>
-        <v>2.1098188364303165E-20</v>
+        <v>2.1098188970636259E-20</v>
       </c>
       <c r="W44">
         <f t="shared" si="11"/>
@@ -13678,11 +13678,11 @@
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="12"/>
-        <v>226.90538847937324</v>
+        <v>226.9053885791825</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="13"/>
-        <v>1279.5406790542038</v>
+        <v>1279.5406719137163</v>
       </c>
     </row>
     <row r="45" spans="7:27">
@@ -13720,19 +13720,19 @@
       </c>
       <c r="Q45">
         <f t="shared" si="7"/>
-        <v>-4.7248225660167549</v>
+        <v>-4.7248225705003968</v>
       </c>
       <c r="R45">
         <f t="shared" si="8"/>
-        <v>-38.287555602775775</v>
+        <v>-38.287555569092028</v>
       </c>
       <c r="T45">
         <f t="shared" si="9"/>
-        <v>-46.277371590842023</v>
+        <v>-46.277371561641914</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="10"/>
-        <v>7.9798160676781034E-21</v>
+        <v>7.9798163006896056E-21</v>
       </c>
       <c r="W45">
         <f t="shared" si="11"/>
@@ -13740,11 +13740,11 @@
       </c>
       <c r="Z45" s="7">
         <f t="shared" si="12"/>
-        <v>223.52868846500567</v>
+        <v>223.52868856641763</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="13"/>
-        <v>1392.0713487825928</v>
+        <v>1392.0713412151367</v>
       </c>
     </row>
     <row r="46" spans="7:27">
@@ -13782,19 +13782,19 @@
       </c>
       <c r="Q46">
         <f t="shared" si="7"/>
-        <v>-4.9402124216244356</v>
+        <v>-4.9402124263124731</v>
       </c>
       <c r="R46">
         <f t="shared" si="8"/>
-        <v>-39.044437562419382</v>
+        <v>-39.044437528069757</v>
       </c>
       <c r="T46">
         <f t="shared" si="9"/>
-        <v>-47.249643406093313</v>
+        <v>-47.24964337643172</v>
       </c>
       <c r="V46" s="7">
         <f t="shared" si="10"/>
-        <v>3.0181484483146086E-21</v>
+        <v>3.0181485378376986E-21</v>
       </c>
       <c r="W46">
         <f t="shared" si="11"/>
@@ -13802,11 +13802,11 @@
       </c>
       <c r="Z46" s="7">
         <f t="shared" si="12"/>
-        <v>220.15198845063793</v>
+        <v>220.15198855365264</v>
       </c>
       <c r="AA46" s="7">
         <f t="shared" si="13"/>
-        <v>1511.3269958081555</v>
+        <v>1511.326987798599</v>
       </c>
     </row>
     <row r="47" spans="7:27">
@@ -13844,19 +13844,19 @@
       </c>
       <c r="Q47">
         <f t="shared" si="7"/>
-        <v>-5.1556022772321102</v>
+        <v>-5.1556022821245424</v>
       </c>
       <c r="R47">
         <f t="shared" si="8"/>
-        <v>-39.801319522062975</v>
+        <v>-39.801319487047486</v>
       </c>
       <c r="T47">
         <f t="shared" si="9"/>
-        <v>-48.221915221344574</v>
+        <v>-48.22191519122152</v>
       </c>
       <c r="V47" s="7">
         <f t="shared" si="10"/>
-        <v>1.1415325840605068E-21</v>
+        <v>1.1415326184469553E-21</v>
       </c>
       <c r="W47">
         <f t="shared" si="11"/>
@@ -13864,11 +13864,11 @@
       </c>
       <c r="Z47" s="7">
         <f t="shared" si="12"/>
-        <v>216.7752884362703</v>
+        <v>216.77528854088766</v>
       </c>
       <c r="AA47" s="7">
         <f t="shared" si="13"/>
-        <v>1637.5045106288528</v>
+        <v>1637.5045021619419</v>
       </c>
     </row>
     <row r="48" spans="7:27">
@@ -13906,19 +13906,19 @@
       </c>
       <c r="Q48">
         <f t="shared" si="7"/>
-        <v>-5.3709921328397838</v>
+        <v>-5.3709921379366117</v>
       </c>
       <c r="R48">
         <f t="shared" si="8"/>
-        <v>-40.558201481706561</v>
+        <v>-40.558201446025194</v>
       </c>
       <c r="T48">
         <f t="shared" si="9"/>
-        <v>-49.194187036595835</v>
+        <v>-49.194187006011298</v>
       </c>
       <c r="V48" s="7">
         <f t="shared" si="10"/>
-        <v>4.3175366049325106E-22</v>
+        <v>4.3175367369823729E-22</v>
       </c>
       <c r="W48">
         <f t="shared" si="11"/>
@@ -13926,11 +13926,11 @@
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="12"/>
-        <v>213.39858842190267</v>
+        <v>213.39858852812276</v>
       </c>
       <c r="AA48" s="7">
         <f t="shared" si="13"/>
-        <v>1770.7990840900338</v>
+        <v>1770.7990751503678</v>
       </c>
     </row>
     <row r="49" spans="7:27">
@@ -13968,19 +13968,19 @@
       </c>
       <c r="Q49">
         <f t="shared" si="7"/>
-        <v>-5.5863819884474584</v>
+        <v>-5.5863819937486809</v>
       </c>
       <c r="R49">
         <f t="shared" si="8"/>
-        <v>-41.315083441350154</v>
+        <v>-41.315083405002916</v>
       </c>
       <c r="T49">
         <f t="shared" si="9"/>
-        <v>-50.166458851847104</v>
+        <v>-50.16645882080109</v>
       </c>
       <c r="V49" s="7">
         <f t="shared" si="10"/>
-        <v>1.6329908226206137E-22</v>
+        <v>1.63299087331847E-22</v>
       </c>
       <c r="W49">
         <f t="shared" si="11"/>
@@ -13988,11 +13988,11 @@
       </c>
       <c r="Z49" s="7">
         <f t="shared" si="12"/>
-        <v>210.02188840753502</v>
+        <v>210.02188851535783</v>
       </c>
       <c r="AA49" s="7">
         <f t="shared" si="13"/>
-        <v>1911.4041403836791</v>
+        <v>1911.4041309557367</v>
       </c>
     </row>
     <row r="50" spans="7:27">
@@ -14030,19 +14030,19 @@
       </c>
       <c r="Q50">
         <f t="shared" si="7"/>
-        <v>-5.801771844055132</v>
+        <v>-5.8017718495607502</v>
       </c>
       <c r="R50">
         <f t="shared" si="8"/>
-        <v>-42.071965400993747</v>
+        <v>-42.071965363980638</v>
       </c>
       <c r="T50">
         <f t="shared" si="9"/>
-        <v>-51.138730667098372</v>
+        <v>-51.138730635590882</v>
       </c>
       <c r="V50" s="7">
         <f t="shared" si="10"/>
-        <v>6.1763437598112324E-23</v>
+        <v>6.176343954412325E-23</v>
       </c>
       <c r="W50">
         <f t="shared" si="11"/>
@@ -14050,11 +14050,11 @@
       </c>
       <c r="Z50" s="7">
         <f t="shared" si="12"/>
-        <v>206.64518839316736</v>
+        <v>206.64518850259287</v>
       </c>
       <c r="AA50" s="7">
         <f t="shared" si="13"/>
-        <v>2059.5112777896707</v>
+        <v>2059.5112678578084</v>
       </c>
     </row>
     <row r="51" spans="7:27">
@@ -14092,19 +14092,19 @@
       </c>
       <c r="Q51">
         <f t="shared" si="7"/>
-        <v>-6.0171616996628066</v>
+        <v>-6.0171617053728195</v>
       </c>
       <c r="R51">
         <f t="shared" si="8"/>
-        <v>-42.828847360637333</v>
+        <v>-42.828847322958353</v>
       </c>
       <c r="T51">
         <f t="shared" si="9"/>
-        <v>-52.111002482349633</v>
+        <v>-52.111002450380667</v>
       </c>
       <c r="V51" s="7">
         <f t="shared" si="10"/>
-        <v>2.3360340861034966E-23</v>
+        <v>2.3360341607840924E-23</v>
       </c>
       <c r="W51">
         <f t="shared" si="11"/>
@@ -14112,11 +14112,11 @@
       </c>
       <c r="Z51" s="7">
         <f t="shared" si="12"/>
-        <v>203.26848837879973</v>
+        <v>203.26848848982794</v>
       </c>
       <c r="AA51" s="7">
         <f t="shared" si="13"/>
-        <v>2215.3102165608261</v>
+        <v>2215.3102061092782</v>
       </c>
     </row>
     <row r="52" spans="7:27">
@@ -14154,19 +14154,19 @@
       </c>
       <c r="Q52">
         <f t="shared" si="7"/>
-        <v>-6.2325515552704802</v>
+        <v>-6.2325515611848887</v>
       </c>
       <c r="R52">
         <f t="shared" si="8"/>
-        <v>-43.585729320280926</v>
+        <v>-43.585729281936068</v>
       </c>
       <c r="T52">
         <f t="shared" si="9"/>
-        <v>-53.083274297600894</v>
+        <v>-53.083274265170445</v>
       </c>
       <c r="V52" s="7">
         <f t="shared" si="10"/>
-        <v>8.8354137393482481E-24</v>
+        <v>8.835414025884691E-24</v>
       </c>
       <c r="W52">
         <f t="shared" si="11"/>
@@ -14174,11 +14174,11 @@
       </c>
       <c r="Z52" s="7">
         <f t="shared" si="12"/>
-        <v>199.8917883644321</v>
+        <v>199.89178847706305</v>
       </c>
       <c r="AA52" s="7">
         <f t="shared" si="13"/>
-        <v>2378.9887533977858</v>
+        <v>2378.9887424106646</v>
       </c>
     </row>
     <row r="53" spans="7:27">
@@ -14216,19 +14216,19 @@
       </c>
       <c r="Q53">
         <f t="shared" si="7"/>
-        <v>-6.4479414108781548</v>
+        <v>-6.447941416996958</v>
       </c>
       <c r="R53">
         <f t="shared" si="8"/>
-        <v>-44.342611279924512</v>
+        <v>-44.34261124091379</v>
       </c>
       <c r="T53">
         <f t="shared" si="9"/>
-        <v>-54.055546112852156</v>
+        <v>-54.055546079960237</v>
       </c>
       <c r="V53" s="7">
         <f t="shared" si="10"/>
-        <v>3.3417550030562869E-24</v>
+        <v>3.3417551129730219E-24</v>
       </c>
       <c r="W53">
         <f t="shared" si="11"/>
@@ -14236,11 +14236,11 @@
       </c>
       <c r="Z53" s="7">
         <f t="shared" si="12"/>
-        <v>196.51508835006447</v>
+        <v>196.51508846429812</v>
       </c>
       <c r="AA53" s="7">
         <f t="shared" si="13"/>
-        <v>2550.7327220007846</v>
+        <v>2550.7327104620949</v>
       </c>
     </row>
     <row r="54" spans="7:27">
@@ -14278,19 +14278,19 @@
       </c>
       <c r="Q54">
         <f t="shared" si="7"/>
-        <v>-6.6633312664858284</v>
+        <v>-6.6633312728090273</v>
       </c>
       <c r="R54">
         <f t="shared" si="8"/>
-        <v>-45.099493239568105</v>
+        <v>-45.099493199891505</v>
       </c>
       <c r="T54">
         <f t="shared" si="9"/>
-        <v>-55.027817928103424</v>
+        <v>-55.027817894750022</v>
       </c>
       <c r="V54" s="7">
         <f t="shared" si="10"/>
-        <v>1.263927964201415E-24</v>
+        <v>1.2639280063577129E-24</v>
       </c>
       <c r="W54">
         <f t="shared" si="11"/>
@@ -14298,11 +14298,11 @@
       </c>
       <c r="Z54" s="7">
         <f t="shared" si="12"/>
-        <v>193.13838833569682</v>
+        <v>193.13838845153319</v>
       </c>
       <c r="AA54" s="7">
         <f t="shared" si="13"/>
-        <v>2730.7259592232072</v>
+        <v>2730.7259471168354</v>
       </c>
     </row>
     <row r="55" spans="7:27">
@@ -14340,19 +14340,19 @@
       </c>
       <c r="Q55">
         <f t="shared" si="7"/>
-        <v>-6.8787211220935021</v>
+        <v>-6.8787211286210965</v>
       </c>
       <c r="R55">
         <f t="shared" si="8"/>
-        <v>-45.856375199211691</v>
+        <v>-45.85637515886922</v>
       </c>
       <c r="T55">
         <f t="shared" si="9"/>
-        <v>-56.000089743354685</v>
+        <v>-56.000089709539807</v>
       </c>
       <c r="V55" s="7">
         <f t="shared" si="10"/>
-        <v>4.7804638497714464E-25</v>
+        <v>4.7804640114222511E-25</v>
       </c>
       <c r="W55">
         <f t="shared" si="11"/>
@@ -14360,11 +14360,11 @@
       </c>
       <c r="Z55" s="7">
         <f t="shared" si="12"/>
-        <v>189.76168832132919</v>
+        <v>189.76168843876826</v>
       </c>
       <c r="AA55" s="7">
         <f t="shared" si="13"/>
-        <v>2919.1502763867638</v>
+        <v>2919.1502636964947</v>
       </c>
     </row>
     <row r="56" spans="7:27">
@@ -14402,19 +14402,19 @@
       </c>
       <c r="Q56">
         <f t="shared" si="7"/>
-        <v>-7.0941109777011766</v>
+        <v>-7.0941109844331658</v>
       </c>
       <c r="R56">
         <f t="shared" si="8"/>
-        <v>-46.613257158855291</v>
+        <v>-46.613257117846942</v>
       </c>
       <c r="T56">
         <f t="shared" si="9"/>
-        <v>-56.972361558605961</v>
+        <v>-56.9723615243296</v>
       </c>
       <c r="V56" s="7">
         <f t="shared" si="10"/>
-        <v>1.8080804655200717E-25</v>
+        <v>1.8080805274944922E-25</v>
       </c>
       <c r="W56">
         <f t="shared" si="11"/>
@@ -14422,11 +14422,11 @@
       </c>
       <c r="Z56" s="7">
         <f t="shared" si="12"/>
-        <v>186.3849883069615</v>
+        <v>186.3849884260033</v>
       </c>
       <c r="AA56" s="7">
         <f t="shared" si="13"/>
-        <v>3116.1854353505905</v>
+        <v>3116.1854220600962</v>
       </c>
     </row>
     <row r="57" spans="7:27">
@@ -14464,19 +14464,19 @@
       </c>
       <c r="Q57">
         <f t="shared" si="7"/>
-        <v>-7.3095008333088503</v>
+        <v>-7.3095008402452342</v>
       </c>
       <c r="R57">
         <f t="shared" si="8"/>
-        <v>-47.370139118498869</v>
+        <v>-47.370139076824657</v>
       </c>
       <c r="T57">
         <f t="shared" si="9"/>
-        <v>-57.944633373857215</v>
+        <v>-57.944633339119385</v>
       </c>
       <c r="V57" s="7">
         <f t="shared" si="10"/>
-        <v>6.8385727254304992E-26</v>
+        <v>6.8385729629876827E-26</v>
       </c>
       <c r="W57">
         <f t="shared" si="11"/>
@@ -14484,11 +14484,11 @@
       </c>
       <c r="Z57" s="7">
         <f t="shared" si="12"/>
-        <v>183.0082882925939</v>
+        <v>183.00828841323838</v>
       </c>
       <c r="AA57" s="7">
         <f t="shared" si="13"/>
-        <v>3322.0091289562965</v>
+        <v>3322.0091150491562</v>
       </c>
     </row>
     <row r="58" spans="7:27">
@@ -14526,19 +14526,19 @@
       </c>
       <c r="Q58">
         <f t="shared" si="7"/>
-        <v>-7.5248906889165248</v>
+        <v>-7.5248906960573034</v>
       </c>
       <c r="R58">
         <f t="shared" si="8"/>
-        <v>-48.127021078142462</v>
+        <v>-48.127021035802372</v>
       </c>
       <c r="T58">
         <f t="shared" si="9"/>
-        <v>-58.916905189108476</v>
+        <v>-58.91690515390917</v>
       </c>
       <c r="V58" s="7">
         <f t="shared" si="10"/>
-        <v>2.5865041856723954E-26</v>
+        <v>2.5865042767155509E-26</v>
       </c>
       <c r="W58">
         <f t="shared" si="11"/>
@@ -14546,11 +14546,11 @@
       </c>
       <c r="Z58" s="7">
         <f t="shared" si="12"/>
-        <v>179.63158827822627</v>
+        <v>179.63158840047348</v>
       </c>
       <c r="AA58" s="7">
         <f t="shared" si="13"/>
-        <v>3536.7969654989661</v>
+        <v>3536.7969509586451</v>
       </c>
     </row>
     <row r="59" spans="7:27">
@@ -14588,19 +14588,19 @@
       </c>
       <c r="Q59">
         <f t="shared" si="7"/>
-        <v>-7.7402805445241984</v>
+        <v>-7.7402805518693727</v>
       </c>
       <c r="R59">
         <f t="shared" si="8"/>
-        <v>-48.883903037786055</v>
+        <v>-48.883902994780094</v>
       </c>
       <c r="T59">
         <f t="shared" si="9"/>
-        <v>-59.889177004359745</v>
+        <v>-59.889176968698962</v>
       </c>
       <c r="V59" s="7">
         <f t="shared" si="10"/>
-        <v>9.7827487856095406E-27</v>
+        <v>9.7827491344700248E-27</v>
       </c>
       <c r="W59">
         <f t="shared" si="11"/>
@@ -14608,11 +14608,11 @@
       </c>
       <c r="Z59" s="7">
         <f t="shared" si="12"/>
-        <v>176.25488826385862</v>
+        <v>176.25488838770852</v>
       </c>
       <c r="AA59" s="7">
         <f t="shared" si="13"/>
-        <v>3760.7224568993997</v>
+        <v>3760.7224417092762</v>
       </c>
     </row>
     <row r="60" spans="7:27">
@@ -14650,19 +14650,19 @@
       </c>
       <c r="Q60">
         <f t="shared" si="7"/>
-        <v>-7.955670400131873</v>
+        <v>-7.955670407681442</v>
       </c>
       <c r="R60">
         <f t="shared" si="8"/>
-        <v>-49.640784997429648</v>
+        <v>-49.640784953757816</v>
       </c>
       <c r="T60">
         <f t="shared" si="9"/>
-        <v>-60.861448819611013</v>
+        <v>-60.861448783488747</v>
       </c>
       <c r="V60" s="7">
         <f t="shared" si="10"/>
-        <v>3.7000587253047847E-27</v>
+        <v>3.7000588589592924E-27</v>
       </c>
       <c r="W60">
         <f t="shared" si="11"/>
@@ -14670,11 +14670,11 @@
       </c>
       <c r="Z60" s="7">
         <f t="shared" si="12"/>
-        <v>172.87818824949096</v>
+        <v>172.87818837494359</v>
       </c>
       <c r="AA60" s="7">
         <f t="shared" si="13"/>
-        <v>3993.9570102769267</v>
+        <v>3993.9569944202763</v>
       </c>
     </row>
     <row r="61" spans="7:27">
@@ -14712,19 +14712,19 @@
       </c>
       <c r="Q61">
         <f t="shared" si="7"/>
-        <v>-8.1710602557395475</v>
+        <v>-8.1710602634935121</v>
       </c>
       <c r="R61">
         <f t="shared" si="8"/>
-        <v>-50.397666957073234</v>
+        <v>-50.397666912735531</v>
       </c>
       <c r="T61">
         <f t="shared" si="9"/>
-        <v>-61.833720634862274</v>
+        <v>-61.833720598278532</v>
       </c>
       <c r="V61" s="7">
         <f t="shared" si="10"/>
-        <v>1.3994466045006537E-27</v>
+        <v>1.3994466556976485E-27</v>
       </c>
       <c r="W61">
         <f t="shared" si="11"/>
@@ -14732,11 +14732,11 @@
       </c>
       <c r="Z61" s="7">
         <f t="shared" si="12"/>
-        <v>169.50148823512333</v>
+        <v>169.50148836217866</v>
       </c>
       <c r="AA61" s="7">
         <f t="shared" si="13"/>
-        <v>4236.6699226439305</v>
+        <v>4236.6699061039426</v>
       </c>
     </row>
     <row r="62" spans="7:27">
@@ -14774,19 +14774,19 @@
       </c>
       <c r="Q62">
         <f t="shared" si="7"/>
-        <v>-8.3864501113472212</v>
+        <v>-8.3864501193055805</v>
       </c>
       <c r="R62">
         <f t="shared" si="8"/>
-        <v>-51.154548916716827</v>
+        <v>-51.154548871713246</v>
       </c>
       <c r="T62">
         <f t="shared" si="9"/>
-        <v>-62.805992450113536</v>
+        <v>-62.805992413068317</v>
       </c>
       <c r="V62" s="7">
         <f t="shared" si="10"/>
-        <v>5.293026257811856E-28</v>
+        <v>5.2930264538931735E-28</v>
       </c>
       <c r="W62">
         <f t="shared" si="11"/>
@@ -14794,11 +14794,11 @@
       </c>
       <c r="Z62" s="7">
         <f t="shared" si="12"/>
-        <v>166.1247882207557</v>
+        <v>166.12478834941373</v>
       </c>
       <c r="AA62" s="7">
         <f t="shared" si="13"/>
-        <v>4489.0283784635749</v>
+        <v>4489.0283612233443</v>
       </c>
     </row>
   </sheetData>
@@ -14924,19 +14924,19 @@
       </c>
       <c r="Q2">
         <f>-0.5*$A$13*$C$13*I2</f>
-        <v>12.263790197344846</v>
+        <v>12.263790193146406</v>
       </c>
       <c r="R2">
         <f>-(1 - 0.5*$A$13*$C$13)*M2</f>
-        <v>-0.537840563121467</v>
+        <v>-0.53784056452155016</v>
       </c>
       <c r="T2">
         <f>P2 + Q2 + R2</f>
-        <v>8.4609562121738886</v>
+        <v>8.4609562065753643</v>
       </c>
       <c r="V2" s="7">
         <f>EXP(T2)</f>
-        <v>4726.5754464530355</v>
+        <v>4726.575419991188</v>
       </c>
       <c r="W2">
         <f>$C$7/G2</f>
@@ -14944,11 +14944,11 @@
       </c>
       <c r="Z2" s="7">
         <f>$Y$4*LN(V2) + $Y$7</f>
-        <v>327.8343774033425</v>
+        <v>327.83437738626139</v>
       </c>
       <c r="AA2" s="7">
         <f>(Z2 - W2)^2</f>
-        <v>491.31482509745354</v>
+        <v>491.31482585468024</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -14992,19 +14992,19 @@
       </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q62" si="7">-0.5*$A$13*$C$13*I3</f>
-        <v>11.85977931376345</v>
+        <v>11.859779309703322</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R62" si="8">-(1 - 0.5*$A$13*$C$13)*M3</f>
-        <v>-0.87696982791774947</v>
+        <v>-0.87696983020063923</v>
       </c>
       <c r="T3">
         <f t="shared" ref="T3:T62" si="9">P3 + Q3 + R3</f>
-        <v>7.7178160637962101</v>
+        <v>7.7178160574531915</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:V62" si="10">EXP(T3)</f>
-        <v>2248.0446294983572</v>
+        <v>2248.0446152389682</v>
       </c>
       <c r="W3">
         <f t="shared" ref="W3:W62" si="11">$C$7/G3</f>
@@ -15015,11 +15015,11 @@
       </c>
       <c r="Z3" s="7">
         <f t="shared" ref="Z3:Z62" si="12">$Y$4*LN(V3) + $Y$7</f>
-        <v>325.56705681064221</v>
+        <v>325.56705679128964</v>
       </c>
       <c r="AA3" s="7">
         <f t="shared" ref="AA3:AA62" si="13">(Z3 - W3)^2</f>
-        <v>439.64010947436793</v>
+        <v>439.64011028592165</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -15066,19 +15066,19 @@
       </c>
       <c r="Q4">
         <f t="shared" si="7"/>
-        <v>11.455768430182049</v>
+        <v>11.455768426260232</v>
       </c>
       <c r="R4">
         <f t="shared" si="8"/>
-        <v>-1.2435145963847771</v>
+        <v>-1.2435145996218404</v>
       </c>
       <c r="T4">
         <f t="shared" si="9"/>
-        <v>6.9472604117477808</v>
+        <v>6.9472604045889002</v>
       </c>
       <c r="V4" s="7">
         <f t="shared" si="10"/>
-        <v>1040.2958384659935</v>
+        <v>1040.2958310186398</v>
       </c>
       <c r="W4">
         <f t="shared" si="11"/>
@@ -15089,11 +15089,11 @@
       </c>
       <c r="Z4" s="7">
         <f t="shared" si="12"/>
-        <v>323.21609151624244</v>
+        <v>323.2160914944007</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" si="13"/>
-        <v>396.8527506404846</v>
+        <v>396.85275151071045</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -15136,19 +15136,19 @@
       </c>
       <c r="Q5">
         <f t="shared" si="7"/>
-        <v>11.051757546600653</v>
+        <v>11.051757542817146</v>
       </c>
       <c r="R5">
         <f t="shared" si="8"/>
-        <v>-1.6375266324409499</v>
+        <v>-1.6375266367036883</v>
       </c>
       <c r="T5">
         <f t="shared" si="9"/>
-        <v>6.1492374921102124</v>
+        <v>6.149237484063967</v>
       </c>
       <c r="V5" s="7">
         <f t="shared" si="10"/>
-        <v>468.36012230271689</v>
+        <v>468.36011853417642</v>
       </c>
       <c r="W5">
         <f t="shared" si="11"/>
@@ -15156,11 +15156,11 @@
       </c>
       <c r="Z5" s="7">
         <f t="shared" si="12"/>
-        <v>320.78132358842822</v>
+        <v>320.78132356387914</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="13"/>
-        <v>361.93166319409022</v>
+        <v>361.93166412815827</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -15204,19 +15204,19 @@
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>10.647746663019257</v>
+        <v>10.647746659374061</v>
       </c>
       <c r="R6">
         <f t="shared" si="8"/>
-        <v>-2.0584381944798986</v>
+        <v>-2.0584381998383354</v>
       </c>
       <c r="T6">
         <f t="shared" si="9"/>
-        <v>5.3243150464898674</v>
+        <v>5.3243150374862349</v>
       </c>
       <c r="V6" s="7">
         <f t="shared" si="10"/>
-        <v>205.26771346110047</v>
+        <v>205.26771161294542</v>
       </c>
       <c r="W6">
         <f t="shared" si="11"/>
@@ -15227,11 +15227,11 @@
       </c>
       <c r="Z6" s="7">
         <f t="shared" si="12"/>
-        <v>318.26448520684056</v>
+        <v>318.26448517937047</v>
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="13"/>
-        <v>333.938210968644</v>
+        <v>333.93821197261968</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -15278,19 +15278,19 @@
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>10.243735779437861</v>
+        <v>10.243735775930977</v>
       </c>
       <c r="R7">
         <f t="shared" si="8"/>
-        <v>-2.3730400026303275</v>
+        <v>-2.3730400088077221</v>
       </c>
       <c r="T7">
         <f t="shared" si="9"/>
-        <v>4.6057023547580425</v>
+        <v>4.6057023450737642</v>
       </c>
       <c r="V7" s="7">
         <f t="shared" si="10"/>
-        <v>100.0532310396873</v>
+        <v>100.05323007074396</v>
       </c>
       <c r="W7">
         <f t="shared" si="11"/>
@@ -15301,11 +15301,11 @@
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="12"/>
-        <v>316.07199788436679</v>
+        <v>316.07199785482004</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="13"/>
-        <v>297.95370148174823</v>
+        <v>297.95370250178109</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -15348,19 +15348,19 @@
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>9.8397248958564596</v>
+        <v>9.8397248924878848</v>
       </c>
       <c r="R8">
         <f t="shared" si="8"/>
-        <v>-2.5526858968674198</v>
+        <v>-2.5526859035124607</v>
       </c>
       <c r="T8">
         <f t="shared" si="9"/>
-        <v>4.0220455769395489</v>
+        <v>4.0220455669259332</v>
       </c>
       <c r="V8" s="7">
         <f t="shared" si="10"/>
-        <v>55.815163341321316</v>
+        <v>55.815162782409722</v>
       </c>
       <c r="W8">
         <f t="shared" si="11"/>
@@ -15368,11 +15368,11 @@
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="12"/>
-        <v>314.29126105524256</v>
+        <v>314.29126102469098</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="13"/>
-        <v>252.72790510902956</v>
+        <v>252.72790608041191</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -15416,19 +15416,19 @@
       </c>
       <c r="Q9">
         <f t="shared" si="7"/>
-        <v>9.4357140122750636</v>
+        <v>9.4357140090448013</v>
       </c>
       <c r="R9">
         <f t="shared" si="8"/>
-        <v>-2.7323317911045093</v>
+        <v>-2.7323317982171971</v>
       </c>
       <c r="T9">
         <f t="shared" si="9"/>
-        <v>3.4383887991210633</v>
+        <v>3.4383887887781133</v>
       </c>
       <c r="V9" s="7">
         <f t="shared" si="10"/>
-        <v>31.136750172342467</v>
+        <v>31.136749850296617</v>
       </c>
       <c r="W9">
         <f t="shared" si="11"/>
@@ -15439,11 +15439,11 @@
       </c>
       <c r="Z9" s="7">
         <f t="shared" si="12"/>
-        <v>312.51052422611832</v>
+        <v>312.51052419456198</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="13"/>
-        <v>212.9346213621547</v>
+        <v>212.93462228311256</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -15490,19 +15490,19 @@
       </c>
       <c r="Q10">
         <f t="shared" si="7"/>
-        <v>9.0317031286936693</v>
+        <v>9.031703125601716</v>
       </c>
       <c r="R10">
         <f t="shared" si="8"/>
-        <v>-2.9119776853415997</v>
+        <v>-2.9119776929219339</v>
       </c>
       <c r="T10">
         <f t="shared" si="9"/>
-        <v>2.8547320213025786</v>
+        <v>2.8547320106302911</v>
       </c>
       <c r="V10" s="7">
         <f t="shared" si="10"/>
-        <v>17.369781852400802</v>
+        <v>17.369781667025496</v>
       </c>
       <c r="W10">
         <f t="shared" si="11"/>
@@ -15510,15 +15510,15 @@
       </c>
       <c r="Y10" s="7">
         <f>AVERAGE(AA18:AA35)</f>
-        <v>6.5762933971230231</v>
+        <v>6.5762933971230124</v>
       </c>
       <c r="Z10" s="7">
         <f t="shared" si="12"/>
-        <v>310.72978739699414</v>
+        <v>310.72978736443298</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="13"/>
-        <v>178.06998692009307</v>
+        <v>178.069987789104</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -15561,19 +15561,19 @@
       </c>
       <c r="Q11">
         <f t="shared" si="7"/>
-        <v>8.6276922451122662</v>
+        <v>8.6276922421586253</v>
       </c>
       <c r="R11">
         <f t="shared" si="8"/>
-        <v>-3.0916235795786911</v>
+        <v>-3.0916235876266716</v>
       </c>
       <c r="T11">
         <f t="shared" si="9"/>
-        <v>2.2710752434840842</v>
+        <v>2.2710752324824628</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" si="10"/>
-        <v>9.6898141241466362</v>
+        <v>9.6898140175429699</v>
       </c>
       <c r="W11">
         <f t="shared" si="11"/>
@@ -15581,11 +15581,11 @@
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="12"/>
-        <v>308.9490505678699</v>
+        <v>308.94905053430398</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="13"/>
-        <v>147.6678682639205</v>
+        <v>147.66786907969782</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -15631,19 +15631,19 @@
       </c>
       <c r="Q12">
         <f t="shared" si="7"/>
-        <v>8.2236813615308719</v>
+        <v>8.22368135871554</v>
       </c>
       <c r="R12">
         <f t="shared" si="8"/>
-        <v>-3.271269473815781</v>
+        <v>-3.2712694823314079</v>
       </c>
       <c r="T12">
         <f t="shared" si="9"/>
-        <v>1.6874184656655999</v>
+        <v>1.6874184543346411</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="10"/>
-        <v>5.4055081726622296</v>
+        <v>5.4055081114126393</v>
       </c>
       <c r="W12">
         <f t="shared" si="11"/>
@@ -15651,19 +15651,19 @@
       </c>
       <c r="Z12" s="7">
         <f t="shared" si="12"/>
-        <v>307.16831373874572</v>
+        <v>307.16831370417498</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="13"/>
-        <v>121.29728011757564</v>
+        <v>121.29728087906578</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13" s="5">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="C13" s="9">
-        <v>0.94018490195138948</v>
+        <v>0.90181000768546027</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -15702,19 +15702,19 @@
       </c>
       <c r="Q13">
         <f t="shared" si="7"/>
-        <v>7.8196704779494759</v>
+        <v>7.8196704752724555</v>
       </c>
       <c r="R13">
         <f t="shared" si="8"/>
-        <v>-3.4509153680528715</v>
+        <v>-3.4509153770361447</v>
       </c>
       <c r="T13">
         <f t="shared" si="9"/>
-        <v>1.1037616878471135</v>
+        <v>1.103761676186819</v>
       </c>
       <c r="V13" s="7">
         <f t="shared" si="10"/>
-        <v>3.0154880403643856</v>
+        <v>3.0154880052029074</v>
       </c>
       <c r="W13">
         <f t="shared" si="11"/>
@@ -15722,11 +15722,11 @@
       </c>
       <c r="Z13" s="7">
         <f t="shared" si="12"/>
-        <v>305.38757690962154</v>
+        <v>305.38757687404598</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="13"/>
-        <v>98.5599898518863</v>
+        <v>98.55999055825616</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -15768,19 +15768,19 @@
       </c>
       <c r="Q14">
         <f t="shared" si="7"/>
-        <v>7.4156595943680799</v>
+        <v>7.4156595918293702</v>
       </c>
       <c r="R14">
         <f t="shared" si="8"/>
-        <v>-3.6305612622899619</v>
+        <v>-3.6305612717408815</v>
       </c>
       <c r="T14">
         <f t="shared" si="9"/>
-        <v>0.52010491002862702</v>
+        <v>0.52010489803899684</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="10"/>
-        <v>1.6822041205243856</v>
+        <v>1.6822041003553803</v>
       </c>
       <c r="W14">
         <f t="shared" si="11"/>
@@ -15788,11 +15788,11 @@
       </c>
       <c r="Z14" s="7">
         <f t="shared" si="12"/>
-        <v>303.60684008049731</v>
+        <v>303.60684004391697</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="13"/>
-        <v>79.088293353848144</v>
+        <v>79.088294004477618</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -15833,19 +15833,19 @@
       </c>
       <c r="Q15">
         <f t="shared" si="7"/>
-        <v>7.0116487107866776</v>
+        <v>7.0116487083862795</v>
       </c>
       <c r="R15">
         <f t="shared" si="8"/>
-        <v>-3.8102071565270528</v>
+        <v>-3.8102071664456187</v>
       </c>
       <c r="T15">
         <f t="shared" si="9"/>
-        <v>-6.3551867789866545E-2</v>
+        <v>-6.3551880108830616E-2</v>
       </c>
       <c r="V15" s="7">
         <f t="shared" si="10"/>
-        <v>0.93842544398460037</v>
+        <v>0.93842543242417109</v>
       </c>
       <c r="W15">
         <f t="shared" si="11"/>
@@ -15853,11 +15853,11 @@
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="12"/>
-        <v>301.82610325137313</v>
+        <v>301.82610321378792</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="13"/>
-        <v>62.54294909130406</v>
+        <v>62.54294968578256</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -15898,19 +15898,19 @@
       </c>
       <c r="Q16">
         <f t="shared" si="7"/>
-        <v>6.6076378272052825</v>
+        <v>6.6076378249431951</v>
       </c>
       <c r="R16">
         <f t="shared" si="8"/>
-        <v>-3.9898530507641432</v>
+        <v>-3.9898530611503555</v>
       </c>
       <c r="T16">
         <f t="shared" si="9"/>
-        <v>-0.64720864560835212</v>
+        <v>-0.64720865825665186</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="10"/>
-        <v>0.52350502722772008</v>
+        <v>0.52350502060627169</v>
       </c>
       <c r="W16">
         <f t="shared" si="11"/>
@@ -15918,11 +15918,11 @@
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="12"/>
-        <v>300.04536642224889</v>
+        <v>300.04536638365892</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="13"/>
-        <v>48.611258218592489</v>
+        <v>48.611258756704785</v>
       </c>
     </row>
     <row r="17" spans="3:27">
@@ -15960,19 +15960,19 @@
       </c>
       <c r="Q17">
         <f t="shared" si="7"/>
-        <v>6.2036269436238864</v>
+        <v>6.2036269415001097</v>
       </c>
       <c r="R17">
         <f t="shared" si="8"/>
-        <v>-4.1694989450012345</v>
+        <v>-4.1694989558550937</v>
       </c>
       <c r="T17">
         <f t="shared" si="9"/>
-        <v>-1.2308654234268395</v>
+        <v>-1.2308654364044753</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="10"/>
-        <v>0.29203973026246371</v>
+        <v>0.2920397264724785</v>
       </c>
       <c r="W17">
         <f t="shared" si="11"/>
@@ -15980,11 +15980,11 @@
       </c>
       <c r="Z17" s="7">
         <f t="shared" si="12"/>
-        <v>298.26462959312471</v>
+        <v>298.26462955352991</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="13"/>
-        <v>37.005279582567411</v>
+        <v>37.005280064293252</v>
       </c>
     </row>
     <row r="18" spans="3:27">
@@ -16025,19 +16025,19 @@
       </c>
       <c r="Q18">
         <f t="shared" si="7"/>
-        <v>5.7996160600424851</v>
+        <v>5.7996160580570191</v>
       </c>
       <c r="R18">
         <f t="shared" si="8"/>
-        <v>-4.349144839238325</v>
+        <v>-4.3491448505598305</v>
       </c>
       <c r="T18">
         <f t="shared" si="9"/>
-        <v>-1.8145222012453313</v>
+        <v>-1.8145222145523028</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="10"/>
-        <v>0.16291573073026674</v>
+        <v>0.16291572856235176</v>
       </c>
       <c r="W18">
         <f t="shared" si="11"/>
@@ -16045,11 +16045,11 @@
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="12"/>
-        <v>296.48389276400047</v>
+        <v>296.48389272340091</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="13"/>
-        <v>27.460169410622644</v>
+        <v>27.460169836125932</v>
       </c>
     </row>
     <row r="19" spans="3:27">
@@ -16090,19 +16090,19 @@
       </c>
       <c r="Q19">
         <f t="shared" si="7"/>
-        <v>5.3956051764610891</v>
+        <v>5.3956051746139346</v>
       </c>
       <c r="R19">
         <f t="shared" si="8"/>
-        <v>-4.5287907334754163</v>
+        <v>-4.5287907452645682</v>
       </c>
       <c r="T19">
         <f t="shared" si="9"/>
-        <v>-2.3981789790638186</v>
+        <v>-2.3981789927001249</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="10"/>
-        <v>9.0883303088669889E-2</v>
+        <v>9.0883301849357348E-2</v>
       </c>
       <c r="W19">
         <f t="shared" si="11"/>
@@ -16110,11 +16110,11 @@
       </c>
       <c r="Z19" s="7">
         <f t="shared" si="12"/>
-        <v>294.70315593487629</v>
+        <v>294.70315589327191</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="13"/>
-        <v>19.73263630190575</v>
+        <v>19.732636671530983</v>
       </c>
     </row>
     <row r="20" spans="3:27">
@@ -16152,19 +16152,19 @@
       </c>
       <c r="Q20">
         <f t="shared" si="7"/>
-        <v>4.9915942928796939</v>
+        <v>4.9915942911708493</v>
       </c>
       <c r="R20">
         <f t="shared" si="8"/>
-        <v>-4.7084366277125058</v>
+        <v>-4.7084366399693041</v>
       </c>
       <c r="T20">
         <f t="shared" si="9"/>
-        <v>-2.9818357568823033</v>
+        <v>-2.9818357708479462</v>
       </c>
       <c r="V20" s="7">
         <f t="shared" si="10"/>
-        <v>5.0699676104221304E-2</v>
+        <v>5.0699675396167744E-2</v>
       </c>
       <c r="W20">
         <f t="shared" si="11"/>
@@ -16172,11 +16172,11 @@
       </c>
       <c r="Z20" s="7">
         <f t="shared" si="12"/>
-        <v>292.92241910575206</v>
+        <v>292.92241906314291</v>
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="13"/>
-        <v>13.599502907771219</v>
+        <v>13.599503222035001</v>
       </c>
     </row>
     <row r="21" spans="3:27">
@@ -16217,19 +16217,19 @@
       </c>
       <c r="Q21">
         <f t="shared" si="7"/>
-        <v>4.5875834092982979</v>
+        <v>4.5875834077277649</v>
       </c>
       <c r="R21">
         <f t="shared" si="8"/>
-        <v>-4.8880825219495962</v>
+        <v>-4.88808253467404</v>
       </c>
       <c r="T21">
         <f t="shared" si="9"/>
-        <v>-3.5654925347007898</v>
+        <v>-3.5654925489957665</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="10"/>
-        <v>2.8283051668633666E-2</v>
+        <v>2.8283051264328105E-2</v>
       </c>
       <c r="W21">
         <f t="shared" si="11"/>
@@ -16237,11 +16237,11 @@
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="12"/>
-        <v>291.14168227662788</v>
+        <v>291.14168223301391</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="13"/>
-        <v>8.8563663848685277</v>
+        <v>8.8563666444557807</v>
       </c>
     </row>
     <row r="22" spans="3:27">
@@ -16283,19 +16283,19 @@
       </c>
       <c r="Q22">
         <f t="shared" si="7"/>
-        <v>4.1835725257168965</v>
+        <v>4.1835725242846733</v>
       </c>
       <c r="R22">
         <f t="shared" si="8"/>
-        <v>-5.0677284161866876</v>
+        <v>-5.0677284293787777</v>
       </c>
       <c r="T22">
         <f t="shared" si="9"/>
-        <v>-4.1491493125192829</v>
+        <v>-4.1491493271435953</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="10"/>
-        <v>1.5777832782328038E-2</v>
+        <v>1.5777832551588083E-2</v>
       </c>
       <c r="W22">
         <f t="shared" si="11"/>
@@ -16303,11 +16303,11 @@
       </c>
       <c r="Z22" s="7">
         <f t="shared" si="12"/>
-        <v>289.36094544750364</v>
+        <v>289.36094540288485</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="13"/>
-        <v>5.3163503404984658</v>
+        <v>5.3163505462554346</v>
       </c>
     </row>
     <row r="23" spans="3:27">
@@ -16345,19 +16345,19 @@
       </c>
       <c r="Q23">
         <f t="shared" si="7"/>
-        <v>3.7795616421355005</v>
+        <v>3.7795616408415889</v>
       </c>
       <c r="R23">
         <f t="shared" si="8"/>
-        <v>-5.247374310423778</v>
+        <v>-5.2473743240835145</v>
       </c>
       <c r="T23">
         <f t="shared" si="9"/>
-        <v>-4.7328060903377693</v>
+        <v>-4.7328061052914165</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="10"/>
-        <v>8.8017378825915437E-3</v>
+        <v>8.8017377509734609E-3</v>
       </c>
       <c r="W23">
         <f t="shared" si="11"/>
@@ -16365,11 +16365,11 @@
       </c>
       <c r="Z23" s="7">
         <f t="shared" si="12"/>
-        <v>287.58020861837946</v>
+        <v>287.58020857275585</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="13"/>
-        <v>2.8089415708015113</v>
+        <v>2.8089417237309102</v>
       </c>
     </row>
     <row r="24" spans="3:27">
@@ -16407,19 +16407,19 @@
       </c>
       <c r="Q24">
         <f t="shared" si="7"/>
-        <v>3.3755507585541049</v>
+        <v>3.375550757398504</v>
       </c>
       <c r="R24">
         <f t="shared" si="8"/>
-        <v>-5.4270202046608675</v>
+        <v>-5.4270202187882512</v>
       </c>
       <c r="T24">
         <f t="shared" si="9"/>
-        <v>-5.316462868156254</v>
+        <v>-5.3164628834392387</v>
       </c>
       <c r="V24" s="7">
         <f t="shared" si="10"/>
-        <v>4.9100906837229357E-3</v>
+        <v>4.9100906086820958E-3</v>
       </c>
       <c r="W24">
         <f t="shared" si="11"/>
@@ -16427,11 +16427,11 @@
       </c>
       <c r="Z24" s="7">
         <f t="shared" si="12"/>
-        <v>285.79947178925522</v>
+        <v>285.79947174262685</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="13"/>
-        <v>1.1789054231233898</v>
+        <v>1.1789055243791509</v>
       </c>
     </row>
     <row r="25" spans="3:27">
@@ -16469,19 +16469,19 @@
       </c>
       <c r="Q25">
         <f t="shared" si="7"/>
-        <v>2.9715398749727031</v>
+        <v>2.9715398739554133</v>
       </c>
       <c r="R25">
         <f t="shared" si="8"/>
-        <v>-5.6066660988979597</v>
+        <v>-5.6066661134929898</v>
       </c>
       <c r="T25">
         <f t="shared" si="9"/>
-        <v>-5.9001196459747476</v>
+        <v>-5.9001196615870679</v>
       </c>
       <c r="V25" s="7">
         <f t="shared" si="10"/>
-        <v>2.7391170748297731E-3</v>
+        <v>2.7391170320658002E-3</v>
       </c>
       <c r="W25">
         <f t="shared" si="11"/>
@@ -16489,11 +16489,11 @@
       </c>
       <c r="Z25" s="7">
         <f t="shared" si="12"/>
-        <v>284.01873496013104</v>
+        <v>284.01873491249785</v>
       </c>
       <c r="AA25" s="7">
         <f t="shared" si="13"/>
-        <v>0.28527409919559449</v>
+        <v>0.28527415007838075</v>
       </c>
     </row>
     <row r="26" spans="3:27">
@@ -16531,19 +16531,19 @@
       </c>
       <c r="Q26">
         <f t="shared" si="7"/>
-        <v>2.5675289913913075</v>
+        <v>2.5675289905123284</v>
       </c>
       <c r="R26">
         <f t="shared" si="8"/>
-        <v>-5.7863119931350502</v>
+        <v>-5.7863120081977266</v>
       </c>
       <c r="T26">
         <f t="shared" si="9"/>
-        <v>-6.483776423793234</v>
+        <v>-6.4837764397348892</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="10"/>
-        <v>1.52802928355191E-3</v>
+        <v>1.5280292591925944E-3</v>
       </c>
       <c r="W26">
         <f t="shared" si="11"/>
@@ -16551,11 +16551,11 @@
       </c>
       <c r="Z26" s="7">
         <f t="shared" si="12"/>
-        <v>282.2379981310068</v>
+        <v>282.23799808236885</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="13"/>
-        <v>4.0265981187098107E-4</v>
+        <v>4.0266176384932669E-4</v>
       </c>
     </row>
     <row r="27" spans="3:27">
@@ -16593,19 +16593,19 @@
       </c>
       <c r="Q27">
         <f t="shared" si="7"/>
-        <v>2.1635181078099119</v>
+        <v>2.1635181070692435</v>
       </c>
       <c r="R27">
         <f t="shared" si="8"/>
-        <v>-5.9659578873721406</v>
+        <v>-5.9659579029024634</v>
       </c>
       <c r="T27">
         <f t="shared" si="9"/>
-        <v>-7.0674332016117205</v>
+        <v>-7.0674332178827113</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="10"/>
-        <v>8.5241828939979435E-4</v>
+        <v>8.5241827553010434E-4</v>
       </c>
       <c r="W27">
         <f t="shared" si="11"/>
@@ -16613,11 +16613,11 @@
       </c>
       <c r="Z27" s="7">
         <f t="shared" si="12"/>
-        <v>280.45726130188262</v>
+        <v>280.45726125223985</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="13"/>
-        <v>0.20908789819944473</v>
+        <v>0.20908785280000389</v>
       </c>
     </row>
     <row r="28" spans="3:27">
@@ -16655,19 +16655,19 @@
       </c>
       <c r="Q28">
         <f t="shared" si="7"/>
-        <v>1.7595072242285161</v>
+        <v>1.7595072236261589</v>
       </c>
       <c r="R28">
         <f t="shared" si="8"/>
-        <v>-6.1456037816092302</v>
+        <v>-6.1456037976071993</v>
       </c>
       <c r="T28">
         <f t="shared" si="9"/>
-        <v>-7.6510899794302052</v>
+        <v>-7.6510899960305316</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="10"/>
-        <v>4.755255333943921E-4</v>
+        <v>4.7552552550051308E-4</v>
       </c>
       <c r="W28">
         <f t="shared" si="11"/>
@@ -16675,11 +16675,11 @@
       </c>
       <c r="Z28" s="7">
         <f t="shared" si="12"/>
-        <v>278.67652447275844</v>
+        <v>278.67652442211084</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="13"/>
-        <v>0.80774562173878517</v>
+        <v>0.80774553070006172</v>
       </c>
     </row>
     <row r="29" spans="3:27">
@@ -16717,19 +16717,19 @@
       </c>
       <c r="Q29">
         <f t="shared" si="7"/>
-        <v>1.3554963406471143</v>
+        <v>1.3554963401830677</v>
       </c>
       <c r="R29">
         <f t="shared" si="8"/>
-        <v>-6.3252496758463224</v>
+        <v>-6.3252496923119379</v>
       </c>
       <c r="T29">
         <f t="shared" si="9"/>
-        <v>-8.2347467572486988</v>
+        <v>-8.2347467741783618</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="10"/>
-        <v>2.6527414500835989E-4</v>
+        <v>2.6527414051735803E-4</v>
       </c>
       <c r="W29">
         <f t="shared" si="11"/>
@@ -16737,11 +16737,11 @@
       </c>
       <c r="Z29" s="7">
         <f t="shared" si="12"/>
-        <v>276.89578764363421</v>
+        <v>276.89578759198179</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="13"/>
-        <v>1.7036422231228476</v>
+        <v>1.7036420882856036</v>
       </c>
     </row>
     <row r="30" spans="3:27">
@@ -16779,19 +16779,19 @@
       </c>
       <c r="Q30">
         <f t="shared" si="7"/>
-        <v>0.95148545706571874</v>
+        <v>0.95148545673998308</v>
       </c>
       <c r="R30">
         <f t="shared" si="8"/>
-        <v>-6.5048955700834119</v>
+        <v>-6.5048955870166738</v>
       </c>
       <c r="T30">
         <f t="shared" si="9"/>
-        <v>-8.8184035350671834</v>
+        <v>-8.8184035523261812</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="10"/>
-        <v>1.4798442369140475E-4</v>
+        <v>1.4798442113734194E-4</v>
       </c>
       <c r="W30">
         <f t="shared" si="11"/>
@@ -16799,11 +16799,11 @@
       </c>
       <c r="Z30" s="7">
         <f t="shared" si="12"/>
-        <v>275.11505081451003</v>
+        <v>275.11505076185279</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="13"/>
-        <v>2.8141767352634477</v>
+        <v>2.8141765585930516</v>
       </c>
     </row>
     <row r="31" spans="3:27">
@@ -16841,19 +16841,19 @@
       </c>
       <c r="Q31">
         <f t="shared" si="7"/>
-        <v>0.54747457348432316</v>
+        <v>0.5474745732968983</v>
       </c>
       <c r="R31">
         <f t="shared" si="8"/>
-        <v>-6.6845414643205032</v>
+        <v>-6.6845414817214115</v>
       </c>
       <c r="T31">
         <f t="shared" si="9"/>
-        <v>-9.4020603128856717</v>
+        <v>-9.4020603304740042</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="10"/>
-        <v>8.2553803555137205E-5</v>
+        <v>8.2553802103153462E-5</v>
       </c>
       <c r="W31">
         <f t="shared" si="11"/>
@@ -16861,11 +16861,11 @@
       </c>
       <c r="Z31" s="7">
         <f t="shared" si="12"/>
-        <v>273.33431398538579</v>
+        <v>273.33431393172378</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="13"/>
-        <v>4.0662098517501795</v>
+        <v>4.0662096353329709</v>
       </c>
     </row>
     <row r="32" spans="3:27">
@@ -16903,19 +16903,19 @@
       </c>
       <c r="Q32">
         <f t="shared" si="7"/>
-        <v>0.14346368990292122</v>
+        <v>0.14346368985380722</v>
       </c>
       <c r="R32">
         <f t="shared" si="8"/>
-        <v>-6.8641873585575954</v>
+        <v>-6.8641873764261501</v>
       </c>
       <c r="T32">
         <f t="shared" si="9"/>
-        <v>-9.9857170907041652</v>
+        <v>-9.9857171086218344</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="10"/>
-        <v>4.6053025794335568E-5</v>
+        <v>4.6053024969172699E-5</v>
       </c>
       <c r="W32">
         <f t="shared" si="11"/>
@@ -16923,11 +16923,11 @@
       </c>
       <c r="Z32" s="7">
         <f t="shared" si="12"/>
-        <v>271.55357715626155</v>
+        <v>271.55357710159478</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="13"/>
-        <v>5.3954366587302331</v>
+        <v>5.3954364047694199</v>
       </c>
     </row>
     <row r="33" spans="7:27">
@@ -16965,19 +16965,19 @@
       </c>
       <c r="Q33">
         <f t="shared" si="7"/>
-        <v>-0.2605471936784744</v>
+        <v>-0.26054719358927753</v>
       </c>
       <c r="R33">
         <f t="shared" si="8"/>
-        <v>-7.0438332527946841</v>
+        <v>-7.0438332711308851</v>
       </c>
       <c r="T33">
         <f t="shared" si="9"/>
-        <v>-10.56937386852265</v>
+        <v>-10.569373886769654</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="10"/>
-        <v>2.5690896039662573E-5</v>
+        <v>2.5690895570880695E-5</v>
       </c>
       <c r="W33">
         <f t="shared" si="11"/>
@@ -16985,11 +16985,11 @@
       </c>
       <c r="Z33" s="7">
         <f t="shared" si="12"/>
-        <v>269.77284032713737</v>
+        <v>269.77284027146578</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="13"/>
-        <v>6.7458000667508209</v>
+        <v>6.7457997775627581</v>
       </c>
     </row>
     <row r="34" spans="7:27">
@@ -17027,19 +17027,19 @@
       </c>
       <c r="Q34">
         <f t="shared" si="7"/>
-        <v>-0.66455807725987004</v>
+        <v>-0.66455807703236225</v>
       </c>
       <c r="R34">
         <f t="shared" si="8"/>
-        <v>-7.2234791470317736</v>
+        <v>-7.223479165835621</v>
       </c>
       <c r="T34">
         <f t="shared" si="9"/>
-        <v>-11.153030646341135</v>
+        <v>-11.153030664917475</v>
       </c>
       <c r="V34" s="7">
         <f t="shared" si="10"/>
-        <v>1.4331786629358269E-5</v>
+        <v>1.4331786363126124E-5</v>
       </c>
       <c r="W34">
         <f t="shared" si="11"/>
@@ -17047,11 +17047,11 @@
       </c>
       <c r="Z34" s="7">
         <f t="shared" si="12"/>
-        <v>267.99210349801319</v>
+        <v>267.99210344133678</v>
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="13"/>
-        <v>8.0689421542609399</v>
+        <v>8.0689418322722268</v>
       </c>
     </row>
     <row r="35" spans="7:27">
@@ -17089,19 +17089,19 @@
       </c>
       <c r="Q35">
         <f t="shared" si="7"/>
-        <v>-1.0685689608412656</v>
+        <v>-1.0685689604754471</v>
       </c>
       <c r="R35">
         <f t="shared" si="8"/>
-        <v>-7.4031250412688632</v>
+        <v>-7.4031250605403569</v>
       </c>
       <c r="T35">
         <f t="shared" si="9"/>
-        <v>-11.736687424159619</v>
+        <v>-11.736687443065296</v>
       </c>
       <c r="V35" s="7">
         <f t="shared" si="10"/>
-        <v>7.9950542663964714E-6</v>
+        <v>7.9950541152445583E-6</v>
       </c>
       <c r="W35">
         <f t="shared" si="11"/>
@@ -17109,11 +17109,11 @@
       </c>
       <c r="Z35" s="7">
         <f t="shared" si="12"/>
-        <v>266.21136666888901</v>
+        <v>266.21136661120778</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="13"/>
-        <v>9.3236908397987719</v>
+        <v>9.3236904875427165</v>
       </c>
     </row>
     <row r="36" spans="7:27">
@@ -17151,19 +17151,19 @@
       </c>
       <c r="Q36">
         <f t="shared" si="7"/>
-        <v>-1.4725798444226674</v>
+        <v>-1.472579843918538</v>
       </c>
       <c r="R36">
         <f t="shared" si="8"/>
-        <v>-7.5827709355059572</v>
+        <v>-7.5827709552450973</v>
       </c>
       <c r="T36">
         <f t="shared" si="9"/>
-        <v>-12.320344201978116</v>
+        <v>-12.320344221213126</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="10"/>
-        <v>4.4600784518856455E-6</v>
+        <v>4.4600783660959929E-6</v>
       </c>
       <c r="W36">
         <f t="shared" si="11"/>
@@ -17171,11 +17171,11 @@
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="12"/>
-        <v>264.43062983976472</v>
+        <v>264.43062978107872</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="13"/>
-        <v>10.475579488914468</v>
+        <v>10.475579109028269</v>
       </c>
     </row>
     <row r="37" spans="7:27">
@@ -17213,19 +17213,19 @@
       </c>
       <c r="Q37">
         <f t="shared" si="7"/>
-        <v>-1.876590728004063</v>
+        <v>-1.8765907273616229</v>
       </c>
       <c r="R37">
         <f t="shared" si="8"/>
-        <v>-7.7624168297430458</v>
+        <v>-7.7624168499498332</v>
       </c>
       <c r="T37">
         <f t="shared" si="9"/>
-        <v>-12.904000979796599</v>
+        <v>-12.904000999360948</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="10"/>
-        <v>2.4880756445372812E-6</v>
+        <v>2.4880755958597029E-6</v>
       </c>
       <c r="W37">
         <f t="shared" si="11"/>
@@ -17233,11 +17233,11 @@
       </c>
       <c r="Z37" s="7">
         <f t="shared" si="12"/>
-        <v>262.64989301064054</v>
+        <v>262.64989295094972</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="13"/>
-        <v>11.496397236006421</v>
+        <v>11.496396831227012</v>
       </c>
     </row>
     <row r="38" spans="7:27">
@@ -17275,19 +17275,19 @@
       </c>
       <c r="Q38">
         <f t="shared" si="7"/>
-        <v>-2.2806016115854586</v>
+        <v>-2.2806016108047076</v>
       </c>
       <c r="R38">
         <f t="shared" si="8"/>
-        <v>-7.9420627239801362</v>
+        <v>-7.94206274465457</v>
       </c>
       <c r="T38">
         <f t="shared" si="9"/>
-        <v>-13.487657757615086</v>
+        <v>-13.487657777508769</v>
       </c>
       <c r="V38" s="7">
         <f t="shared" si="10"/>
-        <v>1.3879846463961498E-6</v>
+        <v>1.3879846187840232E-6</v>
       </c>
       <c r="W38">
         <f t="shared" si="11"/>
@@ -17295,11 +17295,11 @@
       </c>
       <c r="Z38" s="7">
         <f t="shared" si="12"/>
-        <v>260.86915618151636</v>
+        <v>260.86915612082072</v>
       </c>
       <c r="AA38" s="7">
         <f t="shared" si="13"/>
-        <v>12.363767961709293</v>
+        <v>12.363767534871451</v>
       </c>
     </row>
     <row r="39" spans="7:27">
@@ -17337,19 +17337,19 @@
       </c>
       <c r="Q39">
         <f t="shared" si="7"/>
-        <v>-2.6846124951668604</v>
+        <v>-2.6846124942477987</v>
       </c>
       <c r="R39">
         <f t="shared" si="8"/>
-        <v>-8.1217086182172302</v>
+        <v>-8.1217086393593103</v>
       </c>
       <c r="T39">
         <f t="shared" si="9"/>
-        <v>-14.071314535433583</v>
+        <v>-14.071314555656601</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" si="10"/>
-        <v>7.7429373293419493E-7</v>
+        <v>7.7429371727563904E-7</v>
       </c>
       <c r="W39">
         <f t="shared" si="11"/>
@@ -17357,11 +17357,11 @@
       </c>
       <c r="Z39" s="7">
         <f t="shared" si="12"/>
-        <v>259.08841935239212</v>
+        <v>259.08841929069172</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="13"/>
-        <v>13.060756014499704</v>
+        <v>13.060755568533279</v>
       </c>
     </row>
     <row r="40" spans="7:27">
@@ -17399,19 +17399,19 @@
       </c>
       <c r="Q40">
         <f t="shared" si="7"/>
-        <v>-3.0886233787482564</v>
+        <v>-3.0886233776908836</v>
       </c>
       <c r="R40">
         <f t="shared" si="8"/>
-        <v>-8.3013545124543171</v>
+        <v>-8.3013545340640444</v>
       </c>
       <c r="T40">
         <f t="shared" si="9"/>
-        <v>-14.654971313252066</v>
+        <v>-14.654971333804419</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="10"/>
-        <v>4.3194338382476935E-7</v>
+        <v>4.3194337494731667E-7</v>
       </c>
       <c r="W40">
         <f t="shared" si="11"/>
@@ -17419,11 +17419,11 @@
       </c>
       <c r="Z40" s="7">
         <f t="shared" si="12"/>
-        <v>257.30768252326794</v>
+        <v>257.30768246056272</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="13"/>
-        <v>13.575496901677703</v>
+        <v>13.575496439603635</v>
       </c>
     </row>
     <row r="41" spans="7:27">
@@ -17461,19 +17461,19 @@
       </c>
       <c r="Q41">
         <f t="shared" si="7"/>
-        <v>-3.492634262329652</v>
+        <v>-3.492634261133968</v>
       </c>
       <c r="R41">
         <f t="shared" si="8"/>
-        <v>-8.4810004066914075</v>
+        <v>-8.4810004287687804</v>
       </c>
       <c r="T41">
         <f t="shared" si="9"/>
-        <v>-15.23862809107055</v>
+        <v>-15.23862811195224</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="10"/>
-        <v>2.4096163883822647E-7</v>
+        <v>2.4096163380654049E-7</v>
       </c>
       <c r="W41">
         <f t="shared" si="11"/>
@@ -17481,11 +17481,11 @@
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="12"/>
-        <v>255.52694569414373</v>
+        <v>255.52694563043369</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="13"/>
-        <v>13.900851300963501</v>
+        <v>13.900850825892395</v>
       </c>
     </row>
     <row r="42" spans="7:27">
@@ -17523,19 +17523,19 @@
       </c>
       <c r="Q42">
         <f t="shared" si="7"/>
-        <v>-3.8966451459110476</v>
+        <v>-3.8966451445770529</v>
       </c>
       <c r="R42">
         <f t="shared" si="8"/>
-        <v>-8.660646300928498</v>
+        <v>-8.660646323473518</v>
       </c>
       <c r="T42">
         <f t="shared" si="9"/>
-        <v>-15.822284868889037</v>
+        <v>-15.822284890100063</v>
       </c>
       <c r="V42" s="7">
         <f t="shared" si="10"/>
-        <v>1.3442157830378663E-7</v>
+        <v>1.3442157545256711E-7</v>
       </c>
       <c r="W42">
         <f t="shared" si="11"/>
@@ -17543,11 +17543,11 @@
       </c>
       <c r="Z42" s="7">
         <f t="shared" si="12"/>
-        <v>253.74620886501953</v>
+        <v>253.74620880030469</v>
       </c>
       <c r="AA42" s="7">
         <f t="shared" si="13"/>
-        <v>14.034080860351308</v>
+        <v>14.0340803754807</v>
       </c>
     </row>
     <row r="43" spans="7:27">
@@ -17585,19 +17585,19 @@
       </c>
       <c r="Q43">
         <f t="shared" si="7"/>
-        <v>-4.3006560294924432</v>
+        <v>-4.3006560280201374</v>
       </c>
       <c r="R43">
         <f t="shared" si="8"/>
-        <v>-8.8402921951655902</v>
+        <v>-8.8402922181782539</v>
       </c>
       <c r="T43">
         <f t="shared" si="9"/>
-        <v>-16.405941646707525</v>
+        <v>-16.405941668247884</v>
       </c>
       <c r="V43" s="7">
         <f t="shared" si="10"/>
-        <v>7.4987706760294883E-8</v>
+        <v>7.4987705145032791E-8</v>
       </c>
       <c r="W43">
         <f t="shared" si="11"/>
@@ -17605,11 +17605,11 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="12"/>
-        <v>251.96547203589532</v>
+        <v>251.96547197017568</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="13"/>
-        <v>13.976544361441373</v>
+        <v>13.976543870052836</v>
       </c>
     </row>
     <row r="44" spans="7:27">
@@ -17647,19 +17647,19 @@
       </c>
       <c r="Q44">
         <f t="shared" si="7"/>
-        <v>-4.7046669130738517</v>
+        <v>-4.7046669114632351</v>
       </c>
       <c r="R44">
         <f t="shared" si="8"/>
-        <v>-9.0199380894026824</v>
+        <v>-9.0199381128829952</v>
       </c>
       <c r="T44">
         <f t="shared" si="9"/>
-        <v>-16.989598424526026</v>
+        <v>-16.989598446395721</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="10"/>
-        <v>4.1832243276148929E-8</v>
+        <v>4.183224236129052E-8</v>
       </c>
       <c r="W44">
         <f t="shared" si="11"/>
@@ -17667,11 +17667,11 @@
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="12"/>
-        <v>250.18473520677108</v>
+        <v>250.18473514004663</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="13"/>
-        <v>13.733412920936535</v>
+        <v>13.733412426393311</v>
       </c>
     </row>
     <row r="45" spans="7:27">
@@ -17709,19 +17709,19 @@
       </c>
       <c r="Q45">
         <f t="shared" si="7"/>
-        <v>-5.1086777966552468</v>
+        <v>-5.1086777949063196</v>
       </c>
       <c r="R45">
         <f t="shared" si="8"/>
-        <v>-9.1995839836397728</v>
+        <v>-9.1995840075877311</v>
       </c>
       <c r="T45">
         <f t="shared" si="9"/>
-        <v>-17.573255202344512</v>
+        <v>-17.573255224543544</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="10"/>
-        <v>2.3336312752019016E-8</v>
+        <v>2.3336312233975469E-8</v>
       </c>
       <c r="W45">
         <f t="shared" si="11"/>
@@ -17729,11 +17729,11 @@
       </c>
       <c r="Z45" s="7">
         <f t="shared" si="12"/>
-        <v>248.40399837764687</v>
+        <v>248.40399830991763</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="13"/>
-        <v>13.313402996993048</v>
+        <v>13.313402502738388</v>
       </c>
     </row>
     <row r="46" spans="7:27">
@@ -17771,19 +17771,19 @@
       </c>
       <c r="Q46">
         <f t="shared" si="7"/>
-        <v>-5.5126886802366428</v>
+        <v>-5.5126886783494049</v>
       </c>
       <c r="R46">
         <f t="shared" si="8"/>
-        <v>-9.379229877876865</v>
+        <v>-9.3792299022924688</v>
       </c>
       <c r="T46">
         <f t="shared" si="9"/>
-        <v>-18.156911980162999</v>
+        <v>-18.156912002691364</v>
       </c>
       <c r="V46" s="7">
         <f t="shared" si="10"/>
-        <v>1.3018271319208575E-8</v>
+        <v>1.3018271025928209E-8</v>
       </c>
       <c r="W46">
         <f t="shared" si="11"/>
@@ -17791,11 +17791,11 @@
       </c>
       <c r="Z46" s="7">
         <f t="shared" si="12"/>
-        <v>246.62326154852266</v>
+        <v>246.62326147978862</v>
       </c>
       <c r="AA46" s="7">
         <f t="shared" si="13"/>
-        <v>12.72852605225391</v>
+        <v>12.728525561808231</v>
       </c>
     </row>
     <row r="47" spans="7:27">
@@ -17833,19 +17833,19 @@
       </c>
       <c r="Q47">
         <f t="shared" si="7"/>
-        <v>-5.916699563818038</v>
+        <v>-5.9166995617924893</v>
       </c>
       <c r="R47">
         <f t="shared" si="8"/>
-        <v>-9.5588757721139519</v>
+        <v>-9.5588757969972029</v>
       </c>
       <c r="T47">
         <f t="shared" si="9"/>
-        <v>-18.740568757981482</v>
+        <v>-18.740568780839183</v>
       </c>
       <c r="V47" s="7">
         <f t="shared" si="10"/>
-        <v>7.2623036013204978E-9</v>
+        <v>7.2623034353209313E-9</v>
       </c>
       <c r="W47">
         <f t="shared" si="11"/>
@@ -17853,11 +17853,11 @@
       </c>
       <c r="Z47" s="7">
         <f t="shared" si="12"/>
-        <v>244.84252471939848</v>
+        <v>244.84252464965962</v>
       </c>
       <c r="AA47" s="7">
         <f t="shared" si="13"/>
-        <v>11.993853804234876</v>
+        <v>11.993853321193635</v>
       </c>
     </row>
     <row r="48" spans="7:27">
@@ -17895,19 +17895,19 @@
       </c>
       <c r="Q48">
         <f t="shared" si="7"/>
-        <v>-6.320710447399434</v>
+        <v>-6.3207104452355738</v>
       </c>
       <c r="R48">
         <f t="shared" si="8"/>
-        <v>-9.7385216663510423</v>
+        <v>-9.7385216917019388</v>
       </c>
       <c r="T48">
         <f t="shared" si="9"/>
-        <v>-19.324225535799968</v>
+        <v>-19.324225558987003</v>
       </c>
       <c r="V48" s="7">
         <f t="shared" si="10"/>
-        <v>4.0513100629522593E-9</v>
+        <v>4.0513099690143947E-9</v>
       </c>
       <c r="W48">
         <f t="shared" si="11"/>
@@ -17915,11 +17915,11 @@
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="12"/>
-        <v>243.06178789027427</v>
+        <v>243.06178781953065</v>
       </c>
       <c r="AA48" s="7">
         <f t="shared" si="13"/>
-        <v>11.127298066753525</v>
+        <v>11.127297594785956</v>
       </c>
     </row>
     <row r="49" spans="7:27">
@@ -17957,19 +17957,19 @@
       </c>
       <c r="Q49">
         <f t="shared" si="7"/>
-        <v>-6.7247213309808291</v>
+        <v>-6.7247213286786591</v>
       </c>
       <c r="R49">
         <f t="shared" si="8"/>
-        <v>-9.9181675605881363</v>
+        <v>-9.9181675864066801</v>
       </c>
       <c r="T49">
         <f t="shared" si="9"/>
-        <v>-19.907882313618458</v>
+        <v>-19.907882337134829</v>
       </c>
       <c r="V49" s="7">
         <f t="shared" si="10"/>
-        <v>2.2600422850944708E-9</v>
+        <v>2.2600422319464786E-9</v>
       </c>
       <c r="W49">
         <f t="shared" si="11"/>
@@ -17977,11 +17977,11 @@
       </c>
       <c r="Z49" s="7">
         <f t="shared" si="12"/>
-        <v>241.28105106115007</v>
+        <v>241.28105098940162</v>
       </c>
       <c r="AA49" s="7">
         <f t="shared" si="13"/>
-        <v>10.149404253773328</v>
+        <v>10.149403796619078</v>
       </c>
     </row>
     <row r="50" spans="7:27">
@@ -18019,19 +18019,19 @@
       </c>
       <c r="Q50">
         <f t="shared" si="7"/>
-        <v>-7.1287322145622252</v>
+        <v>-7.1287322121217436</v>
       </c>
       <c r="R50">
         <f t="shared" si="8"/>
-        <v>-10.097813454825223</v>
+        <v>-10.097813481111412</v>
       </c>
       <c r="T50">
         <f t="shared" si="9"/>
-        <v>-20.491539091436941</v>
+        <v>-20.491539115282649</v>
       </c>
       <c r="V50" s="7">
         <f t="shared" si="10"/>
-        <v>1.2607751692776975E-9</v>
+        <v>1.2607751392136216E-9</v>
       </c>
       <c r="W50">
         <f t="shared" si="11"/>
@@ -18039,11 +18039,11 @@
       </c>
       <c r="Z50" s="7">
         <f t="shared" si="12"/>
-        <v>239.50031423202586</v>
+        <v>239.50031415927262</v>
       </c>
       <c r="AA50" s="7">
         <f t="shared" si="13"/>
-        <v>9.0831576797832838</v>
+        <v>9.0831572412518344</v>
       </c>
     </row>
     <row r="51" spans="7:27">
@@ -18081,19 +18081,19 @@
       </c>
       <c r="Q51">
         <f t="shared" si="7"/>
-        <v>-7.5327430981436327</v>
+        <v>-7.5327430955648413</v>
       </c>
       <c r="R51">
         <f t="shared" si="8"/>
-        <v>-10.277459349062317</v>
+        <v>-10.277459375816154</v>
       </c>
       <c r="T51">
         <f t="shared" si="9"/>
-        <v>-21.075195869255442</v>
+        <v>-21.075195893430486</v>
       </c>
       <c r="V51" s="7">
         <f t="shared" si="10"/>
-        <v>7.0332933058406655E-10</v>
+        <v>7.0332931358104914E-10</v>
       </c>
       <c r="W51">
         <f t="shared" si="11"/>
@@ -18101,11 +18101,11 @@
       </c>
       <c r="Z51" s="7">
         <f t="shared" si="12"/>
-        <v>237.71957740290162</v>
+        <v>237.71957732914356</v>
       </c>
       <c r="AA51" s="7">
         <f t="shared" si="13"/>
-        <v>7.9538018490388245</v>
+        <v>7.9538014330067117</v>
       </c>
     </row>
     <row r="52" spans="7:27">
@@ -18143,19 +18143,19 @@
       </c>
       <c r="Q52">
         <f t="shared" si="7"/>
-        <v>-7.9367539817250288</v>
+        <v>-7.9367539790079258</v>
       </c>
       <c r="R52">
         <f t="shared" si="8"/>
-        <v>-10.457105243299404</v>
+        <v>-10.457105270520886</v>
       </c>
       <c r="T52">
         <f t="shared" si="9"/>
-        <v>-21.658852647073925</v>
+        <v>-21.658852671578302</v>
       </c>
       <c r="V52" s="7">
         <f t="shared" si="10"/>
-        <v>3.9235555974919729E-10</v>
+        <v>3.9235555013476882E-10</v>
       </c>
       <c r="W52">
         <f t="shared" si="11"/>
@@ -18163,11 +18163,11 @@
       </c>
       <c r="Z52" s="7">
         <f t="shared" si="12"/>
-        <v>235.93884057377744</v>
+        <v>235.93884049901459</v>
       </c>
       <c r="AA52" s="7">
         <f t="shared" si="13"/>
-        <v>6.7886679800070615</v>
+        <v>6.7886675904167637</v>
       </c>
     </row>
     <row r="53" spans="7:27">
@@ -18205,19 +18205,19 @@
       </c>
       <c r="Q53">
         <f t="shared" si="7"/>
-        <v>-8.3407648653064239</v>
+        <v>-8.3407648624510102</v>
       </c>
       <c r="R53">
         <f t="shared" si="8"/>
-        <v>-10.636751137536498</v>
+        <v>-10.636751165225627</v>
       </c>
       <c r="T53">
         <f t="shared" si="9"/>
-        <v>-22.242509424892411</v>
+        <v>-22.242509449726128</v>
       </c>
       <c r="V53" s="7">
         <f t="shared" si="10"/>
-        <v>2.1887738584464612E-10</v>
+        <v>2.1887738040910705E-10</v>
       </c>
       <c r="W53">
         <f t="shared" si="11"/>
@@ -18225,11 +18225,11 @@
       </c>
       <c r="Z53" s="7">
         <f t="shared" si="12"/>
-        <v>234.15810374465323</v>
+        <v>234.15810366888556</v>
       </c>
       <c r="AA53" s="7">
         <f t="shared" si="13"/>
-        <v>5.6170150615042225</v>
+        <v>5.6170147023617805</v>
       </c>
     </row>
     <row r="54" spans="7:27">
@@ -18267,19 +18267,19 @@
       </c>
       <c r="Q54">
         <f t="shared" si="7"/>
-        <v>-8.7447757488878199</v>
+        <v>-8.7447757458940956</v>
       </c>
       <c r="R54">
         <f t="shared" si="8"/>
-        <v>-10.816397031773588</v>
+        <v>-10.816397059930363</v>
       </c>
       <c r="T54">
         <f t="shared" si="9"/>
-        <v>-22.826166202710901</v>
+        <v>-22.826166227873948</v>
       </c>
       <c r="V54" s="7">
         <f t="shared" si="10"/>
-        <v>1.2210177438242336E-10</v>
+        <v>1.2210177130997075E-10</v>
       </c>
       <c r="W54">
         <f t="shared" si="11"/>
@@ -18287,11 +18287,11 @@
       </c>
       <c r="Z54" s="7">
         <f t="shared" si="12"/>
-        <v>232.37736691552902</v>
+        <v>232.37736683875656</v>
       </c>
       <c r="AA54" s="7">
         <f t="shared" si="13"/>
-        <v>4.4698797835993638</v>
+        <v>4.4698794589732902</v>
       </c>
     </row>
     <row r="55" spans="7:27">
@@ -18329,19 +18329,19 @@
       </c>
       <c r="Q55">
         <f t="shared" si="7"/>
-        <v>-9.148786632469216</v>
+        <v>-9.1487866293371791</v>
       </c>
       <c r="R55">
         <f t="shared" si="8"/>
-        <v>-10.996042926010679</v>
+        <v>-10.996042954635101</v>
       </c>
       <c r="T55">
         <f t="shared" si="9"/>
-        <v>-23.409822980529384</v>
+        <v>-23.409823006021771</v>
       </c>
       <c r="V55" s="7">
         <f t="shared" si="10"/>
-        <v>6.81150464667842E-11</v>
+        <v>6.8115044730369114E-11</v>
       </c>
       <c r="W55">
         <f t="shared" si="11"/>
@@ -18349,11 +18349,11 @@
       </c>
       <c r="Z55" s="7">
         <f t="shared" si="12"/>
-        <v>230.59663008640484</v>
+        <v>230.59663000862756</v>
       </c>
       <c r="AA55" s="7">
         <f t="shared" si="13"/>
-        <v>3.3799357296255601</v>
+        <v>3.3799354436446811</v>
       </c>
     </row>
     <row r="56" spans="7:27">
@@ -18391,19 +18391,19 @@
       </c>
       <c r="Q56">
         <f t="shared" si="7"/>
-        <v>-9.5527975160506102</v>
+        <v>-9.5527975127802645</v>
       </c>
       <c r="R56">
         <f t="shared" si="8"/>
-        <v>-11.175688820247766</v>
+        <v>-11.175688849339835</v>
       </c>
       <c r="T56">
         <f t="shared" si="9"/>
-        <v>-23.993479758347867</v>
+        <v>-23.99347978416959</v>
       </c>
       <c r="V56" s="7">
         <f t="shared" si="10"/>
-        <v>3.7998297556600073E-11</v>
+        <v>3.7998296575418554E-11</v>
       </c>
       <c r="W56">
         <f t="shared" si="11"/>
@@ -18411,11 +18411,11 @@
       </c>
       <c r="Z56" s="7">
         <f t="shared" si="12"/>
-        <v>228.81589325728063</v>
+        <v>228.81589317849856</v>
       </c>
       <c r="AA56" s="7">
         <f t="shared" si="13"/>
-        <v>2.381361255882787</v>
+        <v>2.3813610127351428</v>
       </c>
     </row>
     <row r="57" spans="7:27">
@@ -18453,19 +18453,19 @@
       </c>
       <c r="Q57">
         <f t="shared" si="7"/>
-        <v>-9.9568083996320063</v>
+        <v>-9.9568083962233498</v>
       </c>
       <c r="R57">
         <f t="shared" si="8"/>
-        <v>-11.355334714484856</v>
+        <v>-11.355334744044571</v>
       </c>
       <c r="T57">
         <f t="shared" si="9"/>
-        <v>-24.577136536166353</v>
+        <v>-24.577136562317413</v>
       </c>
       <c r="V57" s="7">
         <f t="shared" si="10"/>
-        <v>2.1197528183497705E-11</v>
+        <v>2.119752762915988E-11</v>
       </c>
       <c r="W57">
         <f t="shared" si="11"/>
@@ -18473,11 +18473,11 @@
       </c>
       <c r="Z57" s="7">
         <f t="shared" si="12"/>
-        <v>227.03515642815643</v>
+        <v>227.03515634836955</v>
       </c>
       <c r="AA57" s="7">
         <f t="shared" si="13"/>
-        <v>1.5097155230265982</v>
+        <v>1.5097153269575763</v>
       </c>
     </row>
     <row r="58" spans="7:27">
@@ -18515,19 +18515,19 @@
       </c>
       <c r="Q58">
         <f t="shared" si="7"/>
-        <v>-10.360819283213415</v>
+        <v>-10.360819279666448</v>
       </c>
       <c r="R58">
         <f t="shared" si="8"/>
-        <v>-11.53498060872195</v>
+        <v>-11.534980638749312</v>
       </c>
       <c r="T58">
         <f t="shared" si="9"/>
-        <v>-25.160793313984854</v>
+        <v>-25.160793340465251</v>
       </c>
       <c r="V58" s="7">
         <f t="shared" si="10"/>
-        <v>1.1825140334797086E-11</v>
+        <v>1.1825140021662686E-11</v>
       </c>
       <c r="W58">
         <f t="shared" si="11"/>
@@ -18535,11 +18535,11 @@
       </c>
       <c r="Z58" s="7">
         <f t="shared" si="12"/>
-        <v>225.25441959903219</v>
+        <v>225.2544195182405</v>
       </c>
       <c r="AA58" s="7">
         <f t="shared" si="13"/>
-        <v>0.8018221779423681</v>
+        <v>0.80182203325330015</v>
       </c>
     </row>
     <row r="59" spans="7:27">
@@ -18577,19 +18577,19 @@
       </c>
       <c r="Q59">
         <f t="shared" si="7"/>
-        <v>-10.764830166794811</v>
+        <v>-10.764830163109531</v>
       </c>
       <c r="R59">
         <f t="shared" si="8"/>
-        <v>-11.714626502959044</v>
+        <v>-11.714626533454052</v>
       </c>
       <c r="T59">
         <f t="shared" si="9"/>
-        <v>-25.744450091803344</v>
+        <v>-25.744450118613074</v>
       </c>
       <c r="V59" s="7">
         <f t="shared" si="10"/>
-        <v>6.596709895944722E-12</v>
+        <v>6.596709719088716E-12</v>
       </c>
       <c r="W59">
         <f t="shared" si="11"/>
@@ -18597,11 +18597,11 @@
       </c>
       <c r="Z59" s="7">
         <f t="shared" si="12"/>
-        <v>223.47368276990798</v>
+        <v>223.4736826881115</v>
       </c>
       <c r="AA59" s="7">
         <f t="shared" si="13"/>
-        <v>0.295660217303434</v>
+        <v>0.29566012835034056</v>
       </c>
     </row>
     <row r="60" spans="7:27">
@@ -18639,19 +18639,19 @@
       </c>
       <c r="Q60">
         <f t="shared" si="7"/>
-        <v>-11.168841050376207</v>
+        <v>-11.168841046552616</v>
       </c>
       <c r="R60">
         <f t="shared" si="8"/>
-        <v>-11.894272397196131</v>
+        <v>-11.894272428158786</v>
       </c>
       <c r="T60">
         <f t="shared" si="9"/>
-        <v>-26.328106869621827</v>
+        <v>-26.328106896760893</v>
       </c>
       <c r="V60" s="7">
         <f t="shared" si="10"/>
-        <v>3.680005498387352E-12</v>
+        <v>3.6800053985154406E-12</v>
       </c>
       <c r="W60">
         <f t="shared" si="11"/>
@@ -18659,11 +18659,11 @@
       </c>
       <c r="Z60" s="7">
         <f t="shared" si="12"/>
-        <v>221.69294594078377</v>
+        <v>221.69294585798249</v>
       </c>
       <c r="AA60" s="7">
         <f t="shared" si="13"/>
-        <v>3.0261594170107743E-2</v>
+        <v>3.0261565362125712E-2</v>
       </c>
     </row>
     <row r="61" spans="7:27">
@@ -18701,19 +18701,19 @@
       </c>
       <c r="Q61">
         <f t="shared" si="7"/>
-        <v>-11.572851933957601</v>
+        <v>-11.572851929995702</v>
       </c>
       <c r="R61">
         <f t="shared" si="8"/>
-        <v>-12.073918291433221</v>
+        <v>-12.073918322863523</v>
       </c>
       <c r="T61">
         <f t="shared" si="9"/>
-        <v>-26.911763647440313</v>
+        <v>-26.911763674908716</v>
       </c>
       <c r="V61" s="7">
         <f t="shared" si="10"/>
-        <v>2.052908295465018E-12</v>
+        <v>2.0529082390749072E-12</v>
       </c>
       <c r="W61">
         <f t="shared" si="11"/>
@@ -18721,11 +18721,11 @@
       </c>
       <c r="Z61" s="7">
         <f t="shared" si="12"/>
-        <v>219.91220911165959</v>
+        <v>219.91220902785346</v>
       </c>
       <c r="AA61" s="7">
         <f t="shared" si="13"/>
-        <v>4.5615157082216681E-2</v>
+        <v>4.5615192880355308E-2</v>
       </c>
     </row>
     <row r="62" spans="7:27">
@@ -18763,19 +18763,19 @@
       </c>
       <c r="Q62">
         <f t="shared" si="7"/>
-        <v>-11.976862817538997</v>
+        <v>-11.976862813438785</v>
       </c>
       <c r="R62">
         <f t="shared" si="8"/>
-        <v>-12.25356418567031</v>
+        <v>-12.253564217568256</v>
       </c>
       <c r="T62">
         <f t="shared" si="9"/>
-        <v>-27.4954204252588</v>
+        <v>-27.495420453056532</v>
       </c>
       <c r="V62" s="7">
         <f t="shared" si="10"/>
-        <v>1.1452245034514024E-12</v>
+        <v>1.1452244716167588E-12</v>
       </c>
       <c r="W62">
         <f t="shared" si="11"/>
@@ -18783,11 +18783,11 @@
       </c>
       <c r="Z62" s="7">
         <f t="shared" si="12"/>
-        <v>218.13147228253538</v>
+        <v>218.13147219772449</v>
       </c>
       <c r="AA62" s="7">
         <f t="shared" si="13"/>
-        <v>0.38257653727188234</v>
+        <v>0.38257664218766507</v>
       </c>
     </row>
   </sheetData>
